--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -1453,11 +1453,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2760,7 +2764,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -2768,7 +2773,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -2991,7 +2996,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3223,7 +3228,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3446,7 +3451,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3678,7 +3683,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3901,7 +3906,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -9131,7 +9136,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -9354,7 +9359,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -10,7 +10,6 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="Time Estimator" sheetId="2" r:id="rId4"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
     <sheet name="Tree 3" sheetId="10" r:id="rId13"/>
@@ -19,9 +18,12 @@
     <sheet name="Tree 6" sheetId="13" r:id="rId16"/>
     <sheet name="Tree 7" sheetId="14" r:id="rId17"/>
     <sheet name="Tree 8" sheetId="15" r:id="rId18"/>
+    <sheet name="Names to Print A" sheetId="16" r:id="rId19"/>
+    <sheet name="Names to Print B" sheetId="17" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$91</definedName>
+    <definedName localSheetId="11" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
+    <definedName localSheetId="12" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$404</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
   <si>
     <t>Number of pools</t>
   </si>
@@ -919,13 +921,25 @@
     <t>Round 4 - Match 83</t>
   </si>
   <si>
-    <t>Round 5 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 6 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 7 - Match 0</t>
+    <t>Round 5 - Match 84</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 86</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 85</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 87</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 88</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 89</t>
+  </si>
+  <si>
+    <t>Round 7 - Match 90</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -4134,6 +4148,798 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="17">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="17">
+        <v>4</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="17">
+        <v>5</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="17">
+        <v>6</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="17">
+        <v>7</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="17">
+        <v>8</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="17">
+        <v>9</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="17">
+        <v>10</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="17">
+        <v>11</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="17">
+        <v>12</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="17">
+        <v>13</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="17">
+        <v>14</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="17">
+        <v>15</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="17">
+        <v>16</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="17">
+        <v>17</v>
+      </c>
+      <c r="B15" s="18" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="17">
+        <v>18</v>
+      </c>
+      <c r="B16" s="18" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="17">
+        <v>19</v>
+      </c>
+      <c r="B17" s="18" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="17">
+        <v>20</v>
+      </c>
+      <c r="B18" s="18" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="17">
+        <v>21</v>
+      </c>
+      <c r="B19" s="18" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="17">
+        <v>22</v>
+      </c>
+      <c r="B20" s="18" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="17">
+        <v>23</v>
+      </c>
+      <c r="B21" s="18" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="17">
+        <v>24</v>
+      </c>
+      <c r="B22" s="18" t="str">
+        <f>data!D27</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="17">
+        <v>25</v>
+      </c>
+      <c r="B23" s="18" t="str">
+        <f>data!D28</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="17">
+        <v>26</v>
+      </c>
+      <c r="B24" s="18" t="str">
+        <f>data!D29</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="17">
+        <v>27</v>
+      </c>
+      <c r="B25" s="18" t="str">
+        <f>data!D30</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="17">
+        <v>28</v>
+      </c>
+      <c r="B26" s="18" t="str">
+        <f>data!D31</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="17">
+        <v>29</v>
+      </c>
+      <c r="B27" s="18" t="str">
+        <f>data!D32</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="17">
+        <v>30</v>
+      </c>
+      <c r="B28" s="18" t="str">
+        <f>data!D33</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="17">
+        <v>31</v>
+      </c>
+      <c r="B29" s="18" t="str">
+        <f>data!D34</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="17">
+        <v>32</v>
+      </c>
+      <c r="B30" s="18" t="str">
+        <f>data!D35</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="17">
+        <v>33</v>
+      </c>
+      <c r="B31" s="18" t="str">
+        <f>data!D36</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="17">
+        <v>34</v>
+      </c>
+      <c r="B32" s="18" t="str">
+        <f>data!D37</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="17">
+        <v>3</v>
+      </c>
+      <c r="B33" s="18" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="17">
+        <v>35</v>
+      </c>
+      <c r="B34" s="18" t="str">
+        <f>data!D38</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="17">
+        <v>36</v>
+      </c>
+      <c r="B35" s="18" t="str">
+        <f>data!D39</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="17">
+        <v>37</v>
+      </c>
+      <c r="B36" s="18" t="str">
+        <f>data!D40</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="17">
+        <v>38</v>
+      </c>
+      <c r="B37" s="18" t="str">
+        <f>data!D41</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="17">
+        <v>39</v>
+      </c>
+      <c r="B38" s="18" t="str">
+        <f>data!D42</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="17">
+        <v>40</v>
+      </c>
+      <c r="B39" s="18" t="str">
+        <f>data!D43</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="17">
+        <v>41</v>
+      </c>
+      <c r="B40" s="18" t="str">
+        <f>data!D44</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="17">
+        <v>42</v>
+      </c>
+      <c r="B41" s="18" t="str">
+        <f>data!D45</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="17">
+        <v>43</v>
+      </c>
+      <c r="B42" s="18" t="str">
+        <f>data!D46</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="17">
+        <v>44</v>
+      </c>
+      <c r="B43" s="18" t="str">
+        <f>data!D47</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="17">
+        <v>45</v>
+      </c>
+      <c r="B44" s="18" t="str">
+        <f>data!D48</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="17">
+        <v>46</v>
+      </c>
+      <c r="B45" s="18" t="str">
+        <f>data!D49</f>
+      </c>
+    </row>
+    <row r="46" ht="270" customHeight="true">
+      <c r="A46" s="17">
+        <v>47</v>
+      </c>
+      <c r="B46" s="18" t="str">
+        <f>data!D50</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="17">
+        <v>48</v>
+      </c>
+      <c r="B1" s="18" t="str">
+        <f>data!D51</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="17">
+        <v>49</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>data!D52</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="17">
+        <v>50</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>data!D53</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="17">
+        <v>51</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>data!D54</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="17">
+        <v>52</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>data!D55</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="17">
+        <v>53</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>data!D56</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="17">
+        <v>54</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>data!D57</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="17">
+        <v>55</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>data!D58</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="17">
+        <v>56</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>data!D59</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="17">
+        <v>57</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>data!D60</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="17">
+        <v>58</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>data!D61</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="17">
+        <v>59</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>data!D62</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="17">
+        <v>60</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f>data!D63</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="17">
+        <v>61</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <f>data!D64</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="17">
+        <v>62</v>
+      </c>
+      <c r="B15" s="18" t="str">
+        <f>data!D65</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="17">
+        <v>63</v>
+      </c>
+      <c r="B16" s="18" t="str">
+        <f>data!D66</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="17">
+        <v>64</v>
+      </c>
+      <c r="B17" s="18" t="str">
+        <f>data!D67</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="17">
+        <v>65</v>
+      </c>
+      <c r="B18" s="18" t="str">
+        <f>data!D68</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="17">
+        <v>1</v>
+      </c>
+      <c r="B19" s="18" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="17">
+        <v>66</v>
+      </c>
+      <c r="B20" s="18" t="str">
+        <f>data!D69</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="17">
+        <v>67</v>
+      </c>
+      <c r="B21" s="18" t="str">
+        <f>data!D70</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="17">
+        <v>68</v>
+      </c>
+      <c r="B22" s="18" t="str">
+        <f>data!D71</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="17">
+        <v>69</v>
+      </c>
+      <c r="B23" s="18" t="str">
+        <f>data!D72</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="17">
+        <v>70</v>
+      </c>
+      <c r="B24" s="18" t="str">
+        <f>data!D73</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="17">
+        <v>71</v>
+      </c>
+      <c r="B25" s="18" t="str">
+        <f>data!D74</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="17">
+        <v>72</v>
+      </c>
+      <c r="B26" s="18" t="str">
+        <f>data!D75</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="17">
+        <v>73</v>
+      </c>
+      <c r="B27" s="18" t="str">
+        <f>data!D76</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="17">
+        <v>74</v>
+      </c>
+      <c r="B28" s="18" t="str">
+        <f>data!D77</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="17">
+        <v>75</v>
+      </c>
+      <c r="B29" s="18" t="str">
+        <f>data!D78</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="17">
+        <v>76</v>
+      </c>
+      <c r="B30" s="18" t="str">
+        <f>data!D79</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="17">
+        <v>77</v>
+      </c>
+      <c r="B31" s="18" t="str">
+        <f>data!D80</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="17">
+        <v>78</v>
+      </c>
+      <c r="B32" s="18" t="str">
+        <f>data!D81</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="17">
+        <v>79</v>
+      </c>
+      <c r="B33" s="18" t="str">
+        <f>data!D82</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="17">
+        <v>80</v>
+      </c>
+      <c r="B34" s="18" t="str">
+        <f>data!D83</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="17">
+        <v>81</v>
+      </c>
+      <c r="B35" s="18" t="str">
+        <f>data!D84</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="17">
+        <v>82</v>
+      </c>
+      <c r="B36" s="18" t="str">
+        <f>data!D85</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="17">
+        <v>83</v>
+      </c>
+      <c r="B37" s="18" t="str">
+        <f>data!D86</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="17">
+        <v>84</v>
+      </c>
+      <c r="B38" s="18" t="str">
+        <f>data!D87</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="17">
+        <v>85</v>
+      </c>
+      <c r="B39" s="18" t="str">
+        <f>data!D88</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="17">
+        <v>86</v>
+      </c>
+      <c r="B40" s="18" t="str">
+        <f>data!D89</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="17">
+        <v>87</v>
+      </c>
+      <c r="B41" s="18" t="str">
+        <f>data!D90</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="17">
+        <v>88</v>
+      </c>
+      <c r="B42" s="18" t="str">
+        <f>data!D91</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="17">
+        <v>89</v>
+      </c>
+      <c r="B43" s="18" t="str">
+        <f>data!D92</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="17">
+        <v>90</v>
+      </c>
+      <c r="B44" s="18" t="str">
+        <f>data!D93</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="17">
+        <v>2</v>
+      </c>
+      <c r="B45" s="18" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -4334,7 +5140,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -4345,7 +5151,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
@@ -4355,7 +5161,7 @@
     </row>
     <row r="15">
       <c r="E15" s="19" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
@@ -4365,7 +5171,7 @@
     </row>
     <row r="16">
       <c r="E16" s="19" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
@@ -4375,7 +5181,7 @@
     </row>
     <row r="17">
       <c r="E17" s="19" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -4385,7 +5191,7 @@
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -4395,7 +5201,7 @@
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -7955,7 +8761,7 @@
       <c r="F358" s="11"/>
       <c r="G358" s="11"/>
       <c r="I358" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J358" s="11"/>
       <c r="K358" s="11"/>
@@ -8030,7 +8836,7 @@
     </row>
     <row r="366">
       <c r="A366" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B366" s="11"/>
       <c r="C366" s="11"/>
@@ -8039,7 +8845,7 @@
       <c r="F366" s="11"/>
       <c r="G366" s="11"/>
       <c r="I366" s="11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
@@ -8114,7 +8920,7 @@
     </row>
     <row r="379">
       <c r="A379" s="11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B379" s="11"/>
       <c r="C379" s="11"/>
@@ -8123,7 +8929,7 @@
       <c r="F379" s="11"/>
       <c r="G379" s="11"/>
       <c r="I379" s="11" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
@@ -8154,7 +8960,7 @@
     </row>
     <row r="381">
       <c r="A381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O370)</f>
+        <f>CONCATENATE("M 85 ",G370)</f>
       </c>
       <c r="B381" s="19"/>
       <c r="C381" s="19"/>
@@ -8162,10 +8968,10 @@
       <c r="E381" s="19"/>
       <c r="F381" s="19"/>
       <c r="G381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O370)</f>
+        <f>CONCATENATE("M 84 ",G362)</f>
       </c>
       <c r="I381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",G383)</f>
+        <f>CONCATENATE("M 87 ",O370)</f>
       </c>
       <c r="J381" s="19"/>
       <c r="K381" s="19"/>
@@ -8173,7 +8979,7 @@
       <c r="M381" s="19"/>
       <c r="N381" s="19"/>
       <c r="O381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",G383)</f>
+        <f>CONCATENATE("M 86 ",O362)</f>
       </c>
     </row>
     <row r="383">
@@ -8198,7 +9004,7 @@
     </row>
     <row r="392">
       <c r="A392" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B392" s="11"/>
       <c r="C392" s="11"/>
@@ -8220,7 +9026,7 @@
     </row>
     <row r="394">
       <c r="A394" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O383)</f>
+        <f>CONCATENATE("M 89 ",O383)</f>
       </c>
       <c r="B394" s="19"/>
       <c r="C394" s="19"/>
@@ -8228,7 +9034,7 @@
       <c r="E394" s="19"/>
       <c r="F394" s="19"/>
       <c r="G394" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O383)</f>
+        <f>CONCATENATE("M 88 ",G383)</f>
       </c>
     </row>
     <row r="396">
@@ -8357,781 +9163,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>4</v>
-      </c>
-      <c r="B2" s="18" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>5</v>
-      </c>
-      <c r="B3" s="18" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>6</v>
-      </c>
-      <c r="B4" s="18" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>7</v>
-      </c>
-      <c r="B5" s="18" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>8</v>
-      </c>
-      <c r="B6" s="18" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>9</v>
-      </c>
-      <c r="B7" s="18" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>10</v>
-      </c>
-      <c r="B8" s="18" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>11</v>
-      </c>
-      <c r="B9" s="18" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>12</v>
-      </c>
-      <c r="B10" s="18" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>13</v>
-      </c>
-      <c r="B11" s="18" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>14</v>
-      </c>
-      <c r="B12" s="18" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="17">
-        <v>15</v>
-      </c>
-      <c r="B13" s="18" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="17">
-        <v>16</v>
-      </c>
-      <c r="B14" s="18" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="17">
-        <v>17</v>
-      </c>
-      <c r="B15" s="18" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="17">
-        <v>18</v>
-      </c>
-      <c r="B16" s="18" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="17">
-        <v>19</v>
-      </c>
-      <c r="B17" s="18" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="17">
-        <v>20</v>
-      </c>
-      <c r="B18" s="18" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="17">
-        <v>21</v>
-      </c>
-      <c r="B19" s="18" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="17">
-        <v>22</v>
-      </c>
-      <c r="B20" s="18" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="17">
-        <v>23</v>
-      </c>
-      <c r="B21" s="18" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="17">
-        <v>24</v>
-      </c>
-      <c r="B22" s="18" t="str">
-        <f>data!D27</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="17">
-        <v>25</v>
-      </c>
-      <c r="B23" s="18" t="str">
-        <f>data!D28</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="17">
-        <v>26</v>
-      </c>
-      <c r="B24" s="18" t="str">
-        <f>data!D29</f>
-      </c>
-    </row>
-    <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="17">
-        <v>27</v>
-      </c>
-      <c r="B25" s="18" t="str">
-        <f>data!D30</f>
-      </c>
-    </row>
-    <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="17">
-        <v>28</v>
-      </c>
-      <c r="B26" s="18" t="str">
-        <f>data!D31</f>
-      </c>
-    </row>
-    <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="17">
-        <v>29</v>
-      </c>
-      <c r="B27" s="18" t="str">
-        <f>data!D32</f>
-      </c>
-    </row>
-    <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="17">
-        <v>30</v>
-      </c>
-      <c r="B28" s="18" t="str">
-        <f>data!D33</f>
-      </c>
-    </row>
-    <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="17">
-        <v>31</v>
-      </c>
-      <c r="B29" s="18" t="str">
-        <f>data!D34</f>
-      </c>
-    </row>
-    <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="17">
-        <v>32</v>
-      </c>
-      <c r="B30" s="18" t="str">
-        <f>data!D35</f>
-      </c>
-    </row>
-    <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="17">
-        <v>33</v>
-      </c>
-      <c r="B31" s="18" t="str">
-        <f>data!D36</f>
-      </c>
-    </row>
-    <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="17">
-        <v>34</v>
-      </c>
-      <c r="B32" s="18" t="str">
-        <f>data!D37</f>
-      </c>
-    </row>
-    <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="17">
-        <v>3</v>
-      </c>
-      <c r="B33" s="18" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="17">
-        <v>35</v>
-      </c>
-      <c r="B34" s="18" t="str">
-        <f>data!D38</f>
-      </c>
-    </row>
-    <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="17">
-        <v>36</v>
-      </c>
-      <c r="B35" s="18" t="str">
-        <f>data!D39</f>
-      </c>
-    </row>
-    <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="17">
-        <v>37</v>
-      </c>
-      <c r="B36" s="18" t="str">
-        <f>data!D40</f>
-      </c>
-    </row>
-    <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="17">
-        <v>38</v>
-      </c>
-      <c r="B37" s="18" t="str">
-        <f>data!D41</f>
-      </c>
-    </row>
-    <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="17">
-        <v>39</v>
-      </c>
-      <c r="B38" s="18" t="str">
-        <f>data!D42</f>
-      </c>
-    </row>
-    <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="17">
-        <v>40</v>
-      </c>
-      <c r="B39" s="18" t="str">
-        <f>data!D43</f>
-      </c>
-    </row>
-    <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="17">
-        <v>41</v>
-      </c>
-      <c r="B40" s="18" t="str">
-        <f>data!D44</f>
-      </c>
-    </row>
-    <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="17">
-        <v>42</v>
-      </c>
-      <c r="B41" s="18" t="str">
-        <f>data!D45</f>
-      </c>
-    </row>
-    <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="17">
-        <v>43</v>
-      </c>
-      <c r="B42" s="18" t="str">
-        <f>data!D46</f>
-      </c>
-    </row>
-    <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="17">
-        <v>44</v>
-      </c>
-      <c r="B43" s="18" t="str">
-        <f>data!D47</f>
-      </c>
-    </row>
-    <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="17">
-        <v>45</v>
-      </c>
-      <c r="B44" s="18" t="str">
-        <f>data!D48</f>
-      </c>
-    </row>
-    <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="17">
-        <v>46</v>
-      </c>
-      <c r="B45" s="18" t="str">
-        <f>data!D49</f>
-      </c>
-    </row>
-    <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="17">
-        <v>47</v>
-      </c>
-      <c r="B46" s="18" t="str">
-        <f>data!D50</f>
-      </c>
-    </row>
-    <row r="47" ht="270" customHeight="true">
-      <c r="A47" s="17">
-        <v>48</v>
-      </c>
-      <c r="B47" s="18" t="str">
-        <f>data!D51</f>
-      </c>
-    </row>
-    <row r="48" ht="270" customHeight="true">
-      <c r="A48" s="17">
-        <v>49</v>
-      </c>
-      <c r="B48" s="18" t="str">
-        <f>data!D52</f>
-      </c>
-    </row>
-    <row r="49" ht="270" customHeight="true">
-      <c r="A49" s="17">
-        <v>50</v>
-      </c>
-      <c r="B49" s="18" t="str">
-        <f>data!D53</f>
-      </c>
-    </row>
-    <row r="50" ht="270" customHeight="true">
-      <c r="A50" s="17">
-        <v>51</v>
-      </c>
-      <c r="B50" s="18" t="str">
-        <f>data!D54</f>
-      </c>
-    </row>
-    <row r="51" ht="270" customHeight="true">
-      <c r="A51" s="17">
-        <v>52</v>
-      </c>
-      <c r="B51" s="18" t="str">
-        <f>data!D55</f>
-      </c>
-    </row>
-    <row r="52" ht="270" customHeight="true">
-      <c r="A52" s="17">
-        <v>53</v>
-      </c>
-      <c r="B52" s="18" t="str">
-        <f>data!D56</f>
-      </c>
-    </row>
-    <row r="53" ht="270" customHeight="true">
-      <c r="A53" s="17">
-        <v>54</v>
-      </c>
-      <c r="B53" s="18" t="str">
-        <f>data!D57</f>
-      </c>
-    </row>
-    <row r="54" ht="270" customHeight="true">
-      <c r="A54" s="17">
-        <v>55</v>
-      </c>
-      <c r="B54" s="18" t="str">
-        <f>data!D58</f>
-      </c>
-    </row>
-    <row r="55" ht="270" customHeight="true">
-      <c r="A55" s="17">
-        <v>56</v>
-      </c>
-      <c r="B55" s="18" t="str">
-        <f>data!D59</f>
-      </c>
-    </row>
-    <row r="56" ht="270" customHeight="true">
-      <c r="A56" s="17">
-        <v>57</v>
-      </c>
-      <c r="B56" s="18" t="str">
-        <f>data!D60</f>
-      </c>
-    </row>
-    <row r="57" ht="270" customHeight="true">
-      <c r="A57" s="17">
-        <v>58</v>
-      </c>
-      <c r="B57" s="18" t="str">
-        <f>data!D61</f>
-      </c>
-    </row>
-    <row r="58" ht="270" customHeight="true">
-      <c r="A58" s="17">
-        <v>59</v>
-      </c>
-      <c r="B58" s="18" t="str">
-        <f>data!D62</f>
-      </c>
-    </row>
-    <row r="59" ht="270" customHeight="true">
-      <c r="A59" s="17">
-        <v>60</v>
-      </c>
-      <c r="B59" s="18" t="str">
-        <f>data!D63</f>
-      </c>
-    </row>
-    <row r="60" ht="270" customHeight="true">
-      <c r="A60" s="17">
-        <v>61</v>
-      </c>
-      <c r="B60" s="18" t="str">
-        <f>data!D64</f>
-      </c>
-    </row>
-    <row r="61" ht="270" customHeight="true">
-      <c r="A61" s="17">
-        <v>62</v>
-      </c>
-      <c r="B61" s="18" t="str">
-        <f>data!D65</f>
-      </c>
-    </row>
-    <row r="62" ht="270" customHeight="true">
-      <c r="A62" s="17">
-        <v>63</v>
-      </c>
-      <c r="B62" s="18" t="str">
-        <f>data!D66</f>
-      </c>
-    </row>
-    <row r="63" ht="270" customHeight="true">
-      <c r="A63" s="17">
-        <v>64</v>
-      </c>
-      <c r="B63" s="18" t="str">
-        <f>data!D67</f>
-      </c>
-    </row>
-    <row r="64" ht="270" customHeight="true">
-      <c r="A64" s="17">
-        <v>65</v>
-      </c>
-      <c r="B64" s="18" t="str">
-        <f>data!D68</f>
-      </c>
-    </row>
-    <row r="65" ht="270" customHeight="true">
-      <c r="A65" s="17">
-        <v>1</v>
-      </c>
-      <c r="B65" s="18" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="66" ht="270" customHeight="true">
-      <c r="A66" s="17">
-        <v>66</v>
-      </c>
-      <c r="B66" s="18" t="str">
-        <f>data!D69</f>
-      </c>
-    </row>
-    <row r="67" ht="270" customHeight="true">
-      <c r="A67" s="17">
-        <v>67</v>
-      </c>
-      <c r="B67" s="18" t="str">
-        <f>data!D70</f>
-      </c>
-    </row>
-    <row r="68" ht="270" customHeight="true">
-      <c r="A68" s="17">
-        <v>68</v>
-      </c>
-      <c r="B68" s="18" t="str">
-        <f>data!D71</f>
-      </c>
-    </row>
-    <row r="69" ht="270" customHeight="true">
-      <c r="A69" s="17">
-        <v>69</v>
-      </c>
-      <c r="B69" s="18" t="str">
-        <f>data!D72</f>
-      </c>
-    </row>
-    <row r="70" ht="270" customHeight="true">
-      <c r="A70" s="17">
-        <v>70</v>
-      </c>
-      <c r="B70" s="18" t="str">
-        <f>data!D73</f>
-      </c>
-    </row>
-    <row r="71" ht="270" customHeight="true">
-      <c r="A71" s="17">
-        <v>71</v>
-      </c>
-      <c r="B71" s="18" t="str">
-        <f>data!D74</f>
-      </c>
-    </row>
-    <row r="72" ht="270" customHeight="true">
-      <c r="A72" s="17">
-        <v>72</v>
-      </c>
-      <c r="B72" s="18" t="str">
-        <f>data!D75</f>
-      </c>
-    </row>
-    <row r="73" ht="270" customHeight="true">
-      <c r="A73" s="17">
-        <v>73</v>
-      </c>
-      <c r="B73" s="18" t="str">
-        <f>data!D76</f>
-      </c>
-    </row>
-    <row r="74" ht="270" customHeight="true">
-      <c r="A74" s="17">
-        <v>74</v>
-      </c>
-      <c r="B74" s="18" t="str">
-        <f>data!D77</f>
-      </c>
-    </row>
-    <row r="75" ht="270" customHeight="true">
-      <c r="A75" s="17">
-        <v>75</v>
-      </c>
-      <c r="B75" s="18" t="str">
-        <f>data!D78</f>
-      </c>
-    </row>
-    <row r="76" ht="270" customHeight="true">
-      <c r="A76" s="17">
-        <v>76</v>
-      </c>
-      <c r="B76" s="18" t="str">
-        <f>data!D79</f>
-      </c>
-    </row>
-    <row r="77" ht="270" customHeight="true">
-      <c r="A77" s="17">
-        <v>77</v>
-      </c>
-      <c r="B77" s="18" t="str">
-        <f>data!D80</f>
-      </c>
-    </row>
-    <row r="78" ht="270" customHeight="true">
-      <c r="A78" s="17">
-        <v>78</v>
-      </c>
-      <c r="B78" s="18" t="str">
-        <f>data!D81</f>
-      </c>
-    </row>
-    <row r="79" ht="270" customHeight="true">
-      <c r="A79" s="17">
-        <v>79</v>
-      </c>
-      <c r="B79" s="18" t="str">
-        <f>data!D82</f>
-      </c>
-    </row>
-    <row r="80" ht="270" customHeight="true">
-      <c r="A80" s="17">
-        <v>80</v>
-      </c>
-      <c r="B80" s="18" t="str">
-        <f>data!D83</f>
-      </c>
-    </row>
-    <row r="81" ht="270" customHeight="true">
-      <c r="A81" s="17">
-        <v>81</v>
-      </c>
-      <c r="B81" s="18" t="str">
-        <f>data!D84</f>
-      </c>
-    </row>
-    <row r="82" ht="270" customHeight="true">
-      <c r="A82" s="17">
-        <v>82</v>
-      </c>
-      <c r="B82" s="18" t="str">
-        <f>data!D85</f>
-      </c>
-    </row>
-    <row r="83" ht="270" customHeight="true">
-      <c r="A83" s="17">
-        <v>83</v>
-      </c>
-      <c r="B83" s="18" t="str">
-        <f>data!D86</f>
-      </c>
-    </row>
-    <row r="84" ht="270" customHeight="true">
-      <c r="A84" s="17">
-        <v>84</v>
-      </c>
-      <c r="B84" s="18" t="str">
-        <f>data!D87</f>
-      </c>
-    </row>
-    <row r="85" ht="270" customHeight="true">
-      <c r="A85" s="17">
-        <v>85</v>
-      </c>
-      <c r="B85" s="18" t="str">
-        <f>data!D88</f>
-      </c>
-    </row>
-    <row r="86" ht="270" customHeight="true">
-      <c r="A86" s="17">
-        <v>86</v>
-      </c>
-      <c r="B86" s="18" t="str">
-        <f>data!D89</f>
-      </c>
-    </row>
-    <row r="87" ht="270" customHeight="true">
-      <c r="A87" s="17">
-        <v>87</v>
-      </c>
-      <c r="B87" s="18" t="str">
-        <f>data!D90</f>
-      </c>
-    </row>
-    <row r="88" ht="270" customHeight="true">
-      <c r="A88" s="17">
-        <v>88</v>
-      </c>
-      <c r="B88" s="18" t="str">
-        <f>data!D91</f>
-      </c>
-    </row>
-    <row r="89" ht="270" customHeight="true">
-      <c r="A89" s="17">
-        <v>89</v>
-      </c>
-      <c r="B89" s="18" t="str">
-        <f>data!D92</f>
-      </c>
-    </row>
-    <row r="90" ht="270" customHeight="true">
-      <c r="A90" s="17">
-        <v>90</v>
-      </c>
-      <c r="B90" s="18" t="str">
-        <f>data!D93</f>
-      </c>
-    </row>
-    <row r="91" ht="270" customHeight="true">
-      <c r="A91" s="17">
-        <v>2</v>
-      </c>
-      <c r="B91" s="18" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="30" manualBreakCount="30">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-    <brk id="27" max="16383" man="true"/>
-    <brk id="30" max="16383" man="true"/>
-    <brk id="33" max="16383" man="true"/>
-    <brk id="36" max="16383" man="true"/>
-    <brk id="39" max="16383" man="true"/>
-    <brk id="42" max="16383" man="true"/>
-    <brk id="45" max="16383" man="true"/>
-    <brk id="48" max="16383" man="true"/>
-    <brk id="51" max="16383" man="true"/>
-    <brk id="54" max="16383" man="true"/>
-    <brk id="57" max="16383" man="true"/>
-    <brk id="60" max="16383" man="true"/>
-    <brk id="63" max="16383" man="true"/>
-    <brk id="66" max="16383" man="true"/>
-    <brk id="69" max="16383" man="true"/>
-    <brk id="72" max="16383" man="true"/>
-    <brk id="75" max="16383" man="true"/>
-    <brk id="78" max="16383" man="true"/>
-    <brk id="81" max="16383" man="true"/>
-    <brk id="84" max="16383" man="true"/>
-    <brk id="87" max="16383" man="true"/>
-    <brk id="90" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -1048,12 +1048,17 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1129,7 +1134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -1176,7 +1181,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -1185,16 +1190,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center"/>
+      <protection hidden="false" locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment/>
+      <protection hidden="false" locked="false"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3000,6 +3016,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3232,6 +3249,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3455,6 +3473,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3687,6 +3706,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3910,6 +3930,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -4142,6 +4163,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -4525,6 +4547,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="15" manualBreakCount="15">
@@ -4917,6 +4940,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="15" manualBreakCount="15">
@@ -5000,7 +5024,7 @@
       <c r="G2" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H2" s="22" t="str">
+      <c r="H2" s="24" t="str">
         <f>C2*I2+J2</f>
       </c>
     </row>
@@ -5104,7 +5128,7 @@
       <c r="G8" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" s="24" t="str">
         <f>E8+(A8*F8)+G8</f>
       </c>
     </row>
@@ -5150,42 +5174,42 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="22" t="str">
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="24" t="str">
         <f>H2</f>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="22" t="str">
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="24" t="str">
         <f>H8</f>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="22" t="str">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="24" t="str">
         <f>H14+H15</f>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="22" t="str">
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="24" t="str">
         <f>H16/A14</f>
       </c>
     </row>
@@ -5195,7 +5219,7 @@
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="23">
+      <c r="H18" s="26">
         <v>0.375</v>
       </c>
     </row>
@@ -5205,7 +5229,7 @@
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="23" t="str">
+      <c r="H19" s="26" t="str">
         <f>H18+H17</f>
       </c>
     </row>
@@ -5229,14 +5253,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5303,22 +5328,22 @@
       <c r="A4" s="19" t="str">
         <f>'data'!$B$38</f>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
         <f>'data'!$B$37</f>
       </c>
       <c r="I4" s="19" t="str">
         <f>'data'!$B$54</f>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
         <f>'data'!$B$53</f>
       </c>
@@ -5327,21 +5352,21 @@
       <c r="F6" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="23"/>
       <c r="N6" t="s">
         <v>212</v>
       </c>
-      <c r="O6" s="15"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
         <v>213</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="23"/>
       <c r="N7" t="s">
         <v>213</v>
       </c>
-      <c r="O7" s="15"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
@@ -5387,22 +5412,22 @@
       <c r="A12" s="19" t="str">
         <f>'data'!$B$41</f>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
         <f>'data'!$B$40</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$57</f>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
         <f>'data'!$B$56</f>
       </c>
@@ -5411,21 +5436,21 @@
       <c r="F14" t="s">
         <v>212</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="23"/>
       <c r="N14" t="s">
         <v>212</v>
       </c>
-      <c r="O14" s="15"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
         <v>213</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="23"/>
       <c r="N15" t="s">
         <v>213</v>
       </c>
-      <c r="O15" s="15"/>
+      <c r="O15" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
@@ -5471,22 +5496,22 @@
       <c r="A20" s="19" t="str">
         <f>'data'!$B$16</f>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
         <f>'data'!$B$43</f>
       </c>
       <c r="I20" s="19" t="str">
         <f>'data'!$B$60</f>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
         <f>'data'!$B$81</f>
       </c>
@@ -5495,21 +5520,21 @@
       <c r="F22" t="s">
         <v>212</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="23"/>
       <c r="N22" t="s">
         <v>212</v>
       </c>
-      <c r="O22" s="15"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
         <v>213</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="23"/>
       <c r="N23" t="s">
         <v>213</v>
       </c>
-      <c r="O23" s="15"/>
+      <c r="O23" s="23"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
@@ -5555,22 +5580,22 @@
       <c r="A28" s="19" t="str">
         <f>'data'!$B$21</f>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
         <f>'data'!$B$20</f>
       </c>
       <c r="I28" s="19" t="str">
         <f>'data'!$B$63</f>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
         <f>'data'!$B$62</f>
       </c>
@@ -5579,21 +5604,21 @@
       <c r="F30" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="15"/>
+      <c r="G30" s="23"/>
       <c r="N30" t="s">
         <v>212</v>
       </c>
-      <c r="O30" s="15"/>
+      <c r="O30" s="23"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
         <v>213</v>
       </c>
-      <c r="G31" s="15"/>
+      <c r="G31" s="23"/>
       <c r="N31" t="s">
         <v>213</v>
       </c>
-      <c r="O31" s="15"/>
+      <c r="O31" s="23"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
@@ -5639,22 +5664,22 @@
       <c r="A36" s="19" t="str">
         <f>'data'!$B$24</f>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
       <c r="G36" s="19" t="str">
         <f>'data'!$B$23</f>
       </c>
       <c r="I36" s="19" t="str">
         <f>'data'!$B$66</f>
       </c>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
       <c r="O36" s="19" t="str">
         <f>'data'!$B$65</f>
       </c>
@@ -5663,21 +5688,21 @@
       <c r="F38" t="s">
         <v>212</v>
       </c>
-      <c r="G38" s="15"/>
+      <c r="G38" s="23"/>
       <c r="N38" t="s">
         <v>212</v>
       </c>
-      <c r="O38" s="15"/>
+      <c r="O38" s="23"/>
     </row>
     <row r="39">
       <c r="F39" t="s">
         <v>213</v>
       </c>
-      <c r="G39" s="15"/>
+      <c r="G39" s="23"/>
       <c r="N39" t="s">
         <v>213</v>
       </c>
-      <c r="O39" s="15"/>
+      <c r="O39" s="23"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
@@ -5723,22 +5748,22 @@
       <c r="A44" s="19" t="str">
         <f>'data'!$B$27</f>
       </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
       <c r="G44" s="19" t="str">
         <f>'data'!$B$26</f>
       </c>
       <c r="I44" s="19" t="str">
         <f>'data'!$B$4</f>
       </c>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
       <c r="O44" s="19" t="str">
         <f>'data'!$B$68</f>
       </c>
@@ -5747,21 +5772,21 @@
       <c r="F46" t="s">
         <v>212</v>
       </c>
-      <c r="G46" s="15"/>
+      <c r="G46" s="23"/>
       <c r="N46" t="s">
         <v>212</v>
       </c>
-      <c r="O46" s="15"/>
+      <c r="O46" s="23"/>
     </row>
     <row r="47">
       <c r="F47" t="s">
         <v>213</v>
       </c>
-      <c r="G47" s="15"/>
+      <c r="G47" s="23"/>
       <c r="N47" t="s">
         <v>213</v>
       </c>
-      <c r="O47" s="15"/>
+      <c r="O47" s="23"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="s">
@@ -5807,22 +5832,22 @@
       <c r="A52" s="19" t="str">
         <f>'data'!$B$32</f>
       </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
         <f>'data'!$B$31</f>
       </c>
       <c r="I52" s="19" t="str">
         <f>'data'!$B$88</f>
       </c>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
       <c r="O52" s="19" t="str">
         <f>'data'!$B$74</f>
       </c>
@@ -5831,21 +5856,21 @@
       <c r="F54" t="s">
         <v>212</v>
       </c>
-      <c r="G54" s="15"/>
+      <c r="G54" s="23"/>
       <c r="N54" t="s">
         <v>212</v>
       </c>
-      <c r="O54" s="15"/>
+      <c r="O54" s="23"/>
     </row>
     <row r="55">
       <c r="F55" t="s">
         <v>213</v>
       </c>
-      <c r="G55" s="15"/>
+      <c r="G55" s="23"/>
       <c r="N55" t="s">
         <v>213</v>
       </c>
-      <c r="O55" s="15"/>
+      <c r="O55" s="23"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="s">
@@ -5891,22 +5916,22 @@
       <c r="A60" s="19" t="str">
         <f>'data'!$B$35</f>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
       <c r="G60" s="19" t="str">
         <f>'data'!$B$5</f>
       </c>
       <c r="I60" s="19" t="str">
         <f>'data'!$B$76</f>
       </c>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+      <c r="N60" s="22"/>
       <c r="O60" s="19" t="str">
         <f>'data'!$B$75</f>
       </c>
@@ -5915,21 +5940,21 @@
       <c r="F62" t="s">
         <v>212</v>
       </c>
-      <c r="G62" s="15"/>
+      <c r="G62" s="23"/>
       <c r="N62" t="s">
         <v>212</v>
       </c>
-      <c r="O62" s="15"/>
+      <c r="O62" s="23"/>
     </row>
     <row r="63">
       <c r="F63" t="s">
         <v>213</v>
       </c>
-      <c r="G63" s="15"/>
+      <c r="G63" s="23"/>
       <c r="N63" t="s">
         <v>213</v>
       </c>
-      <c r="O63" s="15"/>
+      <c r="O63" s="23"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="s">
@@ -5975,22 +6000,22 @@
       <c r="A68" s="19" t="str">
         <f>'data'!$B$6</f>
       </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
       <c r="G68" s="19" t="str">
         <f>'data'!$B$37</f>
       </c>
       <c r="I68" s="19" t="str">
         <f>'data'!$B$79</f>
       </c>
-      <c r="J68" s="19"/>
-      <c r="K68" s="19"/>
-      <c r="L68" s="19"/>
-      <c r="M68" s="19"/>
-      <c r="N68" s="19"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
       <c r="O68" s="19" t="str">
         <f>'data'!$B$78</f>
       </c>
@@ -5999,21 +6024,21 @@
       <c r="F70" t="s">
         <v>212</v>
       </c>
-      <c r="G70" s="15"/>
+      <c r="G70" s="23"/>
       <c r="N70" t="s">
         <v>212</v>
       </c>
-      <c r="O70" s="15"/>
+      <c r="O70" s="23"/>
     </row>
     <row r="71">
       <c r="F71" t="s">
         <v>213</v>
       </c>
-      <c r="G71" s="15"/>
+      <c r="G71" s="23"/>
       <c r="N71" t="s">
         <v>213</v>
       </c>
-      <c r="O71" s="15"/>
+      <c r="O71" s="23"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="s">
@@ -6059,22 +6084,22 @@
       <c r="A76" s="19" t="str">
         <f>'data'!$B$40</f>
       </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
       <c r="G76" s="19" t="str">
         <f>'data'!$B$39</f>
       </c>
       <c r="I76" s="19" t="str">
         <f>'data'!$B$82</f>
       </c>
-      <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
-      <c r="L76" s="19"/>
-      <c r="M76" s="19"/>
-      <c r="N76" s="19"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
       <c r="O76" s="19" t="str">
         <f>'data'!$B$81</f>
       </c>
@@ -6083,21 +6108,21 @@
       <c r="F78" t="s">
         <v>212</v>
       </c>
-      <c r="G78" s="15"/>
+      <c r="G78" s="23"/>
       <c r="N78" t="s">
         <v>212</v>
       </c>
-      <c r="O78" s="15"/>
+      <c r="O78" s="23"/>
     </row>
     <row r="79">
       <c r="F79" t="s">
         <v>213</v>
       </c>
-      <c r="G79" s="15"/>
+      <c r="G79" s="23"/>
       <c r="N79" t="s">
         <v>213</v>
       </c>
-      <c r="O79" s="15"/>
+      <c r="O79" s="23"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="s">
@@ -6143,22 +6168,22 @@
       <c r="A84" s="19" t="str">
         <f>'data'!$B$43</f>
       </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
+      <c r="B84" s="22"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
       <c r="G84" s="19" t="str">
         <f>'data'!$B$42</f>
       </c>
       <c r="I84" s="19" t="str">
         <f>'data'!$B$85</f>
       </c>
-      <c r="J84" s="19"/>
-      <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19"/>
+      <c r="J84" s="22"/>
+      <c r="K84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
       <c r="O84" s="19" t="str">
         <f>'data'!$B$84</f>
       </c>
@@ -6167,21 +6192,21 @@
       <c r="F86" t="s">
         <v>212</v>
       </c>
-      <c r="G86" s="15"/>
+      <c r="G86" s="23"/>
       <c r="N86" t="s">
         <v>212</v>
       </c>
-      <c r="O86" s="15"/>
+      <c r="O86" s="23"/>
     </row>
     <row r="87">
       <c r="F87" t="s">
         <v>213</v>
       </c>
-      <c r="G87" s="15"/>
+      <c r="G87" s="23"/>
       <c r="N87" t="s">
         <v>213</v>
       </c>
-      <c r="O87" s="15"/>
+      <c r="O87" s="23"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="s">
@@ -6227,22 +6252,22 @@
       <c r="A92" s="19" t="str">
         <f>'data'!$B$46</f>
       </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
         <f>'data'!$B$45</f>
       </c>
       <c r="I92" s="19" t="str">
         <f>'data'!$B$88</f>
       </c>
-      <c r="J92" s="19"/>
-      <c r="K92" s="19"/>
-      <c r="L92" s="19"/>
-      <c r="M92" s="19"/>
-      <c r="N92" s="19"/>
+      <c r="J92" s="22"/>
+      <c r="K92" s="22"/>
+      <c r="L92" s="22"/>
+      <c r="M92" s="22"/>
+      <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
         <f>'data'!$B$87</f>
       </c>
@@ -6251,21 +6276,21 @@
       <c r="F94" t="s">
         <v>212</v>
       </c>
-      <c r="G94" s="15"/>
+      <c r="G94" s="23"/>
       <c r="N94" t="s">
         <v>212</v>
       </c>
-      <c r="O94" s="15"/>
+      <c r="O94" s="23"/>
     </row>
     <row r="95">
       <c r="F95" t="s">
         <v>213</v>
       </c>
-      <c r="G95" s="15"/>
+      <c r="G95" s="23"/>
       <c r="N95" t="s">
         <v>213</v>
       </c>
-      <c r="O95" s="15"/>
+      <c r="O95" s="23"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="s">
@@ -6311,22 +6336,22 @@
       <c r="A100" s="19" t="str">
         <f>'data'!$B$49</f>
       </c>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
+      <c r="B100" s="22"/>
+      <c r="C100" s="22"/>
+      <c r="D100" s="22"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
         <f>'data'!$B$48</f>
       </c>
       <c r="I100" s="19" t="str">
         <f>'data'!$B$91</f>
       </c>
-      <c r="J100" s="19"/>
-      <c r="K100" s="19"/>
-      <c r="L100" s="19"/>
-      <c r="M100" s="19"/>
-      <c r="N100" s="19"/>
+      <c r="J100" s="22"/>
+      <c r="K100" s="22"/>
+      <c r="L100" s="22"/>
+      <c r="M100" s="22"/>
+      <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
         <f>'data'!$B$90</f>
       </c>
@@ -6335,21 +6360,21 @@
       <c r="F102" t="s">
         <v>212</v>
       </c>
-      <c r="G102" s="15"/>
+      <c r="G102" s="23"/>
       <c r="N102" t="s">
         <v>212</v>
       </c>
-      <c r="O102" s="15"/>
+      <c r="O102" s="23"/>
     </row>
     <row r="103">
       <c r="F103" t="s">
         <v>213</v>
       </c>
-      <c r="G103" s="15"/>
+      <c r="G103" s="23"/>
       <c r="N103" t="s">
         <v>213</v>
       </c>
-      <c r="O103" s="15"/>
+      <c r="O103" s="23"/>
     </row>
     <row r="106">
       <c r="I106" s="11" t="s">
@@ -6377,11 +6402,11 @@
       <c r="I108" s="19" t="str">
         <f>'data'!$B$5</f>
       </c>
-      <c r="J108" s="19"/>
-      <c r="K108" s="19"/>
-      <c r="L108" s="19"/>
-      <c r="M108" s="19"/>
-      <c r="N108" s="19"/>
+      <c r="J108" s="22"/>
+      <c r="K108" s="22"/>
+      <c r="L108" s="22"/>
+      <c r="M108" s="22"/>
+      <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
         <f>'data'!$B$93</f>
       </c>
@@ -6390,13 +6415,13 @@
       <c r="N110" t="s">
         <v>212</v>
       </c>
-      <c r="O110" s="15"/>
+      <c r="O110" s="23"/>
     </row>
     <row r="111">
       <c r="N111" t="s">
         <v>213</v>
       </c>
-      <c r="O111" s="15"/>
+      <c r="O111" s="23"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="s">
@@ -6442,22 +6467,22 @@
       <c r="A121" s="19" t="str">
         <f>'data'!$B$35</f>
       </c>
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-      <c r="D121" s="19"/>
-      <c r="E121" s="19"/>
-      <c r="F121" s="19"/>
+      <c r="B121" s="22"/>
+      <c r="C121" s="22"/>
+      <c r="D121" s="22"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22"/>
       <c r="G121" s="19" t="str">
         <f>'data'!$B$32</f>
       </c>
       <c r="I121" s="19" t="str">
         <f>'data'!$B$51</f>
       </c>
-      <c r="J121" s="19"/>
-      <c r="K121" s="19"/>
-      <c r="L121" s="19"/>
-      <c r="M121" s="19"/>
-      <c r="N121" s="19"/>
+      <c r="J121" s="22"/>
+      <c r="K121" s="22"/>
+      <c r="L121" s="22"/>
+      <c r="M121" s="22"/>
+      <c r="N121" s="22"/>
       <c r="O121" s="19" t="str">
         <f>'data'!$B$50</f>
       </c>
@@ -6466,21 +6491,21 @@
       <c r="F123" t="s">
         <v>212</v>
       </c>
-      <c r="G123" s="15"/>
+      <c r="G123" s="23"/>
       <c r="N123" t="s">
         <v>212</v>
       </c>
-      <c r="O123" s="15"/>
+      <c r="O123" s="23"/>
     </row>
     <row r="124">
       <c r="F124" t="s">
         <v>213</v>
       </c>
-      <c r="G124" s="15"/>
+      <c r="G124" s="23"/>
       <c r="N124" t="s">
         <v>213</v>
       </c>
-      <c r="O124" s="15"/>
+      <c r="O124" s="23"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="s">
@@ -6526,22 +6551,22 @@
       <c r="A129" s="19" t="str">
         <f>CONCATENATE("M 1 ",G6)</f>
       </c>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-      <c r="D129" s="19"/>
-      <c r="E129" s="19"/>
-      <c r="F129" s="19"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
       <c r="G129" s="19" t="str">
         <f>'data'!$B$36</f>
       </c>
       <c r="I129" s="19" t="str">
         <f>CONCATENATE("M 14 ",O6)</f>
       </c>
-      <c r="J129" s="19"/>
-      <c r="K129" s="19"/>
-      <c r="L129" s="19"/>
-      <c r="M129" s="19"/>
-      <c r="N129" s="19"/>
+      <c r="J129" s="22"/>
+      <c r="K129" s="22"/>
+      <c r="L129" s="22"/>
+      <c r="M129" s="22"/>
+      <c r="N129" s="22"/>
       <c r="O129" s="19" t="str">
         <f>'data'!$B$52</f>
       </c>
@@ -6550,21 +6575,21 @@
       <c r="F131" t="s">
         <v>212</v>
       </c>
-      <c r="G131" s="15"/>
+      <c r="G131" s="23"/>
       <c r="N131" t="s">
         <v>212</v>
       </c>
-      <c r="O131" s="15"/>
+      <c r="O131" s="23"/>
     </row>
     <row r="132">
       <c r="F132" t="s">
         <v>213</v>
       </c>
-      <c r="G132" s="15"/>
+      <c r="G132" s="23"/>
       <c r="N132" t="s">
         <v>213</v>
       </c>
-      <c r="O132" s="15"/>
+      <c r="O132" s="23"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="s">
@@ -6610,22 +6635,22 @@
       <c r="A137" s="19" t="str">
         <f>CONCATENATE("M 2 ",G14)</f>
       </c>
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
-      <c r="D137" s="19"/>
-      <c r="E137" s="19"/>
-      <c r="F137" s="19"/>
+      <c r="B137" s="22"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="22"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
         <f>'data'!$B$39</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 15 ",O14)</f>
       </c>
-      <c r="J137" s="19"/>
-      <c r="K137" s="19"/>
-      <c r="L137" s="19"/>
-      <c r="M137" s="19"/>
-      <c r="N137" s="19"/>
+      <c r="J137" s="22"/>
+      <c r="K137" s="22"/>
+      <c r="L137" s="22"/>
+      <c r="M137" s="22"/>
+      <c r="N137" s="22"/>
       <c r="O137" s="19" t="str">
         <f>'data'!$B$55</f>
       </c>
@@ -6634,21 +6659,21 @@
       <c r="F139" t="s">
         <v>212</v>
       </c>
-      <c r="G139" s="15"/>
+      <c r="G139" s="23"/>
       <c r="N139" t="s">
         <v>212</v>
       </c>
-      <c r="O139" s="15"/>
+      <c r="O139" s="23"/>
     </row>
     <row r="140">
       <c r="F140" t="s">
         <v>213</v>
       </c>
-      <c r="G140" s="15"/>
+      <c r="G140" s="23"/>
       <c r="N140" t="s">
         <v>213</v>
       </c>
-      <c r="O140" s="15"/>
+      <c r="O140" s="23"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="s">
@@ -6694,22 +6719,22 @@
       <c r="A145" s="19" t="str">
         <f>CONCATENATE("M 3 ",G22)</f>
       </c>
-      <c r="B145" s="19"/>
-      <c r="C145" s="19"/>
-      <c r="D145" s="19"/>
-      <c r="E145" s="19"/>
-      <c r="F145" s="19"/>
+      <c r="B145" s="22"/>
+      <c r="C145" s="22"/>
+      <c r="D145" s="22"/>
+      <c r="E145" s="22"/>
+      <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
         <f>'data'!$B$42</f>
       </c>
       <c r="I145" s="19" t="str">
         <f>CONCATENATE("M 16 ",O22)</f>
       </c>
-      <c r="J145" s="19"/>
-      <c r="K145" s="19"/>
-      <c r="L145" s="19"/>
-      <c r="M145" s="19"/>
-      <c r="N145" s="19"/>
+      <c r="J145" s="22"/>
+      <c r="K145" s="22"/>
+      <c r="L145" s="22"/>
+      <c r="M145" s="22"/>
+      <c r="N145" s="22"/>
       <c r="O145" s="19" t="str">
         <f>'data'!$B$58</f>
       </c>
@@ -6718,21 +6743,21 @@
       <c r="F147" t="s">
         <v>212</v>
       </c>
-      <c r="G147" s="15"/>
+      <c r="G147" s="23"/>
       <c r="N147" t="s">
         <v>212</v>
       </c>
-      <c r="O147" s="15"/>
+      <c r="O147" s="23"/>
     </row>
     <row r="148">
       <c r="F148" t="s">
         <v>213</v>
       </c>
-      <c r="G148" s="15"/>
+      <c r="G148" s="23"/>
       <c r="N148" t="s">
         <v>213</v>
       </c>
-      <c r="O148" s="15"/>
+      <c r="O148" s="23"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="s">
@@ -6778,22 +6803,22 @@
       <c r="A153" s="19" t="str">
         <f>'data'!$B$18</f>
       </c>
-      <c r="B153" s="19"/>
-      <c r="C153" s="19"/>
-      <c r="D153" s="19"/>
-      <c r="E153" s="19"/>
-      <c r="F153" s="19"/>
+      <c r="B153" s="22"/>
+      <c r="C153" s="22"/>
+      <c r="D153" s="22"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
         <f>'data'!$B$17</f>
       </c>
       <c r="I153" s="19" t="str">
         <f>CONCATENATE("M 17 ",O30)</f>
       </c>
-      <c r="J153" s="19"/>
-      <c r="K153" s="19"/>
-      <c r="L153" s="19"/>
-      <c r="M153" s="19"/>
-      <c r="N153" s="19"/>
+      <c r="J153" s="22"/>
+      <c r="K153" s="22"/>
+      <c r="L153" s="22"/>
+      <c r="M153" s="22"/>
+      <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
         <f>'data'!$B$61</f>
       </c>
@@ -6802,21 +6827,21 @@
       <c r="F155" t="s">
         <v>212</v>
       </c>
-      <c r="G155" s="15"/>
+      <c r="G155" s="23"/>
       <c r="N155" t="s">
         <v>212</v>
       </c>
-      <c r="O155" s="15"/>
+      <c r="O155" s="23"/>
     </row>
     <row r="156">
       <c r="F156" t="s">
         <v>213</v>
       </c>
-      <c r="G156" s="15"/>
+      <c r="G156" s="23"/>
       <c r="N156" t="s">
         <v>213</v>
       </c>
-      <c r="O156" s="15"/>
+      <c r="O156" s="23"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="s">
@@ -6862,22 +6887,22 @@
       <c r="A161" s="19" t="str">
         <f>CONCATENATE("M 4 ",G30)</f>
       </c>
-      <c r="B161" s="19"/>
-      <c r="C161" s="19"/>
-      <c r="D161" s="19"/>
-      <c r="E161" s="19"/>
-      <c r="F161" s="19"/>
+      <c r="B161" s="22"/>
+      <c r="C161" s="22"/>
+      <c r="D161" s="22"/>
+      <c r="E161" s="22"/>
+      <c r="F161" s="22"/>
       <c r="G161" s="19" t="str">
         <f>'data'!$B$30</f>
       </c>
       <c r="I161" s="19" t="str">
         <f>CONCATENATE("M 18 ",O38)</f>
       </c>
-      <c r="J161" s="19"/>
-      <c r="K161" s="19"/>
-      <c r="L161" s="19"/>
-      <c r="M161" s="19"/>
-      <c r="N161" s="19"/>
+      <c r="J161" s="22"/>
+      <c r="K161" s="22"/>
+      <c r="L161" s="22"/>
+      <c r="M161" s="22"/>
+      <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
         <f>'data'!$B$64</f>
       </c>
@@ -6886,21 +6911,21 @@
       <c r="F163" t="s">
         <v>212</v>
       </c>
-      <c r="G163" s="15"/>
+      <c r="G163" s="23"/>
       <c r="N163" t="s">
         <v>212</v>
       </c>
-      <c r="O163" s="15"/>
+      <c r="O163" s="23"/>
     </row>
     <row r="164">
       <c r="F164" t="s">
         <v>213</v>
       </c>
-      <c r="G164" s="15"/>
+      <c r="G164" s="23"/>
       <c r="N164" t="s">
         <v>213</v>
       </c>
-      <c r="O164" s="15"/>
+      <c r="O164" s="23"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="s">
@@ -6946,22 +6971,22 @@
       <c r="A169" s="19" t="str">
         <f>CONCATENATE("M 5 ",G38)</f>
       </c>
-      <c r="B169" s="19"/>
-      <c r="C169" s="19"/>
-      <c r="D169" s="19"/>
-      <c r="E169" s="19"/>
-      <c r="F169" s="19"/>
+      <c r="B169" s="22"/>
+      <c r="C169" s="22"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="22"/>
+      <c r="F169" s="22"/>
       <c r="G169" s="19" t="str">
         <f>'data'!$B$22</f>
       </c>
       <c r="I169" s="19" t="str">
         <f>CONCATENATE("M 19 ",O46)</f>
       </c>
-      <c r="J169" s="19"/>
-      <c r="K169" s="19"/>
-      <c r="L169" s="19"/>
-      <c r="M169" s="19"/>
-      <c r="N169" s="19"/>
+      <c r="J169" s="22"/>
+      <c r="K169" s="22"/>
+      <c r="L169" s="22"/>
+      <c r="M169" s="22"/>
+      <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
         <f>'data'!$B$67</f>
       </c>
@@ -6970,21 +6995,21 @@
       <c r="F171" t="s">
         <v>212</v>
       </c>
-      <c r="G171" s="15"/>
+      <c r="G171" s="23"/>
       <c r="N171" t="s">
         <v>212</v>
       </c>
-      <c r="O171" s="15"/>
+      <c r="O171" s="23"/>
     </row>
     <row r="172">
       <c r="F172" t="s">
         <v>213</v>
       </c>
-      <c r="G172" s="15"/>
+      <c r="G172" s="23"/>
       <c r="N172" t="s">
         <v>213</v>
       </c>
-      <c r="O172" s="15"/>
+      <c r="O172" s="23"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="s">
@@ -7030,22 +7055,22 @@
       <c r="A177" s="19" t="str">
         <f>CONCATENATE("M 6 ",G46)</f>
       </c>
-      <c r="B177" s="19"/>
-      <c r="C177" s="19"/>
-      <c r="D177" s="19"/>
-      <c r="E177" s="19"/>
-      <c r="F177" s="19"/>
+      <c r="B177" s="22"/>
+      <c r="C177" s="22"/>
+      <c r="D177" s="22"/>
+      <c r="E177" s="22"/>
+      <c r="F177" s="22"/>
       <c r="G177" s="19" t="str">
         <f>'data'!$B$25</f>
       </c>
       <c r="I177" s="19" t="str">
         <f>CONCATENATE("M 20 ",O54)</f>
       </c>
-      <c r="J177" s="19"/>
-      <c r="K177" s="19"/>
-      <c r="L177" s="19"/>
-      <c r="M177" s="19"/>
-      <c r="N177" s="19"/>
+      <c r="J177" s="22"/>
+      <c r="K177" s="22"/>
+      <c r="L177" s="22"/>
+      <c r="M177" s="22"/>
+      <c r="N177" s="22"/>
       <c r="O177" s="19" t="str">
         <f>'data'!$B$69</f>
       </c>
@@ -7054,21 +7079,21 @@
       <c r="F179" t="s">
         <v>212</v>
       </c>
-      <c r="G179" s="15"/>
+      <c r="G179" s="23"/>
       <c r="N179" t="s">
         <v>212</v>
       </c>
-      <c r="O179" s="15"/>
+      <c r="O179" s="23"/>
     </row>
     <row r="180">
       <c r="F180" t="s">
         <v>213</v>
       </c>
-      <c r="G180" s="15"/>
+      <c r="G180" s="23"/>
       <c r="N180" t="s">
         <v>213</v>
       </c>
-      <c r="O180" s="15"/>
+      <c r="O180" s="23"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="s">
@@ -7114,22 +7139,22 @@
       <c r="A185" s="19" t="str">
         <f>'data'!$B$29</f>
       </c>
-      <c r="B185" s="19"/>
-      <c r="C185" s="19"/>
-      <c r="D185" s="19"/>
-      <c r="E185" s="19"/>
-      <c r="F185" s="19"/>
+      <c r="B185" s="22"/>
+      <c r="C185" s="22"/>
+      <c r="D185" s="22"/>
+      <c r="E185" s="22"/>
+      <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
         <f>'data'!$B$28</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>'data'!$B$73</f>
       </c>
-      <c r="J185" s="19"/>
-      <c r="K185" s="19"/>
-      <c r="L185" s="19"/>
-      <c r="M185" s="19"/>
-      <c r="N185" s="19"/>
+      <c r="J185" s="22"/>
+      <c r="K185" s="22"/>
+      <c r="L185" s="22"/>
+      <c r="M185" s="22"/>
+      <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
         <f>'data'!$B$72</f>
       </c>
@@ -7138,21 +7163,21 @@
       <c r="F187" t="s">
         <v>212</v>
       </c>
-      <c r="G187" s="15"/>
+      <c r="G187" s="23"/>
       <c r="N187" t="s">
         <v>212</v>
       </c>
-      <c r="O187" s="15"/>
+      <c r="O187" s="23"/>
     </row>
     <row r="188">
       <c r="F188" t="s">
         <v>213</v>
       </c>
-      <c r="G188" s="15"/>
+      <c r="G188" s="23"/>
       <c r="N188" t="s">
         <v>213</v>
       </c>
-      <c r="O188" s="15"/>
+      <c r="O188" s="23"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="s">
@@ -7198,22 +7223,22 @@
       <c r="A193" s="19" t="str">
         <f>CONCATENATE("M 7 ",G54)</f>
       </c>
-      <c r="B193" s="19"/>
-      <c r="C193" s="19"/>
-      <c r="D193" s="19"/>
-      <c r="E193" s="19"/>
-      <c r="F193" s="19"/>
+      <c r="B193" s="22"/>
+      <c r="C193" s="22"/>
+      <c r="D193" s="22"/>
+      <c r="E193" s="22"/>
+      <c r="F193" s="22"/>
       <c r="G193" s="19" t="str">
         <f>'data'!$B$30</f>
       </c>
       <c r="I193" s="19" t="str">
         <f>CONCATENATE("M 21 ",O62)</f>
       </c>
-      <c r="J193" s="19"/>
-      <c r="K193" s="19"/>
-      <c r="L193" s="19"/>
-      <c r="M193" s="19"/>
-      <c r="N193" s="19"/>
+      <c r="J193" s="22"/>
+      <c r="K193" s="22"/>
+      <c r="L193" s="22"/>
+      <c r="M193" s="22"/>
+      <c r="N193" s="22"/>
       <c r="O193" s="19" t="str">
         <f>'data'!$B$74</f>
       </c>
@@ -7222,21 +7247,21 @@
       <c r="F195" t="s">
         <v>212</v>
       </c>
-      <c r="G195" s="15"/>
+      <c r="G195" s="23"/>
       <c r="N195" t="s">
         <v>212</v>
       </c>
-      <c r="O195" s="15"/>
+      <c r="O195" s="23"/>
     </row>
     <row r="196">
       <c r="F196" t="s">
         <v>213</v>
       </c>
-      <c r="G196" s="15"/>
+      <c r="G196" s="23"/>
       <c r="N196" t="s">
         <v>213</v>
       </c>
-      <c r="O196" s="15"/>
+      <c r="O196" s="23"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="s">
@@ -7282,22 +7307,22 @@
       <c r="A201" s="19" t="str">
         <f>CONCATENATE("M 8 ",G62)</f>
       </c>
-      <c r="B201" s="19"/>
-      <c r="C201" s="19"/>
-      <c r="D201" s="19"/>
-      <c r="E201" s="19"/>
-      <c r="F201" s="19"/>
+      <c r="B201" s="22"/>
+      <c r="C201" s="22"/>
+      <c r="D201" s="22"/>
+      <c r="E201" s="22"/>
+      <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
         <f>'data'!$B$4</f>
       </c>
       <c r="I201" s="19" t="str">
         <f>CONCATENATE("M 22 ",O70)</f>
       </c>
-      <c r="J201" s="19"/>
-      <c r="K201" s="19"/>
-      <c r="L201" s="19"/>
-      <c r="M201" s="19"/>
-      <c r="N201" s="19"/>
+      <c r="J201" s="22"/>
+      <c r="K201" s="22"/>
+      <c r="L201" s="22"/>
+      <c r="M201" s="22"/>
+      <c r="N201" s="22"/>
       <c r="O201" s="19" t="str">
         <f>'data'!$B$77</f>
       </c>
@@ -7306,21 +7331,21 @@
       <c r="F203" t="s">
         <v>212</v>
       </c>
-      <c r="G203" s="15"/>
+      <c r="G203" s="23"/>
       <c r="N203" t="s">
         <v>212</v>
       </c>
-      <c r="O203" s="15"/>
+      <c r="O203" s="23"/>
     </row>
     <row r="204">
       <c r="F204" t="s">
         <v>213</v>
       </c>
-      <c r="G204" s="15"/>
+      <c r="G204" s="23"/>
       <c r="N204" t="s">
         <v>213</v>
       </c>
-      <c r="O204" s="15"/>
+      <c r="O204" s="23"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="s">
@@ -7366,22 +7391,22 @@
       <c r="A209" s="19" t="str">
         <f>CONCATENATE("M 9 ",G70)</f>
       </c>
-      <c r="B209" s="19"/>
-      <c r="C209" s="19"/>
-      <c r="D209" s="19"/>
-      <c r="E209" s="19"/>
-      <c r="F209" s="19"/>
+      <c r="B209" s="22"/>
+      <c r="C209" s="22"/>
+      <c r="D209" s="22"/>
+      <c r="E209" s="22"/>
+      <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
         <f>'data'!$B$36</f>
       </c>
       <c r="I209" s="19" t="str">
         <f>CONCATENATE("M 23 ",O78)</f>
       </c>
-      <c r="J209" s="19"/>
-      <c r="K209" s="19"/>
-      <c r="L209" s="19"/>
-      <c r="M209" s="19"/>
-      <c r="N209" s="19"/>
+      <c r="J209" s="22"/>
+      <c r="K209" s="22"/>
+      <c r="L209" s="22"/>
+      <c r="M209" s="22"/>
+      <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
         <f>'data'!$B$80</f>
       </c>
@@ -7390,21 +7415,21 @@
       <c r="F211" t="s">
         <v>212</v>
       </c>
-      <c r="G211" s="15"/>
+      <c r="G211" s="23"/>
       <c r="N211" t="s">
         <v>212</v>
       </c>
-      <c r="O211" s="15"/>
+      <c r="O211" s="23"/>
     </row>
     <row r="212">
       <c r="F212" t="s">
         <v>213</v>
       </c>
-      <c r="G212" s="15"/>
+      <c r="G212" s="23"/>
       <c r="N212" t="s">
         <v>213</v>
       </c>
-      <c r="O212" s="15"/>
+      <c r="O212" s="23"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="s">
@@ -7450,22 +7475,22 @@
       <c r="A217" s="19" t="str">
         <f>CONCATENATE("M 10 ",G78)</f>
       </c>
-      <c r="B217" s="19"/>
-      <c r="C217" s="19"/>
-      <c r="D217" s="19"/>
-      <c r="E217" s="19"/>
-      <c r="F217" s="19"/>
+      <c r="B217" s="22"/>
+      <c r="C217" s="22"/>
+      <c r="D217" s="22"/>
+      <c r="E217" s="22"/>
+      <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
         <f>'data'!$B$38</f>
       </c>
       <c r="I217" s="19" t="str">
         <f>CONCATENATE("M 24 ",O86)</f>
       </c>
-      <c r="J217" s="19"/>
-      <c r="K217" s="19"/>
-      <c r="L217" s="19"/>
-      <c r="M217" s="19"/>
-      <c r="N217" s="19"/>
+      <c r="J217" s="22"/>
+      <c r="K217" s="22"/>
+      <c r="L217" s="22"/>
+      <c r="M217" s="22"/>
+      <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
         <f>'data'!$B$83</f>
       </c>
@@ -7474,21 +7499,21 @@
       <c r="F219" t="s">
         <v>212</v>
       </c>
-      <c r="G219" s="15"/>
+      <c r="G219" s="23"/>
       <c r="N219" t="s">
         <v>212</v>
       </c>
-      <c r="O219" s="15"/>
+      <c r="O219" s="23"/>
     </row>
     <row r="220">
       <c r="F220" t="s">
         <v>213</v>
       </c>
-      <c r="G220" s="15"/>
+      <c r="G220" s="23"/>
       <c r="N220" t="s">
         <v>213</v>
       </c>
-      <c r="O220" s="15"/>
+      <c r="O220" s="23"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="s">
@@ -7534,22 +7559,22 @@
       <c r="A225" s="19" t="str">
         <f>CONCATENATE("M 11 ",G86)</f>
       </c>
-      <c r="B225" s="19"/>
-      <c r="C225" s="19"/>
-      <c r="D225" s="19"/>
-      <c r="E225" s="19"/>
-      <c r="F225" s="19"/>
+      <c r="B225" s="22"/>
+      <c r="C225" s="22"/>
+      <c r="D225" s="22"/>
+      <c r="E225" s="22"/>
+      <c r="F225" s="22"/>
       <c r="G225" s="19" t="str">
         <f>'data'!$B$41</f>
       </c>
       <c r="I225" s="19" t="str">
         <f>CONCATENATE("M 25 ",O94)</f>
       </c>
-      <c r="J225" s="19"/>
-      <c r="K225" s="19"/>
-      <c r="L225" s="19"/>
-      <c r="M225" s="19"/>
-      <c r="N225" s="19"/>
+      <c r="J225" s="22"/>
+      <c r="K225" s="22"/>
+      <c r="L225" s="22"/>
+      <c r="M225" s="22"/>
+      <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
         <f>'data'!$B$86</f>
       </c>
@@ -7558,21 +7583,21 @@
       <c r="F227" t="s">
         <v>212</v>
       </c>
-      <c r="G227" s="15"/>
+      <c r="G227" s="23"/>
       <c r="N227" t="s">
         <v>212</v>
       </c>
-      <c r="O227" s="15"/>
+      <c r="O227" s="23"/>
     </row>
     <row r="228">
       <c r="F228" t="s">
         <v>213</v>
       </c>
-      <c r="G228" s="15"/>
+      <c r="G228" s="23"/>
       <c r="N228" t="s">
         <v>213</v>
       </c>
-      <c r="O228" s="15"/>
+      <c r="O228" s="23"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="s">
@@ -7618,22 +7643,22 @@
       <c r="A233" s="19" t="str">
         <f>CONCATENATE("M 12 ",G94)</f>
       </c>
-      <c r="B233" s="19"/>
-      <c r="C233" s="19"/>
-      <c r="D233" s="19"/>
-      <c r="E233" s="19"/>
-      <c r="F233" s="19"/>
+      <c r="B233" s="22"/>
+      <c r="C233" s="22"/>
+      <c r="D233" s="22"/>
+      <c r="E233" s="22"/>
+      <c r="F233" s="22"/>
       <c r="G233" s="19" t="str">
         <f>'data'!$B$44</f>
       </c>
       <c r="I233" s="19" t="str">
         <f>CONCATENATE("M 26 ",O102)</f>
       </c>
-      <c r="J233" s="19"/>
-      <c r="K233" s="19"/>
-      <c r="L233" s="19"/>
-      <c r="M233" s="19"/>
-      <c r="N233" s="19"/>
+      <c r="J233" s="22"/>
+      <c r="K233" s="22"/>
+      <c r="L233" s="22"/>
+      <c r="M233" s="22"/>
+      <c r="N233" s="22"/>
       <c r="O233" s="19" t="str">
         <f>'data'!$B$89</f>
       </c>
@@ -7642,21 +7667,21 @@
       <c r="F235" t="s">
         <v>212</v>
       </c>
-      <c r="G235" s="15"/>
+      <c r="G235" s="23"/>
       <c r="N235" t="s">
         <v>212</v>
       </c>
-      <c r="O235" s="15"/>
+      <c r="O235" s="23"/>
     </row>
     <row r="236">
       <c r="F236" t="s">
         <v>213</v>
       </c>
-      <c r="G236" s="15"/>
+      <c r="G236" s="23"/>
       <c r="N236" t="s">
         <v>213</v>
       </c>
-      <c r="O236" s="15"/>
+      <c r="O236" s="23"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="s">
@@ -7702,22 +7727,22 @@
       <c r="A241" s="19" t="str">
         <f>CONCATENATE("M 13 ",G102)</f>
       </c>
-      <c r="B241" s="19"/>
-      <c r="C241" s="19"/>
-      <c r="D241" s="19"/>
-      <c r="E241" s="19"/>
-      <c r="F241" s="19"/>
+      <c r="B241" s="22"/>
+      <c r="C241" s="22"/>
+      <c r="D241" s="22"/>
+      <c r="E241" s="22"/>
+      <c r="F241" s="22"/>
       <c r="G241" s="19" t="str">
         <f>'data'!$B$47</f>
       </c>
       <c r="I241" s="19" t="str">
         <f>CONCATENATE("M 27 ",O110)</f>
       </c>
-      <c r="J241" s="19"/>
-      <c r="K241" s="19"/>
-      <c r="L241" s="19"/>
-      <c r="M241" s="19"/>
-      <c r="N241" s="19"/>
+      <c r="J241" s="22"/>
+      <c r="K241" s="22"/>
+      <c r="L241" s="22"/>
+      <c r="M241" s="22"/>
+      <c r="N241" s="22"/>
       <c r="O241" s="19" t="str">
         <f>'data'!$B$92</f>
       </c>
@@ -7726,21 +7751,21 @@
       <c r="F243" t="s">
         <v>212</v>
       </c>
-      <c r="G243" s="15"/>
+      <c r="G243" s="23"/>
       <c r="N243" t="s">
         <v>212</v>
       </c>
-      <c r="O243" s="15"/>
+      <c r="O243" s="23"/>
     </row>
     <row r="244">
       <c r="F244" t="s">
         <v>213</v>
       </c>
-      <c r="G244" s="15"/>
+      <c r="G244" s="23"/>
       <c r="N244" t="s">
         <v>213</v>
       </c>
-      <c r="O244" s="15"/>
+      <c r="O244" s="23"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="s">
@@ -7786,22 +7811,22 @@
       <c r="A254" s="19" t="str">
         <f>CONCATENATE("M 29 ",G131)</f>
       </c>
-      <c r="B254" s="19"/>
-      <c r="C254" s="19"/>
-      <c r="D254" s="19"/>
-      <c r="E254" s="19"/>
-      <c r="F254" s="19"/>
+      <c r="B254" s="22"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="22"/>
+      <c r="F254" s="22"/>
       <c r="G254" s="19" t="str">
         <f>CONCATENATE("M 28 ",G123)</f>
       </c>
       <c r="I254" s="19" t="str">
         <f>CONCATENATE("M 45 ",O131)</f>
       </c>
-      <c r="J254" s="19"/>
-      <c r="K254" s="19"/>
-      <c r="L254" s="19"/>
-      <c r="M254" s="19"/>
-      <c r="N254" s="19"/>
+      <c r="J254" s="22"/>
+      <c r="K254" s="22"/>
+      <c r="L254" s="22"/>
+      <c r="M254" s="22"/>
+      <c r="N254" s="22"/>
       <c r="O254" s="19" t="str">
         <f>CONCATENATE("M 44 ",O123)</f>
       </c>
@@ -7810,21 +7835,21 @@
       <c r="F256" t="s">
         <v>212</v>
       </c>
-      <c r="G256" s="15"/>
+      <c r="G256" s="23"/>
       <c r="N256" t="s">
         <v>212</v>
       </c>
-      <c r="O256" s="15"/>
+      <c r="O256" s="23"/>
     </row>
     <row r="257">
       <c r="F257" t="s">
         <v>213</v>
       </c>
-      <c r="G257" s="15"/>
+      <c r="G257" s="23"/>
       <c r="N257" t="s">
         <v>213</v>
       </c>
-      <c r="O257" s="15"/>
+      <c r="O257" s="23"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="s">
@@ -7870,22 +7895,22 @@
       <c r="A262" s="19" t="str">
         <f>CONCATENATE("M 31 ",G147)</f>
       </c>
-      <c r="B262" s="19"/>
-      <c r="C262" s="19"/>
-      <c r="D262" s="19"/>
-      <c r="E262" s="19"/>
-      <c r="F262" s="19"/>
+      <c r="B262" s="22"/>
+      <c r="C262" s="22"/>
+      <c r="D262" s="22"/>
+      <c r="E262" s="22"/>
+      <c r="F262" s="22"/>
       <c r="G262" s="19" t="str">
         <f>CONCATENATE("M 30 ",G139)</f>
       </c>
       <c r="I262" s="19" t="str">
         <f>CONCATENATE("M 47 ",O147)</f>
       </c>
-      <c r="J262" s="19"/>
-      <c r="K262" s="19"/>
-      <c r="L262" s="19"/>
-      <c r="M262" s="19"/>
-      <c r="N262" s="19"/>
+      <c r="J262" s="22"/>
+      <c r="K262" s="22"/>
+      <c r="L262" s="22"/>
+      <c r="M262" s="22"/>
+      <c r="N262" s="22"/>
       <c r="O262" s="19" t="str">
         <f>CONCATENATE("M 46 ",O139)</f>
       </c>
@@ -7894,21 +7919,21 @@
       <c r="F264" t="s">
         <v>212</v>
       </c>
-      <c r="G264" s="15"/>
+      <c r="G264" s="23"/>
       <c r="N264" t="s">
         <v>212</v>
       </c>
-      <c r="O264" s="15"/>
+      <c r="O264" s="23"/>
     </row>
     <row r="265">
       <c r="F265" t="s">
         <v>213</v>
       </c>
-      <c r="G265" s="15"/>
+      <c r="G265" s="23"/>
       <c r="N265" t="s">
         <v>213</v>
       </c>
-      <c r="O265" s="15"/>
+      <c r="O265" s="23"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="s">
@@ -7954,22 +7979,22 @@
       <c r="A270" s="19" t="str">
         <f>CONCATENATE("M 33 ",G163)</f>
       </c>
-      <c r="B270" s="19"/>
-      <c r="C270" s="19"/>
-      <c r="D270" s="19"/>
-      <c r="E270" s="19"/>
-      <c r="F270" s="19"/>
+      <c r="B270" s="22"/>
+      <c r="C270" s="22"/>
+      <c r="D270" s="22"/>
+      <c r="E270" s="22"/>
+      <c r="F270" s="22"/>
       <c r="G270" s="19" t="str">
         <f>CONCATENATE("M 32 ",G155)</f>
       </c>
       <c r="I270" s="19" t="str">
         <f>CONCATENATE("M 49 ",O163)</f>
       </c>
-      <c r="J270" s="19"/>
-      <c r="K270" s="19"/>
-      <c r="L270" s="19"/>
-      <c r="M270" s="19"/>
-      <c r="N270" s="19"/>
+      <c r="J270" s="22"/>
+      <c r="K270" s="22"/>
+      <c r="L270" s="22"/>
+      <c r="M270" s="22"/>
+      <c r="N270" s="22"/>
       <c r="O270" s="19" t="str">
         <f>CONCATENATE("M 48 ",O155)</f>
       </c>
@@ -7978,21 +8003,21 @@
       <c r="F272" t="s">
         <v>212</v>
       </c>
-      <c r="G272" s="15"/>
+      <c r="G272" s="23"/>
       <c r="N272" t="s">
         <v>212</v>
       </c>
-      <c r="O272" s="15"/>
+      <c r="O272" s="23"/>
     </row>
     <row r="273">
       <c r="F273" t="s">
         <v>213</v>
       </c>
-      <c r="G273" s="15"/>
+      <c r="G273" s="23"/>
       <c r="N273" t="s">
         <v>213</v>
       </c>
-      <c r="O273" s="15"/>
+      <c r="O273" s="23"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="s">
@@ -8038,22 +8063,22 @@
       <c r="A278" s="19" t="str">
         <f>CONCATENATE("M 35 ",G179)</f>
       </c>
-      <c r="B278" s="19"/>
-      <c r="C278" s="19"/>
-      <c r="D278" s="19"/>
-      <c r="E278" s="19"/>
-      <c r="F278" s="19"/>
+      <c r="B278" s="22"/>
+      <c r="C278" s="22"/>
+      <c r="D278" s="22"/>
+      <c r="E278" s="22"/>
+      <c r="F278" s="22"/>
       <c r="G278" s="19" t="str">
         <f>CONCATENATE("M 34 ",G171)</f>
       </c>
       <c r="I278" s="19" t="str">
         <f>CONCATENATE("M 51 ",O179)</f>
       </c>
-      <c r="J278" s="19"/>
-      <c r="K278" s="19"/>
-      <c r="L278" s="19"/>
-      <c r="M278" s="19"/>
-      <c r="N278" s="19"/>
+      <c r="J278" s="22"/>
+      <c r="K278" s="22"/>
+      <c r="L278" s="22"/>
+      <c r="M278" s="22"/>
+      <c r="N278" s="22"/>
       <c r="O278" s="19" t="str">
         <f>CONCATENATE("M 50 ",O171)</f>
       </c>
@@ -8062,21 +8087,21 @@
       <c r="F280" t="s">
         <v>212</v>
       </c>
-      <c r="G280" s="15"/>
+      <c r="G280" s="23"/>
       <c r="N280" t="s">
         <v>212</v>
       </c>
-      <c r="O280" s="15"/>
+      <c r="O280" s="23"/>
     </row>
     <row r="281">
       <c r="F281" t="s">
         <v>213</v>
       </c>
-      <c r="G281" s="15"/>
+      <c r="G281" s="23"/>
       <c r="N281" t="s">
         <v>213</v>
       </c>
-      <c r="O281" s="15"/>
+      <c r="O281" s="23"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="s">
@@ -8122,22 +8147,22 @@
       <c r="A286" s="19" t="str">
         <f>CONCATENATE("M 37 ",G195)</f>
       </c>
-      <c r="B286" s="19"/>
-      <c r="C286" s="19"/>
-      <c r="D286" s="19"/>
-      <c r="E286" s="19"/>
-      <c r="F286" s="19"/>
+      <c r="B286" s="22"/>
+      <c r="C286" s="22"/>
+      <c r="D286" s="22"/>
+      <c r="E286" s="22"/>
+      <c r="F286" s="22"/>
       <c r="G286" s="19" t="str">
         <f>CONCATENATE("M 36 ",G187)</f>
       </c>
       <c r="I286" s="19" t="str">
         <f>CONCATENATE("M 53 ",O195)</f>
       </c>
-      <c r="J286" s="19"/>
-      <c r="K286" s="19"/>
-      <c r="L286" s="19"/>
-      <c r="M286" s="19"/>
-      <c r="N286" s="19"/>
+      <c r="J286" s="22"/>
+      <c r="K286" s="22"/>
+      <c r="L286" s="22"/>
+      <c r="M286" s="22"/>
+      <c r="N286" s="22"/>
       <c r="O286" s="19" t="str">
         <f>CONCATENATE("M 52 ",O187)</f>
       </c>
@@ -8146,21 +8171,21 @@
       <c r="F288" t="s">
         <v>212</v>
       </c>
-      <c r="G288" s="15"/>
+      <c r="G288" s="23"/>
       <c r="N288" t="s">
         <v>212</v>
       </c>
-      <c r="O288" s="15"/>
+      <c r="O288" s="23"/>
     </row>
     <row r="289">
       <c r="F289" t="s">
         <v>213</v>
       </c>
-      <c r="G289" s="15"/>
+      <c r="G289" s="23"/>
       <c r="N289" t="s">
         <v>213</v>
       </c>
-      <c r="O289" s="15"/>
+      <c r="O289" s="23"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="s">
@@ -8206,22 +8231,22 @@
       <c r="A294" s="19" t="str">
         <f>CONCATENATE("M 39 ",G211)</f>
       </c>
-      <c r="B294" s="19"/>
-      <c r="C294" s="19"/>
-      <c r="D294" s="19"/>
-      <c r="E294" s="19"/>
-      <c r="F294" s="19"/>
+      <c r="B294" s="22"/>
+      <c r="C294" s="22"/>
+      <c r="D294" s="22"/>
+      <c r="E294" s="22"/>
+      <c r="F294" s="22"/>
       <c r="G294" s="19" t="str">
         <f>CONCATENATE("M 38 ",G203)</f>
       </c>
       <c r="I294" s="19" t="str">
         <f>CONCATENATE("M 55 ",O211)</f>
       </c>
-      <c r="J294" s="19"/>
-      <c r="K294" s="19"/>
-      <c r="L294" s="19"/>
-      <c r="M294" s="19"/>
-      <c r="N294" s="19"/>
+      <c r="J294" s="22"/>
+      <c r="K294" s="22"/>
+      <c r="L294" s="22"/>
+      <c r="M294" s="22"/>
+      <c r="N294" s="22"/>
       <c r="O294" s="19" t="str">
         <f>CONCATENATE("M 54 ",O203)</f>
       </c>
@@ -8230,21 +8255,21 @@
       <c r="F296" t="s">
         <v>212</v>
       </c>
-      <c r="G296" s="15"/>
+      <c r="G296" s="23"/>
       <c r="N296" t="s">
         <v>212</v>
       </c>
-      <c r="O296" s="15"/>
+      <c r="O296" s="23"/>
     </row>
     <row r="297">
       <c r="F297" t="s">
         <v>213</v>
       </c>
-      <c r="G297" s="15"/>
+      <c r="G297" s="23"/>
       <c r="N297" t="s">
         <v>213</v>
       </c>
-      <c r="O297" s="15"/>
+      <c r="O297" s="23"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="s">
@@ -8290,22 +8315,22 @@
       <c r="A302" s="19" t="str">
         <f>CONCATENATE("M 41 ",G227)</f>
       </c>
-      <c r="B302" s="19"/>
-      <c r="C302" s="19"/>
-      <c r="D302" s="19"/>
-      <c r="E302" s="19"/>
-      <c r="F302" s="19"/>
+      <c r="B302" s="22"/>
+      <c r="C302" s="22"/>
+      <c r="D302" s="22"/>
+      <c r="E302" s="22"/>
+      <c r="F302" s="22"/>
       <c r="G302" s="19" t="str">
         <f>CONCATENATE("M 40 ",G219)</f>
       </c>
       <c r="I302" s="19" t="str">
         <f>CONCATENATE("M 57 ",O227)</f>
       </c>
-      <c r="J302" s="19"/>
-      <c r="K302" s="19"/>
-      <c r="L302" s="19"/>
-      <c r="M302" s="19"/>
-      <c r="N302" s="19"/>
+      <c r="J302" s="22"/>
+      <c r="K302" s="22"/>
+      <c r="L302" s="22"/>
+      <c r="M302" s="22"/>
+      <c r="N302" s="22"/>
       <c r="O302" s="19" t="str">
         <f>CONCATENATE("M 56 ",O219)</f>
       </c>
@@ -8314,21 +8339,21 @@
       <c r="F304" t="s">
         <v>212</v>
       </c>
-      <c r="G304" s="15"/>
+      <c r="G304" s="23"/>
       <c r="N304" t="s">
         <v>212</v>
       </c>
-      <c r="O304" s="15"/>
+      <c r="O304" s="23"/>
     </row>
     <row r="305">
       <c r="F305" t="s">
         <v>213</v>
       </c>
-      <c r="G305" s="15"/>
+      <c r="G305" s="23"/>
       <c r="N305" t="s">
         <v>213</v>
       </c>
-      <c r="O305" s="15"/>
+      <c r="O305" s="23"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="s">
@@ -8374,22 +8399,22 @@
       <c r="A310" s="19" t="str">
         <f>CONCATENATE("M 43 ",G243)</f>
       </c>
-      <c r="B310" s="19"/>
-      <c r="C310" s="19"/>
-      <c r="D310" s="19"/>
-      <c r="E310" s="19"/>
-      <c r="F310" s="19"/>
+      <c r="B310" s="22"/>
+      <c r="C310" s="22"/>
+      <c r="D310" s="22"/>
+      <c r="E310" s="22"/>
+      <c r="F310" s="22"/>
       <c r="G310" s="19" t="str">
         <f>CONCATENATE("M 42 ",G235)</f>
       </c>
       <c r="I310" s="19" t="str">
         <f>CONCATENATE("M 59 ",O243)</f>
       </c>
-      <c r="J310" s="19"/>
-      <c r="K310" s="19"/>
-      <c r="L310" s="19"/>
-      <c r="M310" s="19"/>
-      <c r="N310" s="19"/>
+      <c r="J310" s="22"/>
+      <c r="K310" s="22"/>
+      <c r="L310" s="22"/>
+      <c r="M310" s="22"/>
+      <c r="N310" s="22"/>
       <c r="O310" s="19" t="str">
         <f>CONCATENATE("M 58 ",O235)</f>
       </c>
@@ -8398,21 +8423,21 @@
       <c r="F312" t="s">
         <v>212</v>
       </c>
-      <c r="G312" s="15"/>
+      <c r="G312" s="23"/>
       <c r="N312" t="s">
         <v>212</v>
       </c>
-      <c r="O312" s="15"/>
+      <c r="O312" s="23"/>
     </row>
     <row r="313">
       <c r="F313" t="s">
         <v>213</v>
       </c>
-      <c r="G313" s="15"/>
+      <c r="G313" s="23"/>
       <c r="N313" t="s">
         <v>213</v>
       </c>
-      <c r="O313" s="15"/>
+      <c r="O313" s="23"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="s">
@@ -8458,22 +8483,22 @@
       <c r="A323" s="19" t="str">
         <f>CONCATENATE("M 61 ",G264)</f>
       </c>
-      <c r="B323" s="19"/>
-      <c r="C323" s="19"/>
-      <c r="D323" s="19"/>
-      <c r="E323" s="19"/>
-      <c r="F323" s="19"/>
+      <c r="B323" s="22"/>
+      <c r="C323" s="22"/>
+      <c r="D323" s="22"/>
+      <c r="E323" s="22"/>
+      <c r="F323" s="22"/>
       <c r="G323" s="19" t="str">
         <f>CONCATENATE("M 60 ",G256)</f>
       </c>
       <c r="I323" s="19" t="str">
         <f>CONCATENATE("M 69 ",O264)</f>
       </c>
-      <c r="J323" s="19"/>
-      <c r="K323" s="19"/>
-      <c r="L323" s="19"/>
-      <c r="M323" s="19"/>
-      <c r="N323" s="19"/>
+      <c r="J323" s="22"/>
+      <c r="K323" s="22"/>
+      <c r="L323" s="22"/>
+      <c r="M323" s="22"/>
+      <c r="N323" s="22"/>
       <c r="O323" s="19" t="str">
         <f>CONCATENATE("M 68 ",O256)</f>
       </c>
@@ -8482,21 +8507,21 @@
       <c r="F325" t="s">
         <v>212</v>
       </c>
-      <c r="G325" s="15"/>
+      <c r="G325" s="23"/>
       <c r="N325" t="s">
         <v>212</v>
       </c>
-      <c r="O325" s="15"/>
+      <c r="O325" s="23"/>
     </row>
     <row r="326">
       <c r="F326" t="s">
         <v>213</v>
       </c>
-      <c r="G326" s="15"/>
+      <c r="G326" s="23"/>
       <c r="N326" t="s">
         <v>213</v>
       </c>
-      <c r="O326" s="15"/>
+      <c r="O326" s="23"/>
     </row>
     <row r="329">
       <c r="A329" s="11" t="s">
@@ -8542,22 +8567,22 @@
       <c r="A331" s="19" t="str">
         <f>CONCATENATE("M 63 ",G280)</f>
       </c>
-      <c r="B331" s="19"/>
-      <c r="C331" s="19"/>
-      <c r="D331" s="19"/>
-      <c r="E331" s="19"/>
-      <c r="F331" s="19"/>
+      <c r="B331" s="22"/>
+      <c r="C331" s="22"/>
+      <c r="D331" s="22"/>
+      <c r="E331" s="22"/>
+      <c r="F331" s="22"/>
       <c r="G331" s="19" t="str">
         <f>CONCATENATE("M 62 ",G272)</f>
       </c>
       <c r="I331" s="19" t="str">
         <f>CONCATENATE("M 71 ",O280)</f>
       </c>
-      <c r="J331" s="19"/>
-      <c r="K331" s="19"/>
-      <c r="L331" s="19"/>
-      <c r="M331" s="19"/>
-      <c r="N331" s="19"/>
+      <c r="J331" s="22"/>
+      <c r="K331" s="22"/>
+      <c r="L331" s="22"/>
+      <c r="M331" s="22"/>
+      <c r="N331" s="22"/>
       <c r="O331" s="19" t="str">
         <f>CONCATENATE("M 70 ",O272)</f>
       </c>
@@ -8566,21 +8591,21 @@
       <c r="F333" t="s">
         <v>212</v>
       </c>
-      <c r="G333" s="15"/>
+      <c r="G333" s="23"/>
       <c r="N333" t="s">
         <v>212</v>
       </c>
-      <c r="O333" s="15"/>
+      <c r="O333" s="23"/>
     </row>
     <row r="334">
       <c r="F334" t="s">
         <v>213</v>
       </c>
-      <c r="G334" s="15"/>
+      <c r="G334" s="23"/>
       <c r="N334" t="s">
         <v>213</v>
       </c>
-      <c r="O334" s="15"/>
+      <c r="O334" s="23"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="s">
@@ -8626,22 +8651,22 @@
       <c r="A339" s="19" t="str">
         <f>CONCATENATE("M 65 ",G296)</f>
       </c>
-      <c r="B339" s="19"/>
-      <c r="C339" s="19"/>
-      <c r="D339" s="19"/>
-      <c r="E339" s="19"/>
-      <c r="F339" s="19"/>
+      <c r="B339" s="22"/>
+      <c r="C339" s="22"/>
+      <c r="D339" s="22"/>
+      <c r="E339" s="22"/>
+      <c r="F339" s="22"/>
       <c r="G339" s="19" t="str">
         <f>CONCATENATE("M 64 ",G288)</f>
       </c>
       <c r="I339" s="19" t="str">
         <f>CONCATENATE("M 73 ",O296)</f>
       </c>
-      <c r="J339" s="19"/>
-      <c r="K339" s="19"/>
-      <c r="L339" s="19"/>
-      <c r="M339" s="19"/>
-      <c r="N339" s="19"/>
+      <c r="J339" s="22"/>
+      <c r="K339" s="22"/>
+      <c r="L339" s="22"/>
+      <c r="M339" s="22"/>
+      <c r="N339" s="22"/>
       <c r="O339" s="19" t="str">
         <f>CONCATENATE("M 72 ",O288)</f>
       </c>
@@ -8650,21 +8675,21 @@
       <c r="F341" t="s">
         <v>212</v>
       </c>
-      <c r="G341" s="15"/>
+      <c r="G341" s="23"/>
       <c r="N341" t="s">
         <v>212</v>
       </c>
-      <c r="O341" s="15"/>
+      <c r="O341" s="23"/>
     </row>
     <row r="342">
       <c r="F342" t="s">
         <v>213</v>
       </c>
-      <c r="G342" s="15"/>
+      <c r="G342" s="23"/>
       <c r="N342" t="s">
         <v>213</v>
       </c>
-      <c r="O342" s="15"/>
+      <c r="O342" s="23"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="s">
@@ -8710,22 +8735,22 @@
       <c r="A347" s="19" t="str">
         <f>CONCATENATE("M 67 ",G312)</f>
       </c>
-      <c r="B347" s="19"/>
-      <c r="C347" s="19"/>
-      <c r="D347" s="19"/>
-      <c r="E347" s="19"/>
-      <c r="F347" s="19"/>
+      <c r="B347" s="22"/>
+      <c r="C347" s="22"/>
+      <c r="D347" s="22"/>
+      <c r="E347" s="22"/>
+      <c r="F347" s="22"/>
       <c r="G347" s="19" t="str">
         <f>CONCATENATE("M 66 ",G304)</f>
       </c>
       <c r="I347" s="19" t="str">
         <f>CONCATENATE("M 75 ",O312)</f>
       </c>
-      <c r="J347" s="19"/>
-      <c r="K347" s="19"/>
-      <c r="L347" s="19"/>
-      <c r="M347" s="19"/>
-      <c r="N347" s="19"/>
+      <c r="J347" s="22"/>
+      <c r="K347" s="22"/>
+      <c r="L347" s="22"/>
+      <c r="M347" s="22"/>
+      <c r="N347" s="22"/>
       <c r="O347" s="19" t="str">
         <f>CONCATENATE("M 74 ",O304)</f>
       </c>
@@ -8734,21 +8759,21 @@
       <c r="F349" t="s">
         <v>212</v>
       </c>
-      <c r="G349" s="15"/>
+      <c r="G349" s="23"/>
       <c r="N349" t="s">
         <v>212</v>
       </c>
-      <c r="O349" s="15"/>
+      <c r="O349" s="23"/>
     </row>
     <row r="350">
       <c r="F350" t="s">
         <v>213</v>
       </c>
-      <c r="G350" s="15"/>
+      <c r="G350" s="23"/>
       <c r="N350" t="s">
         <v>213</v>
       </c>
-      <c r="O350" s="15"/>
+      <c r="O350" s="23"/>
     </row>
     <row r="358">
       <c r="A358" s="11" t="s">
@@ -8794,22 +8819,22 @@
       <c r="A360" s="19" t="str">
         <f>CONCATENATE("M 77 ",G333)</f>
       </c>
-      <c r="B360" s="19"/>
-      <c r="C360" s="19"/>
-      <c r="D360" s="19"/>
-      <c r="E360" s="19"/>
-      <c r="F360" s="19"/>
+      <c r="B360" s="22"/>
+      <c r="C360" s="22"/>
+      <c r="D360" s="22"/>
+      <c r="E360" s="22"/>
+      <c r="F360" s="22"/>
       <c r="G360" s="19" t="str">
         <f>CONCATENATE("M 76 ",G325)</f>
       </c>
       <c r="I360" s="19" t="str">
         <f>CONCATENATE("M 81 ",O333)</f>
       </c>
-      <c r="J360" s="19"/>
-      <c r="K360" s="19"/>
-      <c r="L360" s="19"/>
-      <c r="M360" s="19"/>
-      <c r="N360" s="19"/>
+      <c r="J360" s="22"/>
+      <c r="K360" s="22"/>
+      <c r="L360" s="22"/>
+      <c r="M360" s="22"/>
+      <c r="N360" s="22"/>
       <c r="O360" s="19" t="str">
         <f>CONCATENATE("M 80 ",O325)</f>
       </c>
@@ -8818,21 +8843,21 @@
       <c r="F362" t="s">
         <v>212</v>
       </c>
-      <c r="G362" s="15"/>
+      <c r="G362" s="23"/>
       <c r="N362" t="s">
         <v>212</v>
       </c>
-      <c r="O362" s="15"/>
+      <c r="O362" s="23"/>
     </row>
     <row r="363">
       <c r="F363" t="s">
         <v>213</v>
       </c>
-      <c r="G363" s="15"/>
+      <c r="G363" s="23"/>
       <c r="N363" t="s">
         <v>213</v>
       </c>
-      <c r="O363" s="15"/>
+      <c r="O363" s="23"/>
     </row>
     <row r="366">
       <c r="A366" s="11" t="s">
@@ -8878,22 +8903,22 @@
       <c r="A368" s="19" t="str">
         <f>CONCATENATE("M 79 ",G349)</f>
       </c>
-      <c r="B368" s="19"/>
-      <c r="C368" s="19"/>
-      <c r="D368" s="19"/>
-      <c r="E368" s="19"/>
-      <c r="F368" s="19"/>
+      <c r="B368" s="22"/>
+      <c r="C368" s="22"/>
+      <c r="D368" s="22"/>
+      <c r="E368" s="22"/>
+      <c r="F368" s="22"/>
       <c r="G368" s="19" t="str">
         <f>CONCATENATE("M 78 ",G341)</f>
       </c>
       <c r="I368" s="19" t="str">
         <f>CONCATENATE("M 83 ",O349)</f>
       </c>
-      <c r="J368" s="19"/>
-      <c r="K368" s="19"/>
-      <c r="L368" s="19"/>
-      <c r="M368" s="19"/>
-      <c r="N368" s="19"/>
+      <c r="J368" s="22"/>
+      <c r="K368" s="22"/>
+      <c r="L368" s="22"/>
+      <c r="M368" s="22"/>
+      <c r="N368" s="22"/>
       <c r="O368" s="19" t="str">
         <f>CONCATENATE("M 82 ",O341)</f>
       </c>
@@ -8902,21 +8927,21 @@
       <c r="F370" t="s">
         <v>212</v>
       </c>
-      <c r="G370" s="15"/>
+      <c r="G370" s="23"/>
       <c r="N370" t="s">
         <v>212</v>
       </c>
-      <c r="O370" s="15"/>
+      <c r="O370" s="23"/>
     </row>
     <row r="371">
       <c r="F371" t="s">
         <v>213</v>
       </c>
-      <c r="G371" s="15"/>
+      <c r="G371" s="23"/>
       <c r="N371" t="s">
         <v>213</v>
       </c>
-      <c r="O371" s="15"/>
+      <c r="O371" s="23"/>
     </row>
     <row r="379">
       <c r="A379" s="11" t="s">
@@ -8962,22 +8987,22 @@
       <c r="A381" s="19" t="str">
         <f>CONCATENATE("M 85 ",G370)</f>
       </c>
-      <c r="B381" s="19"/>
-      <c r="C381" s="19"/>
-      <c r="D381" s="19"/>
-      <c r="E381" s="19"/>
-      <c r="F381" s="19"/>
+      <c r="B381" s="22"/>
+      <c r="C381" s="22"/>
+      <c r="D381" s="22"/>
+      <c r="E381" s="22"/>
+      <c r="F381" s="22"/>
       <c r="G381" s="19" t="str">
         <f>CONCATENATE("M 84 ",G362)</f>
       </c>
       <c r="I381" s="19" t="str">
         <f>CONCATENATE("M 87 ",O370)</f>
       </c>
-      <c r="J381" s="19"/>
-      <c r="K381" s="19"/>
-      <c r="L381" s="19"/>
-      <c r="M381" s="19"/>
-      <c r="N381" s="19"/>
+      <c r="J381" s="22"/>
+      <c r="K381" s="22"/>
+      <c r="L381" s="22"/>
+      <c r="M381" s="22"/>
+      <c r="N381" s="22"/>
       <c r="O381" s="19" t="str">
         <f>CONCATENATE("M 86 ",O362)</f>
       </c>
@@ -8986,21 +9011,21 @@
       <c r="F383" t="s">
         <v>212</v>
       </c>
-      <c r="G383" s="15"/>
+      <c r="G383" s="23"/>
       <c r="N383" t="s">
         <v>212</v>
       </c>
-      <c r="O383" s="15"/>
+      <c r="O383" s="23"/>
     </row>
     <row r="384">
       <c r="F384" t="s">
         <v>213</v>
       </c>
-      <c r="G384" s="15"/>
+      <c r="G384" s="23"/>
       <c r="N384" t="s">
         <v>213</v>
       </c>
-      <c r="O384" s="15"/>
+      <c r="O384" s="23"/>
     </row>
     <row r="392">
       <c r="A392" s="11" t="s">
@@ -9028,11 +9053,11 @@
       <c r="A394" s="19" t="str">
         <f>CONCATENATE("M 89 ",O383)</f>
       </c>
-      <c r="B394" s="19"/>
-      <c r="C394" s="19"/>
-      <c r="D394" s="19"/>
-      <c r="E394" s="19"/>
-      <c r="F394" s="19"/>
+      <c r="B394" s="22"/>
+      <c r="C394" s="22"/>
+      <c r="D394" s="22"/>
+      <c r="E394" s="22"/>
+      <c r="F394" s="22"/>
       <c r="G394" s="19" t="str">
         <f>CONCATENATE("M 88 ",G383)</f>
       </c>
@@ -9041,15 +9066,16 @@
       <c r="F396" t="s">
         <v>212</v>
       </c>
-      <c r="G396" s="15"/>
+      <c r="G396" s="23"/>
     </row>
     <row r="397">
       <c r="F397" t="s">
         <v>213</v>
       </c>
-      <c r="G397" s="15"/>
+      <c r="G397" s="23"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="92">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
@@ -9380,6 +9406,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -9603,6 +9630,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName localSheetId="11" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
     <definedName localSheetId="12" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$404</definedName>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$404</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>data!D3</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>data!D7</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
@@ -4199,7 +4199,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>data!D8</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -4207,7 +4207,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>data!D9</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
@@ -4215,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>data!D10</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -4223,7 +4223,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>data!D11</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -4231,7 +4231,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>data!D12</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -4239,7 +4239,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>data!D13</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -4247,7 +4247,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>data!D14</f>
+        <f>'data'!D14</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
@@ -4255,7 +4255,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>data!D15</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -4263,7 +4263,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>data!D16</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -4271,7 +4271,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>data!D17</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
@@ -4279,7 +4279,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>data!D18</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
@@ -4287,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>data!D19</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4295,7 +4295,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="18" t="str">
-        <f>data!D20</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
@@ -4303,7 +4303,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="18" t="str">
-        <f>data!D21</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4311,7 +4311,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="18" t="str">
-        <f>data!D22</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
@@ -4319,7 +4319,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>data!D23</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
@@ -4327,7 +4327,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="18" t="str">
-        <f>data!D24</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
@@ -4335,7 +4335,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>data!D25</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4343,7 +4343,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>data!D26</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
@@ -4351,7 +4351,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>data!D27</f>
+        <f>'data'!D27</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
@@ -4359,7 +4359,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="18" t="str">
-        <f>data!D28</f>
+        <f>'data'!D28</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
@@ -4367,7 +4367,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="18" t="str">
-        <f>data!D29</f>
+        <f>'data'!D29</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="18" t="str">
-        <f>data!D30</f>
+        <f>'data'!D30</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
@@ -4383,7 +4383,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="18" t="str">
-        <f>data!D31</f>
+        <f>'data'!D31</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
@@ -4391,7 +4391,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>data!D32</f>
+        <f>'data'!D32</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4399,7 +4399,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="18" t="str">
-        <f>data!D33</f>
+        <f>'data'!D33</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
@@ -4407,7 +4407,7 @@
         <v>31</v>
       </c>
       <c r="B29" s="18" t="str">
-        <f>data!D34</f>
+        <f>'data'!D34</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
@@ -4415,7 +4415,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="18" t="str">
-        <f>data!D35</f>
+        <f>'data'!D35</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
@@ -4423,7 +4423,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>data!D36</f>
+        <f>'data'!D36</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
@@ -4431,7 +4431,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>data!D37</f>
+        <f>'data'!D37</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
@@ -4439,7 +4439,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>data!D6</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
@@ -4447,7 +4447,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>data!D38</f>
+        <f>'data'!D38</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
@@ -4455,7 +4455,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>data!D39</f>
+        <f>'data'!D39</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
@@ -4463,7 +4463,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>data!D40</f>
+        <f>'data'!D40</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
@@ -4471,7 +4471,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>data!D41</f>
+        <f>'data'!D41</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
@@ -4479,7 +4479,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>data!D42</f>
+        <f>'data'!D42</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4487,7 +4487,7 @@
         <v>40</v>
       </c>
       <c r="B39" s="18" t="str">
-        <f>data!D43</f>
+        <f>'data'!D43</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
@@ -4495,7 +4495,7 @@
         <v>41</v>
       </c>
       <c r="B40" s="18" t="str">
-        <f>data!D44</f>
+        <f>'data'!D44</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
@@ -4503,7 +4503,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="18" t="str">
-        <f>data!D45</f>
+        <f>'data'!D45</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
@@ -4511,7 +4511,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>data!D46</f>
+        <f>'data'!D46</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
@@ -4519,7 +4519,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="18" t="str">
-        <f>data!D47</f>
+        <f>'data'!D47</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
@@ -4527,7 +4527,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="18" t="str">
-        <f>data!D48</f>
+        <f>'data'!D48</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
@@ -4535,7 +4535,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="18" t="str">
-        <f>data!D49</f>
+        <f>'data'!D49</f>
       </c>
     </row>
     <row r="46" ht="270" customHeight="true">
@@ -4543,7 +4543,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="18" t="str">
-        <f>data!D50</f>
+        <f>'data'!D50</f>
       </c>
     </row>
   </sheetData>
@@ -4584,7 +4584,7 @@
         <v>48</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>data!D51</f>
+        <f>'data'!D51</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -4592,7 +4592,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>data!D52</f>
+        <f>'data'!D52</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
@@ -4600,7 +4600,7 @@
         <v>50</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>data!D53</f>
+        <f>'data'!D53</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -4608,7 +4608,7 @@
         <v>51</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>data!D54</f>
+        <f>'data'!D54</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
@@ -4616,7 +4616,7 @@
         <v>52</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>data!D55</f>
+        <f>'data'!D55</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -4624,7 +4624,7 @@
         <v>53</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>data!D56</f>
+        <f>'data'!D56</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -4632,7 +4632,7 @@
         <v>54</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>data!D57</f>
+        <f>'data'!D57</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -4640,7 +4640,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>data!D58</f>
+        <f>'data'!D58</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -4648,7 +4648,7 @@
         <v>56</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>data!D59</f>
+        <f>'data'!D59</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
@@ -4656,7 +4656,7 @@
         <v>57</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>data!D60</f>
+        <f>'data'!D60</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -4664,7 +4664,7 @@
         <v>58</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>data!D61</f>
+        <f>'data'!D61</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -4672,7 +4672,7 @@
         <v>59</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>data!D62</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
@@ -4680,7 +4680,7 @@
         <v>60</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>data!D63</f>
+        <f>'data'!D63</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
@@ -4688,7 +4688,7 @@
         <v>61</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>data!D64</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4696,7 +4696,7 @@
         <v>62</v>
       </c>
       <c r="B15" s="18" t="str">
-        <f>data!D65</f>
+        <f>'data'!D65</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
@@ -4704,7 +4704,7 @@
         <v>63</v>
       </c>
       <c r="B16" s="18" t="str">
-        <f>data!D66</f>
+        <f>'data'!D66</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4712,7 +4712,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="18" t="str">
-        <f>data!D67</f>
+        <f>'data'!D67</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
@@ -4720,7 +4720,7 @@
         <v>65</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>data!D68</f>
+        <f>'data'!D68</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
@@ -4728,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="18" t="str">
-        <f>data!D4</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
@@ -4736,7 +4736,7 @@
         <v>66</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>data!D69</f>
+        <f>'data'!D69</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4744,7 +4744,7 @@
         <v>67</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>data!D70</f>
+        <f>'data'!D70</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
@@ -4752,7 +4752,7 @@
         <v>68</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>data!D71</f>
+        <f>'data'!D71</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
@@ -4760,7 +4760,7 @@
         <v>69</v>
       </c>
       <c r="B23" s="18" t="str">
-        <f>data!D72</f>
+        <f>'data'!D72</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
@@ -4768,7 +4768,7 @@
         <v>70</v>
       </c>
       <c r="B24" s="18" t="str">
-        <f>data!D73</f>
+        <f>'data'!D73</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
@@ -4776,7 +4776,7 @@
         <v>71</v>
       </c>
       <c r="B25" s="18" t="str">
-        <f>data!D74</f>
+        <f>'data'!D74</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
@@ -4784,7 +4784,7 @@
         <v>72</v>
       </c>
       <c r="B26" s="18" t="str">
-        <f>data!D75</f>
+        <f>'data'!D75</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
@@ -4792,7 +4792,7 @@
         <v>73</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>data!D76</f>
+        <f>'data'!D76</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4800,7 +4800,7 @@
         <v>74</v>
       </c>
       <c r="B28" s="18" t="str">
-        <f>data!D77</f>
+        <f>'data'!D77</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
@@ -4808,7 +4808,7 @@
         <v>75</v>
       </c>
       <c r="B29" s="18" t="str">
-        <f>data!D78</f>
+        <f>'data'!D78</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
@@ -4816,7 +4816,7 @@
         <v>76</v>
       </c>
       <c r="B30" s="18" t="str">
-        <f>data!D79</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
@@ -4824,7 +4824,7 @@
         <v>77</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>data!D80</f>
+        <f>'data'!D80</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
@@ -4832,7 +4832,7 @@
         <v>78</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>data!D81</f>
+        <f>'data'!D81</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
@@ -4840,7 +4840,7 @@
         <v>79</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>data!D82</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
@@ -4848,7 +4848,7 @@
         <v>80</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>data!D83</f>
+        <f>'data'!D83</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
@@ -4856,7 +4856,7 @@
         <v>81</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>data!D84</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
@@ -4864,7 +4864,7 @@
         <v>82</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>data!D85</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
@@ -4872,7 +4872,7 @@
         <v>83</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>data!D86</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
@@ -4880,7 +4880,7 @@
         <v>84</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>data!D87</f>
+        <f>'data'!D87</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4888,7 +4888,7 @@
         <v>85</v>
       </c>
       <c r="B39" s="18" t="str">
-        <f>data!D88</f>
+        <f>'data'!D88</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
@@ -4896,7 +4896,7 @@
         <v>86</v>
       </c>
       <c r="B40" s="18" t="str">
-        <f>data!D89</f>
+        <f>'data'!D89</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
@@ -4904,7 +4904,7 @@
         <v>87</v>
       </c>
       <c r="B41" s="18" t="str">
-        <f>data!D90</f>
+        <f>'data'!D90</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
@@ -4912,7 +4912,7 @@
         <v>88</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>data!D91</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
@@ -4920,7 +4920,7 @@
         <v>89</v>
       </c>
       <c r="B43" s="18" t="str">
-        <f>data!D92</f>
+        <f>'data'!D92</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
@@ -4928,7 +4928,7 @@
         <v>90</v>
       </c>
       <c r="B44" s="18" t="str">
-        <f>data!D93</f>
+        <f>'data'!D93</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
@@ -4936,7 +4936,7 @@
         <v>2</v>
       </c>
       <c r="B45" s="18" t="str">
-        <f>data!D5</f>
+        <f>'data'!D5</f>
       </c>
     </row>
   </sheetData>
@@ -5249,19 +5249,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -22,6 +22,14 @@
     <sheet name="Names to Print B" sheetId="17" r:id="rId20"/>
   </sheets>
   <definedNames>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Tree 1'!$A$1:$K$35</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Tree 2'!$A$1:$K$35</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 3'!$A$1:$K$35</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 4'!$A$1:$K$35</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Tree 5'!$A$1:$K$35</definedName>
+    <definedName localSheetId="8" name="_xlnm.Print_Area">'Tree 6'!$A$1:$K$35</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Tree 7'!$A$1:$K$35</definedName>
+    <definedName localSheetId="10" name="_xlnm.Print_Area">'Tree 8'!$A$1:$K$35</definedName>
     <definedName localSheetId="11" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
     <definedName localSheetId="12" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$404</definedName>
@@ -2800,12 +2808,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2822,11 +2835,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3018,18 +3026,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3046,11 +3061,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3251,18 +3261,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3279,11 +3296,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3475,18 +3487,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3503,11 +3522,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3708,18 +3722,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3736,11 +3757,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3932,18 +3948,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3960,11 +3983,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -4165,8 +4183,10 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -9185,12 +9205,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9207,11 +9232,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -9403,18 +9423,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9431,11 +9458,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -9627,7 +9649,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -1189,7 +1189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -2837,6 +2837,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>77</v>
       </c>
@@ -2856,6 +2858,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>79</v>
       </c>
@@ -2877,6 +2881,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>54</v>
       </c>
@@ -2930,6 +2936,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>21</v>
       </c>
@@ -2985,6 +2993,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>32</v>
       </c>
@@ -3063,6 +3073,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>36</v>
       </c>
@@ -3112,6 +3124,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>42</v>
       </c>
@@ -3165,6 +3179,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>96</v>
       </c>
@@ -3220,6 +3236,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>102</v>
       </c>
@@ -3298,6 +3316,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>108</v>
       </c>
@@ -3317,6 +3337,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>110</v>
       </c>
@@ -3338,6 +3360,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>112</v>
       </c>
@@ -3391,6 +3415,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>120</v>
       </c>
@@ -3446,6 +3472,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>129</v>
       </c>
@@ -3524,6 +3552,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>138</v>
       </c>
@@ -3573,6 +3603,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>147</v>
       </c>
@@ -3626,6 +3658,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>156</v>
       </c>
@@ -3681,6 +3715,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>160</v>
       </c>
@@ -3759,6 +3795,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>166</v>
       </c>
@@ -3778,6 +3816,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>168</v>
       </c>
@@ -3799,6 +3839,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>162</v>
       </c>
@@ -3852,6 +3894,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>175</v>
       </c>
@@ -3907,6 +3951,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>181</v>
       </c>
@@ -3985,6 +4031,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>186</v>
       </c>
@@ -4034,6 +4082,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>192</v>
       </c>
@@ -4087,6 +4137,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>197</v>
       </c>
@@ -4142,6 +4194,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>203</v>
       </c>
@@ -9234,6 +9288,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>18</v>
       </c>
@@ -9253,6 +9309,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>30</v>
       </c>
@@ -9274,6 +9332,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>32</v>
       </c>
@@ -9327,6 +9387,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>38</v>
       </c>
@@ -9382,6 +9444,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>44</v>
       </c>
@@ -9460,6 +9524,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>50</v>
       </c>
@@ -9479,6 +9545,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>52</v>
       </c>
@@ -9500,6 +9568,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>54</v>
       </c>
@@ -9553,6 +9623,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>60</v>
       </c>
@@ -9608,6 +9680,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>68</v>
       </c>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -683,175 +683,175 @@
     <t>2.</t>
   </si>
   <si>
+    <t>Round 1 - Match 17</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 2</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 18</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 3</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 19</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 4</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 20</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 5</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 21</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 6</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 22</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 7</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 23</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 8</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 24</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 9</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 25</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 10</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 26</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 11</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 27</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 12</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 28</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 13</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 29</t>
+  </si>
+  <si>
     <t>Round 1 - Match 14</t>
   </si>
   <si>
-    <t>Round 1 - Match 2</t>
+    <t>Round 1 - Match 30</t>
   </si>
   <si>
     <t>Round 1 - Match 15</t>
   </si>
   <si>
-    <t>Round 1 - Match 3</t>
+    <t>Round 1 - Match 31</t>
   </si>
   <si>
     <t>Round 1 - Match 16</t>
   </si>
   <si>
-    <t>Round 1 - Match 4</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 17</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 5</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 18</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 6</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 19</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 7</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 20</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 8</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 21</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 9</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 22</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 10</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 23</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 11</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 24</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 12</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 25</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 13</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 26</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 27</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 28</t>
+    <t>Round 1 - Match 32</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 33</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 46</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 34</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 47</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 35</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 48</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 36</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 49</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 37</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 50</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 38</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 51</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 39</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 52</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 40</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 53</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 41</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 54</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 42</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 55</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 43</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 56</t>
   </si>
   <si>
     <t>Round 2 - Match 44</t>
   </si>
   <si>
-    <t>Round 2 - Match 29</t>
+    <t>Round 2 - Match 57</t>
   </si>
   <si>
     <t>Round 2 - Match 45</t>
   </si>
   <si>
-    <t>Round 2 - Match 30</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 46</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 31</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 47</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 32</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 48</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 33</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 49</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 34</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 50</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 35</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 51</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 36</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 52</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 37</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 53</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 38</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 54</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 39</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 55</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 40</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 56</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 41</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 57</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 42</t>
-  </si>
-  <si>
     <t>Round 2 - Match 58</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 43</t>
   </si>
   <si>
     <t>Round 2 - Match 59</t>
@@ -2836,35 +2836,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>77</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>36</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -2897,7 +2891,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -2913,7 +2907,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -2950,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -2966,7 +2960,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3007,7 +3001,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3021,7 +3015,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3085,7 +3079,7 @@
     </row>
     <row r="8">
       <c r="G8" s="13">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -3099,7 +3093,7 @@
     <row r="10">
       <c r="D10" s="14"/>
       <c r="E10" s="13">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
@@ -3140,7 +3134,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -3156,7 +3150,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3193,7 +3187,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -3209,7 +3203,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3250,7 +3244,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3264,7 +3258,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3315,35 +3309,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>108</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>44</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -3376,7 +3364,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -3392,7 +3380,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3429,7 +3417,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -3445,7 +3433,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3486,7 +3474,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3500,7 +3488,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3564,7 +3552,7 @@
     </row>
     <row r="8">
       <c r="G8" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -3578,7 +3566,7 @@
     <row r="10">
       <c r="D10" s="14"/>
       <c r="E10" s="13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
@@ -3619,7 +3607,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -3635,7 +3623,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3672,7 +3660,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -3688,7 +3676,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3729,7 +3717,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3743,7 +3731,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3794,35 +3782,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>166</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>52</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -3871,7 +3853,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3924,7 +3906,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3979,7 +3961,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -4057,7 +4039,7 @@
     <row r="10">
       <c r="D10" s="14"/>
       <c r="E10" s="13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
@@ -4114,7 +4096,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -4167,7 +4149,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -4222,7 +4204,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -5395,7 +5377,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5403,10 +5385,10 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$32</f>
       </c>
       <c r="I4" s="19" t="str">
-        <f>'data'!$B$54</f>
+        <f>'data'!$B$51</f>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
@@ -5414,7 +5396,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
-        <f>'data'!$B$53</f>
+        <f>'data'!$B$50</f>
       </c>
     </row>
     <row r="6">
@@ -5479,7 +5461,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -5487,10 +5469,10 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$37</f>
       </c>
       <c r="I12" s="19" t="str">
-        <f>'data'!$B$57</f>
+        <f>'data'!$B$54</f>
       </c>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
@@ -5498,7 +5480,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
-        <f>'data'!$B$56</f>
+        <f>'data'!$B$53</f>
       </c>
     </row>
     <row r="14">
@@ -5563,7 +5545,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$16</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -5571,10 +5553,10 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$60</f>
+        <f>'data'!$B$57</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -5582,7 +5564,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$56</f>
       </c>
     </row>
     <row r="22">
@@ -5647,7 +5629,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$16</f>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -5655,10 +5637,10 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$20</f>
+        <f>'data'!$B$43</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$60</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -5666,7 +5648,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$81</f>
       </c>
     </row>
     <row r="30">
@@ -5731,7 +5713,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="str">
-        <f>'data'!$B$24</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -5739,10 +5721,10 @@
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
       <c r="G36" s="19" t="str">
-        <f>'data'!$B$23</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="I36" s="19" t="str">
-        <f>'data'!$B$66</f>
+        <f>'data'!$B$63</f>
       </c>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
@@ -5750,7 +5732,7 @@
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="19" t="str">
-        <f>'data'!$B$65</f>
+        <f>'data'!$B$62</f>
       </c>
     </row>
     <row r="38">
@@ -5815,7 +5797,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="str">
-        <f>'data'!$B$27</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -5823,10 +5805,10 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="I44" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$66</f>
       </c>
       <c r="J44" s="22"/>
       <c r="K44" s="22"/>
@@ -5834,7 +5816,7 @@
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
       <c r="O44" s="19" t="str">
-        <f>'data'!$B$68</f>
+        <f>'data'!$B$65</f>
       </c>
     </row>
     <row r="46">
@@ -5899,7 +5881,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$24</f>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -5907,10 +5889,10 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
-        <f>'data'!$B$31</f>
+        <f>'data'!$B$23</f>
       </c>
       <c r="I52" s="19" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="J52" s="22"/>
       <c r="K52" s="22"/>
@@ -5918,7 +5900,7 @@
       <c r="M52" s="22"/>
       <c r="N52" s="22"/>
       <c r="O52" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$68</f>
       </c>
     </row>
     <row r="54">
@@ -5983,7 +5965,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$27</f>
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -5991,10 +5973,10 @@
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
       <c r="G60" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="I60" s="19" t="str">
-        <f>'data'!$B$76</f>
+        <f>'data'!$B$88</f>
       </c>
       <c r="J60" s="22"/>
       <c r="K60" s="22"/>
@@ -6002,7 +5984,7 @@
       <c r="M60" s="22"/>
       <c r="N60" s="22"/>
       <c r="O60" s="19" t="str">
-        <f>'data'!$B$75</f>
+        <f>'data'!$B$74</f>
       </c>
     </row>
     <row r="62">
@@ -6067,7 +6049,7 @@
     </row>
     <row r="68">
       <c r="A68" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -6075,10 +6057,10 @@
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
       <c r="G68" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$28</f>
       </c>
       <c r="I68" s="19" t="str">
-        <f>'data'!$B$79</f>
+        <f>'data'!$B$73</f>
       </c>
       <c r="J68" s="22"/>
       <c r="K68" s="22"/>
@@ -6086,7 +6068,7 @@
       <c r="M68" s="22"/>
       <c r="N68" s="22"/>
       <c r="O68" s="19" t="str">
-        <f>'data'!$B$78</f>
+        <f>'data'!$B$72</f>
       </c>
     </row>
     <row r="70">
@@ -6151,7 +6133,7 @@
     </row>
     <row r="76">
       <c r="A76" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$32</f>
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -6159,10 +6141,10 @@
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
       <c r="G76" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$31</f>
       </c>
       <c r="I76" s="19" t="str">
-        <f>'data'!$B$82</f>
+        <f>'data'!$B$76</f>
       </c>
       <c r="J76" s="22"/>
       <c r="K76" s="22"/>
@@ -6170,7 +6152,7 @@
       <c r="M76" s="22"/>
       <c r="N76" s="22"/>
       <c r="O76" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$75</f>
       </c>
     </row>
     <row r="78">
@@ -6235,7 +6217,7 @@
     </row>
     <row r="84">
       <c r="A84" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -6243,10 +6225,10 @@
       <c r="E84" s="22"/>
       <c r="F84" s="22"/>
       <c r="G84" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="I84" s="19" t="str">
-        <f>'data'!$B$85</f>
+        <f>'data'!$B$79</f>
       </c>
       <c r="J84" s="22"/>
       <c r="K84" s="22"/>
@@ -6254,7 +6236,7 @@
       <c r="M84" s="22"/>
       <c r="N84" s="22"/>
       <c r="O84" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$78</f>
       </c>
     </row>
     <row r="86">
@@ -6319,7 +6301,7 @@
     </row>
     <row r="92">
       <c r="A92" s="19" t="str">
-        <f>'data'!$B$46</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6327,10 +6309,10 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
-        <f>'data'!$B$45</f>
+        <f>'data'!$B$37</f>
       </c>
       <c r="I92" s="19" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$82</f>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="22"/>
@@ -6338,7 +6320,7 @@
       <c r="M92" s="22"/>
       <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
-        <f>'data'!$B$87</f>
+        <f>'data'!$B$81</f>
       </c>
     </row>
     <row r="94">
@@ -6403,7 +6385,7 @@
     </row>
     <row r="100">
       <c r="A100" s="19" t="str">
-        <f>'data'!$B$49</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6411,10 +6393,10 @@
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
-        <f>'data'!$B$48</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="I100" s="19" t="str">
-        <f>'data'!$B$91</f>
+        <f>'data'!$B$85</f>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -6422,7 +6404,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
-        <f>'data'!$B$90</f>
+        <f>'data'!$B$84</f>
       </c>
     </row>
     <row r="102">
@@ -6446,8 +6428,17 @@
       <c r="O103" s="23"/>
     </row>
     <row r="106">
+      <c r="A106" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
       <c r="I106" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
@@ -6457,6 +6448,15 @@
       <c r="O106" s="11"/>
     </row>
     <row r="107">
+      <c r="A107" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G107" s="20" t="s">
+        <v>211</v>
+      </c>
       <c r="I107" s="21" t="s">
         <v>209</v>
       </c>
@@ -6468,8 +6468,19 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" s="19" t="str">
+        <f>'data'!$B$43</f>
+      </c>
+      <c r="B108" s="22"/>
+      <c r="C108" s="22"/>
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="19" t="str">
+        <f>'data'!$B$42</f>
+      </c>
       <c r="I108" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$88</f>
       </c>
       <c r="J108" s="22"/>
       <c r="K108" s="22"/>
@@ -6477,192 +6488,200 @@
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
-        <f>'data'!$B$93</f>
+        <f>'data'!$B$87</f>
       </c>
     </row>
     <row r="110">
+      <c r="F110" t="s">
+        <v>212</v>
+      </c>
+      <c r="G110" s="23"/>
       <c r="N110" t="s">
         <v>212</v>
       </c>
       <c r="O110" s="23"/>
     </row>
     <row r="111">
+      <c r="F111" t="s">
+        <v>213</v>
+      </c>
+      <c r="G111" s="23"/>
       <c r="N111" t="s">
         <v>213</v>
       </c>
       <c r="O111" s="23"/>
     </row>
+    <row r="114">
+      <c r="A114" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="11"/>
+      <c r="I114" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="J114" s="11"/>
+      <c r="K114" s="11"/>
+      <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
+      <c r="N114" s="11"/>
+      <c r="O114" s="11"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G115" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="I115" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="L115" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="O115" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="str">
+        <f>'data'!$B$46</f>
+      </c>
+      <c r="B116" s="22"/>
+      <c r="C116" s="22"/>
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="19" t="str">
+        <f>'data'!$B$45</f>
+      </c>
+      <c r="I116" s="19" t="str">
+        <f>'data'!$B$91</f>
+      </c>
+      <c r="J116" s="22"/>
+      <c r="K116" s="22"/>
+      <c r="L116" s="22"/>
+      <c r="M116" s="22"/>
+      <c r="N116" s="22"/>
+      <c r="O116" s="19" t="str">
+        <f>'data'!$B$90</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="F118" t="s">
+        <v>212</v>
+      </c>
+      <c r="G118" s="23"/>
+      <c r="N118" t="s">
+        <v>212</v>
+      </c>
+      <c r="O118" s="23"/>
+    </row>
     <row r="119">
-      <c r="A119" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="11"/>
-      <c r="I119" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="J119" s="11"/>
-      <c r="K119" s="11"/>
-      <c r="L119" s="11"/>
-      <c r="M119" s="11"/>
-      <c r="N119" s="11"/>
-      <c r="O119" s="11"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="21" t="s">
+      <c r="F119" t="s">
+        <v>213</v>
+      </c>
+      <c r="G119" s="23"/>
+      <c r="N119" t="s">
+        <v>213</v>
+      </c>
+      <c r="O119" s="23"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B122" s="11"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
+      <c r="F122" s="11"/>
+      <c r="G122" s="11"/>
+      <c r="I122" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="J122" s="11"/>
+      <c r="K122" s="11"/>
+      <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
+      <c r="N122" s="11"/>
+      <c r="O122" s="11"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="D123" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="G120" s="20" t="s">
+      <c r="G123" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="I120" s="21" t="s">
+      <c r="I123" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="L120" s="19" t="s">
+      <c r="L123" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="O120" s="20" t="s">
+      <c r="O123" s="20" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="19" t="str">
-        <f>'data'!$B$35</f>
-      </c>
-      <c r="B121" s="22"/>
-      <c r="C121" s="22"/>
-      <c r="D121" s="22"/>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
-      <c r="G121" s="19" t="str">
-        <f>'data'!$B$32</f>
-      </c>
-      <c r="I121" s="19" t="str">
-        <f>'data'!$B$51</f>
-      </c>
-      <c r="J121" s="22"/>
-      <c r="K121" s="22"/>
-      <c r="L121" s="22"/>
-      <c r="M121" s="22"/>
-      <c r="N121" s="22"/>
-      <c r="O121" s="19" t="str">
-        <f>'data'!$B$50</f>
-      </c>
-    </row>
-    <row r="123">
-      <c r="F123" t="s">
+    <row r="124">
+      <c r="A124" s="19" t="str">
+        <f>'data'!$B$49</f>
+      </c>
+      <c r="B124" s="22"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="22"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="19" t="str">
+        <f>'data'!$B$48</f>
+      </c>
+      <c r="I124" s="19" t="str">
+        <f>'data'!$B$5</f>
+      </c>
+      <c r="J124" s="22"/>
+      <c r="K124" s="22"/>
+      <c r="L124" s="22"/>
+      <c r="M124" s="22"/>
+      <c r="N124" s="22"/>
+      <c r="O124" s="19" t="str">
+        <f>'data'!$B$93</f>
+      </c>
+    </row>
+    <row r="126">
+      <c r="F126" t="s">
         <v>212</v>
       </c>
-      <c r="G123" s="23"/>
-      <c r="N123" t="s">
+      <c r="G126" s="23"/>
+      <c r="N126" t="s">
         <v>212</v>
       </c>
-      <c r="O123" s="23"/>
-    </row>
-    <row r="124">
-      <c r="F124" t="s">
+      <c r="O126" s="23"/>
+    </row>
+    <row r="127">
+      <c r="F127" t="s">
         <v>213</v>
       </c>
-      <c r="G124" s="23"/>
-      <c r="N124" t="s">
+      <c r="G127" s="23"/>
+      <c r="N127" t="s">
         <v>213</v>
       </c>
-      <c r="O124" s="23"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
-      <c r="I127" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="J127" s="11"/>
-      <c r="K127" s="11"/>
-      <c r="L127" s="11"/>
-      <c r="M127" s="11"/>
-      <c r="N127" s="11"/>
-      <c r="O127" s="11"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D128" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="G128" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="I128" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="L128" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="O128" s="20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G6)</f>
-      </c>
-      <c r="B129" s="22"/>
-      <c r="C129" s="22"/>
-      <c r="D129" s="22"/>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22"/>
-      <c r="G129" s="19" t="str">
-        <f>'data'!$B$36</f>
-      </c>
-      <c r="I129" s="19" t="str">
-        <f>CONCATENATE("M 14 ",O6)</f>
-      </c>
-      <c r="J129" s="22"/>
-      <c r="K129" s="22"/>
-      <c r="L129" s="22"/>
-      <c r="M129" s="22"/>
-      <c r="N129" s="22"/>
-      <c r="O129" s="19" t="str">
-        <f>'data'!$B$52</f>
-      </c>
-    </row>
-    <row r="131">
-      <c r="F131" t="s">
-        <v>212</v>
-      </c>
-      <c r="G131" s="23"/>
-      <c r="N131" t="s">
-        <v>212</v>
-      </c>
-      <c r="O131" s="23"/>
-    </row>
-    <row r="132">
-      <c r="F132" t="s">
-        <v>213</v>
-      </c>
-      <c r="G132" s="23"/>
-      <c r="N132" t="s">
-        <v>213</v>
-      </c>
-      <c r="O132" s="23"/>
+      <c r="O127" s="23"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
@@ -6671,7 +6690,7 @@
       <c r="F135" s="11"/>
       <c r="G135" s="11"/>
       <c r="I135" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
@@ -6710,10 +6729,10 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$36</f>
       </c>
       <c r="I137" s="19" t="str">
-        <f>CONCATENATE("M 15 ",O14)</f>
+        <f>CONCATENATE("M 18 ",O14)</f>
       </c>
       <c r="J137" s="22"/>
       <c r="K137" s="22"/>
@@ -6721,7 +6740,7 @@
       <c r="M137" s="22"/>
       <c r="N137" s="22"/>
       <c r="O137" s="19" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$52</f>
       </c>
     </row>
     <row r="139">
@@ -6746,7 +6765,7 @@
     </row>
     <row r="143">
       <c r="A143" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
@@ -6755,7 +6774,7 @@
       <c r="F143" s="11"/>
       <c r="G143" s="11"/>
       <c r="I143" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J143" s="11"/>
       <c r="K143" s="11"/>
@@ -6794,10 +6813,10 @@
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="I145" s="19" t="str">
-        <f>CONCATENATE("M 16 ",O22)</f>
+        <f>CONCATENATE("M 19 ",O22)</f>
       </c>
       <c r="J145" s="22"/>
       <c r="K145" s="22"/>
@@ -6805,7 +6824,7 @@
       <c r="M145" s="22"/>
       <c r="N145" s="22"/>
       <c r="O145" s="19" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$55</f>
       </c>
     </row>
     <row r="147">
@@ -6830,7 +6849,7 @@
     </row>
     <row r="151">
       <c r="A151" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
@@ -6839,7 +6858,7 @@
       <c r="F151" s="11"/>
       <c r="G151" s="11"/>
       <c r="I151" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J151" s="11"/>
       <c r="K151" s="11"/>
@@ -6870,7 +6889,7 @@
     </row>
     <row r="153">
       <c r="A153" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>CONCATENATE("M 4 ",G30)</f>
       </c>
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
@@ -6878,10 +6897,10 @@
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I153" s="19" t="str">
-        <f>CONCATENATE("M 17 ",O30)</f>
+        <f>CONCATENATE("M 20 ",O30)</f>
       </c>
       <c r="J153" s="22"/>
       <c r="K153" s="22"/>
@@ -6889,7 +6908,7 @@
       <c r="M153" s="22"/>
       <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
-        <f>'data'!$B$61</f>
+        <f>'data'!$B$58</f>
       </c>
     </row>
     <row r="155">
@@ -6914,7 +6933,7 @@
     </row>
     <row r="159">
       <c r="A159" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="11"/>
@@ -6923,7 +6942,7 @@
       <c r="F159" s="11"/>
       <c r="G159" s="11"/>
       <c r="I159" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J159" s="11"/>
       <c r="K159" s="11"/>
@@ -6954,7 +6973,7 @@
     </row>
     <row r="161">
       <c r="A161" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G30)</f>
+        <f>CONCATENATE("M 6 ",G46)</f>
       </c>
       <c r="B161" s="22"/>
       <c r="C161" s="22"/>
@@ -6965,7 +6984,7 @@
         <f>'data'!$B$30</f>
       </c>
       <c r="I161" s="19" t="str">
-        <f>CONCATENATE("M 18 ",O38)</f>
+        <f>CONCATENATE("M 21 ",O38)</f>
       </c>
       <c r="J161" s="22"/>
       <c r="K161" s="22"/>
@@ -6973,7 +6992,7 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$61</f>
       </c>
     </row>
     <row r="163">
@@ -6998,7 +7017,7 @@
     </row>
     <row r="167">
       <c r="A167" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B167" s="11"/>
       <c r="C167" s="11"/>
@@ -7007,7 +7026,7 @@
       <c r="F167" s="11"/>
       <c r="G167" s="11"/>
       <c r="I167" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J167" s="11"/>
       <c r="K167" s="11"/>
@@ -7038,7 +7057,7 @@
     </row>
     <row r="169">
       <c r="A169" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G38)</f>
+        <f>CONCATENATE("M 7 ",G54)</f>
       </c>
       <c r="B169" s="22"/>
       <c r="C169" s="22"/>
@@ -7049,7 +7068,7 @@
         <f>'data'!$B$22</f>
       </c>
       <c r="I169" s="19" t="str">
-        <f>CONCATENATE("M 19 ",O46)</f>
+        <f>CONCATENATE("M 22 ",O46)</f>
       </c>
       <c r="J169" s="22"/>
       <c r="K169" s="22"/>
@@ -7057,7 +7076,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$67</f>
+        <f>'data'!$B$64</f>
       </c>
     </row>
     <row r="171">
@@ -7082,7 +7101,7 @@
     </row>
     <row r="175">
       <c r="A175" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B175" s="11"/>
       <c r="C175" s="11"/>
@@ -7091,7 +7110,7 @@
       <c r="F175" s="11"/>
       <c r="G175" s="11"/>
       <c r="I175" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
@@ -7122,7 +7141,7 @@
     </row>
     <row r="177">
       <c r="A177" s="19" t="str">
-        <f>CONCATENATE("M 6 ",G46)</f>
+        <f>CONCATENATE("M 8 ",G62)</f>
       </c>
       <c r="B177" s="22"/>
       <c r="C177" s="22"/>
@@ -7133,7 +7152,7 @@
         <f>'data'!$B$25</f>
       </c>
       <c r="I177" s="19" t="str">
-        <f>CONCATENATE("M 20 ",O54)</f>
+        <f>CONCATENATE("M 23 ",O54)</f>
       </c>
       <c r="J177" s="22"/>
       <c r="K177" s="22"/>
@@ -7141,7 +7160,7 @@
       <c r="M177" s="22"/>
       <c r="N177" s="22"/>
       <c r="O177" s="19" t="str">
-        <f>'data'!$B$69</f>
+        <f>'data'!$B$67</f>
       </c>
     </row>
     <row r="179">
@@ -7166,7 +7185,7 @@
     </row>
     <row r="183">
       <c r="A183" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="11"/>
@@ -7175,7 +7194,7 @@
       <c r="F183" s="11"/>
       <c r="G183" s="11"/>
       <c r="I183" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
@@ -7206,7 +7225,7 @@
     </row>
     <row r="185">
       <c r="A185" s="19" t="str">
-        <f>'data'!$B$29</f>
+        <f>CONCATENATE("M 10 ",G78)</f>
       </c>
       <c r="B185" s="22"/>
       <c r="C185" s="22"/>
@@ -7214,10 +7233,10 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$28</f>
+        <f>'data'!$B$30</f>
       </c>
       <c r="I185" s="19" t="str">
-        <f>'data'!$B$73</f>
+        <f>CONCATENATE("M 24 ",O62)</f>
       </c>
       <c r="J185" s="22"/>
       <c r="K185" s="22"/>
@@ -7225,7 +7244,7 @@
       <c r="M185" s="22"/>
       <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
-        <f>'data'!$B$72</f>
+        <f>'data'!$B$69</f>
       </c>
     </row>
     <row r="187">
@@ -7250,7 +7269,7 @@
     </row>
     <row r="191">
       <c r="A191" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B191" s="11"/>
       <c r="C191" s="11"/>
@@ -7259,7 +7278,7 @@
       <c r="F191" s="11"/>
       <c r="G191" s="11"/>
       <c r="I191" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J191" s="11"/>
       <c r="K191" s="11"/>
@@ -7290,7 +7309,7 @@
     </row>
     <row r="193">
       <c r="A193" s="19" t="str">
-        <f>CONCATENATE("M 7 ",G54)</f>
+        <f>CONCATENATE("M 11 ",G86)</f>
       </c>
       <c r="B193" s="22"/>
       <c r="C193" s="22"/>
@@ -7298,10 +7317,10 @@
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
       <c r="G193" s="19" t="str">
-        <f>'data'!$B$30</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="I193" s="19" t="str">
-        <f>CONCATENATE("M 21 ",O62)</f>
+        <f>CONCATENATE("M 26 ",O78)</f>
       </c>
       <c r="J193" s="22"/>
       <c r="K193" s="22"/>
@@ -7334,7 +7353,7 @@
     </row>
     <row r="199">
       <c r="A199" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B199" s="11"/>
       <c r="C199" s="11"/>
@@ -7343,7 +7362,7 @@
       <c r="F199" s="11"/>
       <c r="G199" s="11"/>
       <c r="I199" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J199" s="11"/>
       <c r="K199" s="11"/>
@@ -7374,7 +7393,7 @@
     </row>
     <row r="201">
       <c r="A201" s="19" t="str">
-        <f>CONCATENATE("M 8 ",G62)</f>
+        <f>CONCATENATE("M 12 ",G94)</f>
       </c>
       <c r="B201" s="22"/>
       <c r="C201" s="22"/>
@@ -7382,10 +7401,10 @@
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$36</f>
       </c>
       <c r="I201" s="19" t="str">
-        <f>CONCATENATE("M 22 ",O70)</f>
+        <f>CONCATENATE("M 27 ",O86)</f>
       </c>
       <c r="J201" s="22"/>
       <c r="K201" s="22"/>
@@ -7418,7 +7437,7 @@
     </row>
     <row r="207">
       <c r="A207" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="11"/>
@@ -7427,7 +7446,7 @@
       <c r="F207" s="11"/>
       <c r="G207" s="11"/>
       <c r="I207" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
@@ -7458,7 +7477,7 @@
     </row>
     <row r="209">
       <c r="A209" s="19" t="str">
-        <f>CONCATENATE("M 9 ",G70)</f>
+        <f>CONCATENATE("M 13 ",G102)</f>
       </c>
       <c r="B209" s="22"/>
       <c r="C209" s="22"/>
@@ -7466,10 +7485,10 @@
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
-        <f>'data'!$B$36</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="I209" s="19" t="str">
-        <f>CONCATENATE("M 23 ",O78)</f>
+        <f>CONCATENATE("M 28 ",O94)</f>
       </c>
       <c r="J209" s="22"/>
       <c r="K209" s="22"/>
@@ -7502,7 +7521,7 @@
     </row>
     <row r="215">
       <c r="A215" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -7511,7 +7530,7 @@
       <c r="F215" s="11"/>
       <c r="G215" s="11"/>
       <c r="I215" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
@@ -7542,7 +7561,7 @@
     </row>
     <row r="217">
       <c r="A217" s="19" t="str">
-        <f>CONCATENATE("M 10 ",G78)</f>
+        <f>CONCATENATE("M 14 ",G110)</f>
       </c>
       <c r="B217" s="22"/>
       <c r="C217" s="22"/>
@@ -7550,10 +7569,10 @@
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="I217" s="19" t="str">
-        <f>CONCATENATE("M 24 ",O86)</f>
+        <f>CONCATENATE("M 29 ",O102)</f>
       </c>
       <c r="J217" s="22"/>
       <c r="K217" s="22"/>
@@ -7586,7 +7605,7 @@
     </row>
     <row r="223">
       <c r="A223" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B223" s="11"/>
       <c r="C223" s="11"/>
@@ -7595,7 +7614,7 @@
       <c r="F223" s="11"/>
       <c r="G223" s="11"/>
       <c r="I223" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J223" s="11"/>
       <c r="K223" s="11"/>
@@ -7626,7 +7645,7 @@
     </row>
     <row r="225">
       <c r="A225" s="19" t="str">
-        <f>CONCATENATE("M 11 ",G86)</f>
+        <f>CONCATENATE("M 15 ",G118)</f>
       </c>
       <c r="B225" s="22"/>
       <c r="C225" s="22"/>
@@ -7634,10 +7653,10 @@
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
       <c r="G225" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$44</f>
       </c>
       <c r="I225" s="19" t="str">
-        <f>CONCATENATE("M 25 ",O94)</f>
+        <f>CONCATENATE("M 30 ",O110)</f>
       </c>
       <c r="J225" s="22"/>
       <c r="K225" s="22"/>
@@ -7670,7 +7689,7 @@
     </row>
     <row r="231">
       <c r="A231" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B231" s="11"/>
       <c r="C231" s="11"/>
@@ -7679,7 +7698,7 @@
       <c r="F231" s="11"/>
       <c r="G231" s="11"/>
       <c r="I231" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J231" s="11"/>
       <c r="K231" s="11"/>
@@ -7710,7 +7729,7 @@
     </row>
     <row r="233">
       <c r="A233" s="19" t="str">
-        <f>CONCATENATE("M 12 ",G94)</f>
+        <f>CONCATENATE("M 16 ",G126)</f>
       </c>
       <c r="B233" s="22"/>
       <c r="C233" s="22"/>
@@ -7718,10 +7737,10 @@
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
       <c r="G233" s="19" t="str">
-        <f>'data'!$B$44</f>
+        <f>'data'!$B$47</f>
       </c>
       <c r="I233" s="19" t="str">
-        <f>CONCATENATE("M 26 ",O102)</f>
+        <f>CONCATENATE("M 31 ",O118)</f>
       </c>
       <c r="J233" s="22"/>
       <c r="K233" s="22"/>
@@ -7753,15 +7772,6 @@
       <c r="O236" s="23"/>
     </row>
     <row r="239">
-      <c r="A239" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B239" s="11"/>
-      <c r="C239" s="11"/>
-      <c r="D239" s="11"/>
-      <c r="E239" s="11"/>
-      <c r="F239" s="11"/>
-      <c r="G239" s="11"/>
       <c r="I239" s="11" t="s">
         <v>271</v>
       </c>
@@ -7773,15 +7783,6 @@
       <c r="O239" s="11"/>
     </row>
     <row r="240">
-      <c r="A240" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D240" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="G240" s="20" t="s">
-        <v>211</v>
-      </c>
       <c r="I240" s="21" t="s">
         <v>209</v>
       </c>
@@ -7793,19 +7794,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="19" t="str">
-        <f>CONCATENATE("M 13 ",G102)</f>
-      </c>
-      <c r="B241" s="22"/>
-      <c r="C241" s="22"/>
-      <c r="D241" s="22"/>
-      <c r="E241" s="22"/>
-      <c r="F241" s="22"/>
-      <c r="G241" s="19" t="str">
-        <f>'data'!$B$47</f>
-      </c>
       <c r="I241" s="19" t="str">
-        <f>CONCATENATE("M 27 ",O110)</f>
+        <f>CONCATENATE("M 32 ",O126)</f>
       </c>
       <c r="J241" s="22"/>
       <c r="K241" s="22"/>
@@ -7817,20 +7807,12 @@
       </c>
     </row>
     <row r="243">
-      <c r="F243" t="s">
-        <v>212</v>
-      </c>
-      <c r="G243" s="23"/>
       <c r="N243" t="s">
         <v>212</v>
       </c>
       <c r="O243" s="23"/>
     </row>
     <row r="244">
-      <c r="F244" t="s">
-        <v>213</v>
-      </c>
-      <c r="G244" s="23"/>
       <c r="N244" t="s">
         <v>213</v>
       </c>
@@ -7878,7 +7860,7 @@
     </row>
     <row r="254">
       <c r="A254" s="19" t="str">
-        <f>CONCATENATE("M 29 ",G131)</f>
+        <f>CONCATENATE("M 33 ",G139)</f>
       </c>
       <c r="B254" s="22"/>
       <c r="C254" s="22"/>
@@ -7886,10 +7868,10 @@
       <c r="E254" s="22"/>
       <c r="F254" s="22"/>
       <c r="G254" s="19" t="str">
-        <f>CONCATENATE("M 28 ",G123)</f>
+        <f>CONCATENATE("M 1 ",G6)</f>
       </c>
       <c r="I254" s="19" t="str">
-        <f>CONCATENATE("M 45 ",O131)</f>
+        <f>CONCATENATE("M 46 ",O139)</f>
       </c>
       <c r="J254" s="22"/>
       <c r="K254" s="22"/>
@@ -7897,7 +7879,7 @@
       <c r="M254" s="22"/>
       <c r="N254" s="22"/>
       <c r="O254" s="19" t="str">
-        <f>CONCATENATE("M 44 ",O123)</f>
+        <f>CONCATENATE("M 17 ",O6)</f>
       </c>
     </row>
     <row r="256">
@@ -7962,7 +7944,7 @@
     </row>
     <row r="262">
       <c r="A262" s="19" t="str">
-        <f>CONCATENATE("M 31 ",G147)</f>
+        <f>CONCATENATE("M 35 ",G155)</f>
       </c>
       <c r="B262" s="22"/>
       <c r="C262" s="22"/>
@@ -7970,10 +7952,10 @@
       <c r="E262" s="22"/>
       <c r="F262" s="22"/>
       <c r="G262" s="19" t="str">
-        <f>CONCATENATE("M 30 ",G139)</f>
+        <f>CONCATENATE("M 34 ",G147)</f>
       </c>
       <c r="I262" s="19" t="str">
-        <f>CONCATENATE("M 47 ",O147)</f>
+        <f>CONCATENATE("M 48 ",O155)</f>
       </c>
       <c r="J262" s="22"/>
       <c r="K262" s="22"/>
@@ -7981,7 +7963,7 @@
       <c r="M262" s="22"/>
       <c r="N262" s="22"/>
       <c r="O262" s="19" t="str">
-        <f>CONCATENATE("M 46 ",O139)</f>
+        <f>CONCATENATE("M 47 ",O147)</f>
       </c>
     </row>
     <row r="264">
@@ -8046,7 +8028,7 @@
     </row>
     <row r="270">
       <c r="A270" s="19" t="str">
-        <f>CONCATENATE("M 33 ",G163)</f>
+        <f>CONCATENATE("M 36 ",G163)</f>
       </c>
       <c r="B270" s="22"/>
       <c r="C270" s="22"/>
@@ -8054,10 +8036,10 @@
       <c r="E270" s="22"/>
       <c r="F270" s="22"/>
       <c r="G270" s="19" t="str">
-        <f>CONCATENATE("M 32 ",G155)</f>
+        <f>CONCATENATE("M 5 ",G38)</f>
       </c>
       <c r="I270" s="19" t="str">
-        <f>CONCATENATE("M 49 ",O163)</f>
+        <f>CONCATENATE("M 50 ",O171)</f>
       </c>
       <c r="J270" s="22"/>
       <c r="K270" s="22"/>
@@ -8065,7 +8047,7 @@
       <c r="M270" s="22"/>
       <c r="N270" s="22"/>
       <c r="O270" s="19" t="str">
-        <f>CONCATENATE("M 48 ",O155)</f>
+        <f>CONCATENATE("M 49 ",O163)</f>
       </c>
     </row>
     <row r="272">
@@ -8130,7 +8112,7 @@
     </row>
     <row r="278">
       <c r="A278" s="19" t="str">
-        <f>CONCATENATE("M 35 ",G179)</f>
+        <f>CONCATENATE("M 38 ",G179)</f>
       </c>
       <c r="B278" s="22"/>
       <c r="C278" s="22"/>
@@ -8138,10 +8120,10 @@
       <c r="E278" s="22"/>
       <c r="F278" s="22"/>
       <c r="G278" s="19" t="str">
-        <f>CONCATENATE("M 34 ",G171)</f>
+        <f>CONCATENATE("M 37 ",G171)</f>
       </c>
       <c r="I278" s="19" t="str">
-        <f>CONCATENATE("M 51 ",O179)</f>
+        <f>CONCATENATE("M 52 ",O187)</f>
       </c>
       <c r="J278" s="22"/>
       <c r="K278" s="22"/>
@@ -8149,7 +8131,7 @@
       <c r="M278" s="22"/>
       <c r="N278" s="22"/>
       <c r="O278" s="19" t="str">
-        <f>CONCATENATE("M 50 ",O171)</f>
+        <f>CONCATENATE("M 51 ",O179)</f>
       </c>
     </row>
     <row r="280">
@@ -8214,7 +8196,7 @@
     </row>
     <row r="286">
       <c r="A286" s="19" t="str">
-        <f>CONCATENATE("M 37 ",G195)</f>
+        <f>CONCATENATE("M 39 ",G187)</f>
       </c>
       <c r="B286" s="22"/>
       <c r="C286" s="22"/>
@@ -8222,7 +8204,7 @@
       <c r="E286" s="22"/>
       <c r="F286" s="22"/>
       <c r="G286" s="19" t="str">
-        <f>CONCATENATE("M 36 ",G187)</f>
+        <f>CONCATENATE("M 9 ",G70)</f>
       </c>
       <c r="I286" s="19" t="str">
         <f>CONCATENATE("M 53 ",O195)</f>
@@ -8233,7 +8215,7 @@
       <c r="M286" s="22"/>
       <c r="N286" s="22"/>
       <c r="O286" s="19" t="str">
-        <f>CONCATENATE("M 52 ",O187)</f>
+        <f>CONCATENATE("M 25 ",O70)</f>
       </c>
     </row>
     <row r="288">
@@ -8298,7 +8280,7 @@
     </row>
     <row r="294">
       <c r="A294" s="19" t="str">
-        <f>CONCATENATE("M 39 ",G211)</f>
+        <f>CONCATENATE("M 41 ",G203)</f>
       </c>
       <c r="B294" s="22"/>
       <c r="C294" s="22"/>
@@ -8306,7 +8288,7 @@
       <c r="E294" s="22"/>
       <c r="F294" s="22"/>
       <c r="G294" s="19" t="str">
-        <f>CONCATENATE("M 38 ",G203)</f>
+        <f>CONCATENATE("M 40 ",G195)</f>
       </c>
       <c r="I294" s="19" t="str">
         <f>CONCATENATE("M 55 ",O211)</f>
@@ -8382,7 +8364,7 @@
     </row>
     <row r="302">
       <c r="A302" s="19" t="str">
-        <f>CONCATENATE("M 41 ",G227)</f>
+        <f>CONCATENATE("M 43 ",G219)</f>
       </c>
       <c r="B302" s="22"/>
       <c r="C302" s="22"/>
@@ -8390,7 +8372,7 @@
       <c r="E302" s="22"/>
       <c r="F302" s="22"/>
       <c r="G302" s="19" t="str">
-        <f>CONCATENATE("M 40 ",G219)</f>
+        <f>CONCATENATE("M 42 ",G211)</f>
       </c>
       <c r="I302" s="19" t="str">
         <f>CONCATENATE("M 57 ",O227)</f>
@@ -8466,7 +8448,7 @@
     </row>
     <row r="310">
       <c r="A310" s="19" t="str">
-        <f>CONCATENATE("M 43 ",G243)</f>
+        <f>CONCATENATE("M 45 ",G235)</f>
       </c>
       <c r="B310" s="22"/>
       <c r="C310" s="22"/>
@@ -8474,7 +8456,7 @@
       <c r="E310" s="22"/>
       <c r="F310" s="22"/>
       <c r="G310" s="19" t="str">
-        <f>CONCATENATE("M 42 ",G235)</f>
+        <f>CONCATENATE("M 44 ",G227)</f>
       </c>
       <c r="I310" s="19" t="str">
         <f>CONCATENATE("M 59 ",O243)</f>
@@ -9174,11 +9156,12 @@
     <mergeCell ref="I90:O90"/>
     <mergeCell ref="A98:G98"/>
     <mergeCell ref="I98:O98"/>
+    <mergeCell ref="A106:G106"/>
     <mergeCell ref="I106:O106"/>
-    <mergeCell ref="A119:G119"/>
-    <mergeCell ref="I119:O119"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="I127:O127"/>
+    <mergeCell ref="A114:G114"/>
+    <mergeCell ref="I114:O114"/>
+    <mergeCell ref="A122:G122"/>
+    <mergeCell ref="I122:O122"/>
     <mergeCell ref="A135:G135"/>
     <mergeCell ref="I135:O135"/>
     <mergeCell ref="A143:G143"/>
@@ -9205,7 +9188,6 @@
     <mergeCell ref="I223:O223"/>
     <mergeCell ref="A231:G231"/>
     <mergeCell ref="I231:O231"/>
-    <mergeCell ref="A239:G239"/>
     <mergeCell ref="I239:O239"/>
     <mergeCell ref="A252:G252"/>
     <mergeCell ref="I252:O252"/>
@@ -9244,7 +9226,7 @@
   <rowBreaks count="9" manualBreakCount="9">
     <brk id="41" max="16383" man="true"/>
     <brk id="81" max="16383" man="true"/>
-    <brk id="118" max="16383" man="true"/>
+    <brk id="121" max="16383" man="true"/>
     <brk id="158" max="16383" man="true"/>
     <brk id="198" max="16383" man="true"/>
     <brk id="238" max="16383" man="true"/>
@@ -9287,35 +9269,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>18</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>28</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -9348,7 +9324,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -9364,7 +9340,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -9401,7 +9377,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -9417,7 +9393,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -9458,7 +9434,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -9472,7 +9448,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -9523,35 +9499,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>50</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>32</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -9584,7 +9554,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -9600,7 +9570,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -9637,7 +9607,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -9653,7 +9623,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -9694,7 +9664,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -9708,7 +9678,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -4158,7 +4158,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>201</v>
+        <v>54</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D19</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="42" ht="270" customHeight="true">
       <c r="A42" s="17">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>'data'!D91</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
@@ -6564,7 +6564,7 @@
         <f>'data'!$B$45</f>
       </c>
       <c r="I116" s="19" t="str">
-        <f>'data'!$B$91</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="J116" s="22"/>
       <c r="K116" s="22"/>
@@ -6981,7 +6981,7 @@
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
       <c r="G161" s="19" t="str">
-        <f>'data'!$B$30</f>
+        <f>'data'!$B$91</f>
       </c>
       <c r="I161" s="19" t="str">
         <f>CONCATENATE("M 21 ",O38)</f>
@@ -7233,7 +7233,7 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$30</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>CONCATENATE("M 24 ",O62)</f>
@@ -9541,7 +9541,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -2950,7 +2950,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>179</v>
+        <v>52</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3936,7 +3936,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>188</v>
+        <v>32</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4067,7 +4067,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4088,7 +4088,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4244,18 +4244,18 @@
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D7</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D8</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -4292,26 +4292,26 @@
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D34</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D14</f>
+        <f>'data'!D80</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D15</f>
+        <f>'data'!D81</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -4332,18 +4332,18 @@
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D18</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D91</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4460,10 +4460,10 @@
     </row>
     <row r="29" ht="270" customHeight="true">
       <c r="A29" s="17">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B29" s="18" t="str">
-        <f>'data'!D34</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
@@ -4508,10 +4508,10 @@
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D39</f>
+        <f>'data'!D49</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
@@ -4532,10 +4532,10 @@
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D42</f>
+        <f>'data'!D87</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4588,10 +4588,10 @@
     </row>
     <row r="45" ht="270" customHeight="true">
       <c r="A45" s="17">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B45" s="18" t="str">
-        <f>'data'!D49</f>
+        <f>'data'!D39</f>
       </c>
     </row>
     <row r="46" ht="270" customHeight="true">
@@ -4797,10 +4797,10 @@
     </row>
     <row r="21" ht="270" customHeight="true">
       <c r="A21" s="17">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>'data'!D70</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
@@ -4869,26 +4869,26 @@
     </row>
     <row r="30" ht="270" customHeight="true">
       <c r="A30" s="17">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="B30" s="18" t="str">
-        <f>'data'!D79</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
       <c r="A31" s="17">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>'data'!D80</f>
+        <f>'data'!D14</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
       <c r="A32" s="17">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>'data'!D81</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
@@ -4909,34 +4909,34 @@
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D84</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
       <c r="A36" s="17">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>'data'!D85</f>
+        <f>'data'!D70</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D86</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D87</f>
+        <f>'data'!D42</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="42" ht="270" customHeight="true">
       <c r="A42" s="17">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>'data'!D19</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
@@ -5377,7 +5377,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$86</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -5637,7 +5637,7 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$59</f>
       </c>
       <c r="I28" s="19" t="str">
         <f>'data'!$B$60</f>
@@ -5648,7 +5648,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$59</f>
       </c>
     </row>
     <row r="30">
@@ -5713,7 +5713,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$79</f>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -5984,7 +5984,7 @@
       <c r="M60" s="22"/>
       <c r="N60" s="22"/>
       <c r="O60" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$85</f>
       </c>
     </row>
     <row r="62">
@@ -6217,7 +6217,7 @@
     </row>
     <row r="84">
       <c r="A84" s="19" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -6225,10 +6225,10 @@
       <c r="E84" s="22"/>
       <c r="F84" s="22"/>
       <c r="G84" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="I84" s="19" t="str">
-        <f>'data'!$B$79</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="J84" s="22"/>
       <c r="K84" s="22"/>
@@ -6320,7 +6320,7 @@
       <c r="M92" s="22"/>
       <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$15</f>
       </c>
     </row>
     <row r="94">
@@ -6393,10 +6393,10 @@
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$49</f>
       </c>
       <c r="I100" s="19" t="str">
-        <f>'data'!$B$85</f>
+        <f>'data'!$B$70</f>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -6404,7 +6404,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="102">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="108">
       <c r="A108" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$15</f>
       </c>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -6477,7 +6477,7 @@
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$87</f>
       </c>
       <c r="I108" s="19" t="str">
         <f>'data'!$B$88</f>
@@ -6488,7 +6488,7 @@
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
-        <f>'data'!$B$87</f>
+        <f>'data'!$B$42</f>
       </c>
     </row>
     <row r="110">
@@ -6564,7 +6564,7 @@
         <f>'data'!$B$45</f>
       </c>
       <c r="I116" s="19" t="str">
-        <f>'data'!$B$19</f>
+        <f>'data'!$B$91</f>
       </c>
       <c r="J116" s="22"/>
       <c r="K116" s="22"/>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="124">
       <c r="A124" s="19" t="str">
-        <f>'data'!$B$49</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -6729,7 +6729,7 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$36</f>
+        <f>'data'!$B$84</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 18 ",O14)</f>
@@ -6897,7 +6897,7 @@
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$80</f>
       </c>
       <c r="I153" s="19" t="str">
         <f>CONCATENATE("M 20 ",O30)</f>
@@ -6981,7 +6981,7 @@
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
       <c r="G161" s="19" t="str">
-        <f>'data'!$B$91</f>
+        <f>'data'!$B$30</f>
       </c>
       <c r="I161" s="19" t="str">
         <f>CONCATENATE("M 21 ",O38)</f>
@@ -7233,7 +7233,7 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$19</f>
+        <f>'data'!$B$30</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>CONCATENATE("M 24 ",O62)</f>
@@ -7328,7 +7328,7 @@
       <c r="M193" s="22"/>
       <c r="N193" s="22"/>
       <c r="O193" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$70</f>
       </c>
     </row>
     <row r="195">
@@ -7401,7 +7401,7 @@
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
-        <f>'data'!$B$36</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="I201" s="19" t="str">
         <f>CONCATENATE("M 27 ",O86)</f>
@@ -7496,7 +7496,7 @@
       <c r="M209" s="22"/>
       <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
-        <f>'data'!$B$80</f>
+        <f>'data'!$B$42</f>
       </c>
     </row>
     <row r="211">
@@ -7664,7 +7664,7 @@
       <c r="M225" s="22"/>
       <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="227">
@@ -9282,7 +9282,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9311,7 +9311,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>32</v>
+        <v>188</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9402,7 +9402,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9423,7 +9423,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9512,7 +9512,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>52</v>
+        <v>179</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9541,7 +9541,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>201</v>
+        <v>54</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -3495,7 +3495,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3594,7 +3594,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4016,7 +4016,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>186</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -4244,50 +4244,50 @@
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D86</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D84</f>
+        <f>'data'!D27</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D9</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D10</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D11</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D83</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -4364,18 +4364,18 @@
     </row>
     <row r="17" ht="270" customHeight="true">
       <c r="A17" s="17">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B17" s="18" t="str">
-        <f>'data'!D22</f>
+        <f>'data'!D60</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
       <c r="A18" s="17">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>'data'!D23</f>
+        <f>'data'!D63</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
@@ -4388,26 +4388,26 @@
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D25</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
       <c r="A21" s="17">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
       <c r="A22" s="17">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>'data'!D27</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
@@ -4709,10 +4709,10 @@
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D60</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -4725,26 +4725,26 @@
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D62</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D63</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D64</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4893,18 +4893,18 @@
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D82</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
       <c r="A34" s="17">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>'data'!D83</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
@@ -5377,7 +5377,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$25</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -5469,7 +5469,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$62</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$54</f>
@@ -5553,7 +5553,7 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$83</f>
       </c>
       <c r="I20" s="19" t="str">
         <f>'data'!$B$57</f>
@@ -5640,7 +5640,7 @@
         <f>'data'!$B$59</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$60</f>
+        <f>'data'!$B$22</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -5724,7 +5724,7 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="I36" s="19" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$23</f>
       </c>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
@@ -5732,7 +5732,7 @@
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$9</f>
       </c>
     </row>
     <row r="38">
@@ -5889,7 +5889,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
-        <f>'data'!$B$23</f>
+        <f>'data'!$B$63</f>
       </c>
       <c r="I52" s="19" t="str">
         <f>'data'!$B$4</f>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="str">
-        <f>'data'!$B$27</f>
+        <f>'data'!$B$84</f>
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -5973,7 +5973,7 @@
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
       <c r="G60" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$86</f>
       </c>
       <c r="I60" s="19" t="str">
         <f>'data'!$B$88</f>
@@ -6309,10 +6309,10 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="I92" s="19" t="str">
-        <f>'data'!$B$82</f>
+        <f>'data'!$B$11</f>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="22"/>
@@ -6385,7 +6385,7 @@
     </row>
     <row r="100">
       <c r="A100" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="124">
       <c r="A124" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$11</f>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -6729,7 +6729,7 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$27</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 18 ",O14)</f>
@@ -6813,7 +6813,7 @@
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$82</f>
       </c>
       <c r="I145" s="19" t="str">
         <f>CONCATENATE("M 19 ",O22)</f>
@@ -7065,7 +7065,7 @@
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
       <c r="G169" s="19" t="str">
-        <f>'data'!$B$22</f>
+        <f>'data'!$B$60</f>
       </c>
       <c r="I169" s="19" t="str">
         <f>CONCATENATE("M 22 ",O46)</f>
@@ -7076,7 +7076,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="171">
@@ -7149,7 +7149,7 @@
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
       <c r="G177" s="19" t="str">
-        <f>'data'!$B$25</f>
+        <f>'data'!$B$64</f>
       </c>
       <c r="I177" s="19" t="str">
         <f>CONCATENATE("M 23 ",O54)</f>
@@ -7485,7 +7485,7 @@
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="I209" s="19" t="str">
         <f>CONCATENATE("M 28 ",O94)</f>
@@ -7580,7 +7580,7 @@
       <c r="M217" s="22"/>
       <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
-        <f>'data'!$B$83</f>
+        <f>'data'!$B$12</f>
       </c>
     </row>
     <row r="219">
@@ -9282,7 +9282,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9311,7 +9311,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9366,7 +9366,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9596,7 +9596,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9653,7 +9653,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9685,7 +9685,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
   <si>
     <t>Number of pools</t>
   </si>
@@ -86,6 +86,9 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
     <t>CLARK</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
@@ -107,6 +113,9 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Michael Lewis</t>
   </si>
   <si>
@@ -116,6 +125,9 @@
     <t>LEWIS</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Nathan Lee</t>
   </si>
   <si>
@@ -125,6 +137,9 @@
     <t>LEE</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Oliver Walker</t>
   </si>
   <si>
@@ -134,102 +149,153 @@
     <t>WALKER</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Paul Hall</t>
   </si>
   <si>
     <t>HALL</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Quentin Allen</t>
   </si>
   <si>
     <t>ALLEN</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Robert Young</t>
   </si>
   <si>
     <t>YOUNG</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Steven Hernandez</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Thomas King</t>
   </si>
   <si>
     <t>KING</t>
   </si>
   <si>
+    <t>K10</t>
+  </si>
+  <si>
     <t>Uriel Wright</t>
   </si>
   <si>
     <t>WRIGHT</t>
   </si>
   <si>
+    <t>K11</t>
+  </si>
+  <si>
     <t>Victor Lopez</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>K12</t>
+  </si>
+  <si>
     <t>William Hill</t>
   </si>
   <si>
     <t>HILL</t>
   </si>
   <si>
+    <t>K13</t>
+  </si>
+  <si>
     <t>Xavier Scott</t>
   </si>
   <si>
     <t>SCOTT</t>
   </si>
   <si>
+    <t>K14</t>
+  </si>
+  <si>
     <t>Yosef Green</t>
   </si>
   <si>
     <t>GREEN</t>
   </si>
   <si>
+    <t>K15</t>
+  </si>
+  <si>
     <t>Zachary Adams</t>
   </si>
   <si>
     <t>ADAMS</t>
   </si>
   <si>
+    <t>K16</t>
+  </si>
+  <si>
     <t>Aaron Thompson</t>
   </si>
   <si>
     <t>THOMPSON</t>
   </si>
   <si>
+    <t>K17</t>
+  </si>
+  <si>
     <t>Benjamin Evans</t>
   </si>
   <si>
     <t>EVANS</t>
   </si>
   <si>
+    <t>K18</t>
+  </si>
+  <si>
     <t>Caleb Wilson</t>
   </si>
   <si>
     <t>WILSON</t>
   </si>
   <si>
+    <t>K19</t>
+  </si>
+  <si>
     <t>Dylan Moore</t>
   </si>
   <si>
     <t>MOORE</t>
   </si>
   <si>
+    <t>K20</t>
+  </si>
+  <si>
     <t>Elijah Taylor</t>
   </si>
   <si>
     <t>TAYLOR</t>
   </si>
   <si>
+    <t>K21</t>
+  </si>
+  <si>
     <t>Finn Anderson</t>
   </si>
   <si>
@@ -239,6 +305,9 @@
     <t>ANDERSON</t>
   </si>
   <si>
+    <t>K22</t>
+  </si>
+  <si>
     <t>Gabriel Thomas</t>
   </si>
   <si>
@@ -248,6 +317,9 @@
     <t>THOMAS</t>
   </si>
   <si>
+    <t>K23</t>
+  </si>
+  <si>
     <t>Hudson Jackson</t>
   </si>
   <si>
@@ -257,6 +329,9 @@
     <t>JACKSON</t>
   </si>
   <si>
+    <t>K24</t>
+  </si>
+  <si>
     <t>Isaac White</t>
   </si>
   <si>
@@ -266,6 +341,9 @@
     <t>WHITE</t>
   </si>
   <si>
+    <t>K25</t>
+  </si>
+  <si>
     <t>Jackson Harris</t>
   </si>
   <si>
@@ -275,117 +353,195 @@
     <t>HARRIS</t>
   </si>
   <si>
+    <t>K26</t>
+  </si>
+  <si>
     <t>Kaden Martin</t>
   </si>
   <si>
     <t>MARTIN</t>
   </si>
   <si>
+    <t>K27</t>
+  </si>
+  <si>
     <t>Liam Thompson</t>
   </si>
   <si>
+    <t>K28</t>
+  </si>
+  <si>
     <t>Mason Martinez</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>K29</t>
+  </si>
+  <si>
     <t>Nolan Clark</t>
   </si>
   <si>
+    <t>K30</t>
+  </si>
+  <si>
     <t>Owen Rodriguez</t>
   </si>
   <si>
+    <t>K31</t>
+  </si>
+  <si>
     <t>Parker Lewis</t>
   </si>
   <si>
+    <t>K32</t>
+  </si>
+  <si>
     <t>Quinn Walker</t>
   </si>
   <si>
+    <t>K33</t>
+  </si>
+  <si>
     <t>Ryan Hall</t>
   </si>
   <si>
+    <t>K34</t>
+  </si>
+  <si>
     <t>Sebastian Allen</t>
   </si>
   <si>
+    <t>K35</t>
+  </si>
+  <si>
     <t>Tristan Young</t>
   </si>
   <si>
+    <t>K36</t>
+  </si>
+  <si>
     <t>Ulysses Hernandez</t>
   </si>
   <si>
+    <t>K37</t>
+  </si>
+  <si>
     <t>Vincent King</t>
   </si>
   <si>
+    <t>K38</t>
+  </si>
+  <si>
     <t>William Wright</t>
   </si>
   <si>
+    <t>K39</t>
+  </si>
+  <si>
     <t>Xavier Lopez</t>
   </si>
   <si>
+    <t>K40</t>
+  </si>
+  <si>
     <t>Yosef Hill</t>
   </si>
   <si>
+    <t>K41</t>
+  </si>
+  <si>
     <t>Arthur Conan</t>
   </si>
   <si>
     <t>CONAN</t>
   </si>
   <si>
+    <t>K42</t>
+  </si>
+  <si>
     <t>Bram Stoker</t>
   </si>
   <si>
     <t>STOKER</t>
   </si>
   <si>
+    <t>K43</t>
+  </si>
+  <si>
     <t>Charles Dickens</t>
   </si>
   <si>
     <t>DICKENS</t>
   </si>
   <si>
+    <t>K44</t>
+  </si>
+  <si>
     <t>Daniel Defoe</t>
   </si>
   <si>
     <t>DEFOE</t>
   </si>
   <si>
+    <t>K45</t>
+  </si>
+  <si>
     <t>Emily Bronte</t>
   </si>
   <si>
     <t>BRONTE</t>
   </si>
   <si>
+    <t>K46</t>
+  </si>
+  <si>
     <t>Fyodor Dostoevsky</t>
   </si>
   <si>
     <t>DOSTOEVSKY</t>
   </si>
   <si>
+    <t>K47</t>
+  </si>
+  <si>
     <t>George Orwell</t>
   </si>
   <si>
     <t>ORWELL</t>
   </si>
   <si>
+    <t>K48</t>
+  </si>
+  <si>
     <t>Herman Melville</t>
   </si>
   <si>
     <t>MELVILLE</t>
   </si>
   <si>
+    <t>K49</t>
+  </si>
+  <si>
     <t>Isaac Asimov</t>
   </si>
   <si>
     <t>ASIMOV</t>
   </si>
   <si>
+    <t>K50</t>
+  </si>
+  <si>
     <t>Jane Austen</t>
   </si>
   <si>
     <t>AUSTEN</t>
   </si>
   <si>
+    <t>K51</t>
+  </si>
+  <si>
     <t>Kurt Vonnegut</t>
   </si>
   <si>
@@ -395,6 +551,9 @@
     <t>VONNEGUT</t>
   </si>
   <si>
+    <t>K52</t>
+  </si>
+  <si>
     <t>Lewis Carroll</t>
   </si>
   <si>
@@ -404,6 +563,9 @@
     <t>CARROLL</t>
   </si>
   <si>
+    <t>K53</t>
+  </si>
+  <si>
     <t>Mary Shelley</t>
   </si>
   <si>
@@ -413,6 +575,9 @@
     <t>SHELLEY</t>
   </si>
   <si>
+    <t>K54</t>
+  </si>
+  <si>
     <t>Nathaniel Hawthorne</t>
   </si>
   <si>
@@ -422,6 +587,9 @@
     <t>HAWTHORNE</t>
   </si>
   <si>
+    <t>K55</t>
+  </si>
+  <si>
     <t>Oscar Wilde</t>
   </si>
   <si>
@@ -431,6 +599,9 @@
     <t>WILDE</t>
   </si>
   <si>
+    <t>K56</t>
+  </si>
+  <si>
     <t>Philip K Dick</t>
   </si>
   <si>
@@ -440,6 +611,9 @@
     <t>DICK</t>
   </si>
   <si>
+    <t>K57</t>
+  </si>
+  <si>
     <t>Quentin Blake</t>
   </si>
   <si>
@@ -449,6 +623,9 @@
     <t>BLAKE</t>
   </si>
   <si>
+    <t>K58</t>
+  </si>
+  <si>
     <t>Ray Bradbury</t>
   </si>
   <si>
@@ -458,6 +635,9 @@
     <t>BRADBURY</t>
   </si>
   <si>
+    <t>K59</t>
+  </si>
+  <si>
     <t>Sylvia Plath</t>
   </si>
   <si>
@@ -467,6 +647,9 @@
     <t>PLATH</t>
   </si>
   <si>
+    <t>K60</t>
+  </si>
+  <si>
     <t>Thomas Hardy</t>
   </si>
   <si>
@@ -476,6 +659,9 @@
     <t>HARDY</t>
   </si>
   <si>
+    <t>K61</t>
+  </si>
+  <si>
     <t>Ursula K Le Guin</t>
   </si>
   <si>
@@ -485,6 +671,9 @@
     <t>LE GUIN</t>
   </si>
   <si>
+    <t>K62</t>
+  </si>
+  <si>
     <t>Virginia Woolf</t>
   </si>
   <si>
@@ -494,6 +683,9 @@
     <t>WOOLF</t>
   </si>
   <si>
+    <t>K63</t>
+  </si>
+  <si>
     <t>William Shakespeare</t>
   </si>
   <si>
@@ -503,6 +695,9 @@
     <t>SHAKESPEARE</t>
   </si>
   <si>
+    <t>K64</t>
+  </si>
+  <si>
     <t>Xavier Herbert</t>
   </si>
   <si>
@@ -512,151 +707,232 @@
     <t>HERBERT</t>
   </si>
   <si>
+    <t>K65</t>
+  </si>
+  <si>
     <t>Yann Martel</t>
   </si>
   <si>
     <t>MARTEL</t>
   </si>
   <si>
+    <t>K66</t>
+  </si>
+  <si>
     <t>Albus Dumbledore</t>
   </si>
   <si>
     <t>DUMBLEDORE</t>
   </si>
   <si>
+    <t>K67</t>
+  </si>
+  <si>
     <t>Bilbo Baggins</t>
   </si>
   <si>
     <t>BAGGINS</t>
   </si>
   <si>
+    <t>K68</t>
+  </si>
+  <si>
     <t>Cersei Lannister</t>
   </si>
   <si>
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>K69</t>
+  </si>
+  <si>
     <t>Daenerys Targaryen</t>
   </si>
   <si>
     <t>TARGARYEN</t>
   </si>
   <si>
+    <t>K70</t>
+  </si>
+  <si>
     <t>Eddard Stark</t>
   </si>
   <si>
     <t>STARK</t>
   </si>
   <si>
+    <t>K71</t>
+  </si>
+  <si>
     <t>Frodo Baggins</t>
   </si>
   <si>
+    <t>K72</t>
+  </si>
+  <si>
     <t>Gandalf The Grey</t>
   </si>
   <si>
     <t>GANDALF</t>
   </si>
   <si>
+    <t>K73</t>
+  </si>
+  <si>
     <t>Hermione Granger</t>
   </si>
   <si>
     <t>GRANGER</t>
   </si>
   <si>
+    <t>K74</t>
+  </si>
+  <si>
     <t>Inigo Montoya</t>
   </si>
   <si>
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>K75</t>
+  </si>
+  <si>
     <t>Jon Snow</t>
   </si>
   <si>
     <t>SNOW</t>
   </si>
   <si>
+    <t>K76</t>
+  </si>
+  <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
     <t>EVERDEEN</t>
   </si>
   <si>
+    <t>K77</t>
+  </si>
+  <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
     <t>GREENLEAF</t>
   </si>
   <si>
+    <t>K78</t>
+  </si>
+  <si>
     <t>Moby Dick</t>
   </si>
   <si>
+    <t>K79</t>
+  </si>
+  <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
     <t>LONGBOTTOM</t>
   </si>
   <si>
+    <t>K80</t>
+  </si>
+  <si>
     <t>Othello</t>
   </si>
   <si>
     <t>OTHELLO</t>
   </si>
   <si>
+    <t>K81</t>
+  </si>
+  <si>
     <t>Petyr Baelish</t>
   </si>
   <si>
     <t>BAELISH</t>
   </si>
   <si>
+    <t>K82</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
     <t>QUIRRELL</t>
   </si>
   <si>
+    <t>K83</t>
+  </si>
+  <si>
     <t>Ron Weasley</t>
   </si>
   <si>
     <t>WEASLEY</t>
   </si>
   <si>
+    <t>K84</t>
+  </si>
+  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
     <t>GAMGEE</t>
   </si>
   <si>
+    <t>K85</t>
+  </si>
+  <si>
     <t>Tyrion Lannister</t>
   </si>
   <si>
+    <t>K86</t>
+  </si>
+  <si>
     <t>Ulysses</t>
   </si>
   <si>
     <t>ULYSSES</t>
   </si>
   <si>
+    <t>K87</t>
+  </si>
+  <si>
     <t>Voldemort</t>
   </si>
   <si>
     <t>VOLDEMORT</t>
   </si>
   <si>
+    <t>K88</t>
+  </si>
+  <si>
     <t>Willy Wonka</t>
   </si>
   <si>
     <t>WONKA</t>
   </si>
   <si>
+    <t>K89</t>
+  </si>
+  <si>
     <t>Xaro Xhoan Daxos</t>
   </si>
   <si>
     <t>DAXOS</t>
   </si>
   <si>
+    <t>K90</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
     <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>K91</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1526,19 +1802,25 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1546,13 +1828,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -1560,13 +1845,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1574,13 +1862,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -1588,13 +1879,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -1602,13 +1896,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1616,13 +1913,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -1630,13 +1930,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -1644,13 +1947,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -1658,13 +1964,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -1672,13 +1981,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -1686,13 +1998,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -1700,13 +2015,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1714,13 +2032,16 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1728,13 +2049,16 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -1742,13 +2066,16 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -1756,13 +2083,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -1770,13 +2100,16 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -1784,13 +2117,16 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22">
@@ -1798,13 +2134,16 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="23">
@@ -1812,13 +2151,16 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -1826,13 +2168,16 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="25">
@@ -1840,13 +2185,16 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>91</v>
+      </c>
+      <c r="E25" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26">
@@ -1854,13 +2202,16 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+      <c r="E26" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="27">
@@ -1868,13 +2219,16 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1882,13 +2236,16 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>103</v>
+      </c>
+      <c r="E28" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="29">
@@ -1896,13 +2253,16 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>106</v>
+      </c>
+      <c r="E29" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="30">
@@ -1910,13 +2270,16 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>71</v>
+      </c>
+      <c r="E30" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="31">
@@ -1924,13 +2287,16 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="32">
@@ -1938,13 +2304,16 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="33">
@@ -1952,13 +2321,16 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="34">
@@ -1966,13 +2338,16 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="E34" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -1980,13 +2355,16 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="E35" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="36">
@@ -1994,13 +2372,16 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="E36" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="37">
@@ -2008,13 +2389,16 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="E37" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="38">
@@ -2022,13 +2406,16 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="E38" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="39">
@@ -2036,13 +2423,16 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="40">
@@ -2050,13 +2440,16 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="E40" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="41">
@@ -2064,13 +2457,16 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="E41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="42">
@@ -2078,13 +2474,16 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="E42" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="43">
@@ -2092,13 +2491,16 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>59</v>
+      </c>
+      <c r="E43" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="44">
@@ -2106,13 +2508,16 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>138</v>
+      </c>
+      <c r="E44" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="45">
@@ -2120,13 +2525,16 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>141</v>
+      </c>
+      <c r="E45" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="46">
@@ -2134,13 +2542,16 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>144</v>
+      </c>
+      <c r="E46" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="47">
@@ -2148,13 +2559,16 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>147</v>
+      </c>
+      <c r="E47" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="48">
@@ -2162,13 +2576,16 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>150</v>
+      </c>
+      <c r="E48" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="49">
@@ -2176,13 +2593,16 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>153</v>
+      </c>
+      <c r="E49" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="50">
@@ -2190,13 +2610,16 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>156</v>
+      </c>
+      <c r="E50" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="51">
@@ -2204,13 +2627,16 @@
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>159</v>
+      </c>
+      <c r="E51" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="52">
@@ -2218,13 +2644,16 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C52" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>162</v>
+      </c>
+      <c r="E52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="53">
@@ -2232,13 +2661,16 @@
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>165</v>
+      </c>
+      <c r="E53" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="54">
@@ -2246,13 +2678,16 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="D54" t="s">
-        <v>117</v>
+        <v>169</v>
+      </c>
+      <c r="E54" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="55">
@@ -2260,13 +2695,16 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D55" t="s">
-        <v>120</v>
+        <v>173</v>
+      </c>
+      <c r="E55" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="56">
@@ -2274,13 +2712,16 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>123</v>
+        <v>177</v>
+      </c>
+      <c r="E56" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="57">
@@ -2288,13 +2729,16 @@
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>181</v>
+      </c>
+      <c r="E57" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="58">
@@ -2302,13 +2746,16 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>185</v>
+      </c>
+      <c r="E58" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="59">
@@ -2316,13 +2763,16 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D59" t="s">
-        <v>132</v>
+        <v>189</v>
+      </c>
+      <c r="E59" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="60">
@@ -2330,13 +2780,16 @@
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>193</v>
+      </c>
+      <c r="E60" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="61">
@@ -2344,13 +2797,16 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>197</v>
+      </c>
+      <c r="E61" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="62">
@@ -2358,13 +2814,16 @@
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="C62" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="D62" t="s">
-        <v>141</v>
+        <v>201</v>
+      </c>
+      <c r="E62" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="63">
@@ -2372,13 +2831,16 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>205</v>
+      </c>
+      <c r="E63" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="64">
@@ -2386,13 +2848,16 @@
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>209</v>
+      </c>
+      <c r="E64" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="65">
@@ -2400,13 +2865,16 @@
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>213</v>
+      </c>
+      <c r="E65" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="66">
@@ -2414,13 +2882,16 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="C66" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>217</v>
+      </c>
+      <c r="E66" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="67">
@@ -2428,13 +2899,16 @@
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="D67" t="s">
-        <v>156</v>
+        <v>221</v>
+      </c>
+      <c r="E67" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="68">
@@ -2442,13 +2916,16 @@
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>158</v>
+        <v>224</v>
+      </c>
+      <c r="E68" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="69">
@@ -2456,13 +2933,16 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>227</v>
+      </c>
+      <c r="E69" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="70">
@@ -2470,13 +2950,16 @@
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>162</v>
+        <v>230</v>
+      </c>
+      <c r="E70" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="71">
@@ -2484,13 +2967,16 @@
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>164</v>
+        <v>233</v>
+      </c>
+      <c r="E71" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="72">
@@ -2498,13 +2984,16 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D72" t="s">
-        <v>166</v>
+        <v>236</v>
+      </c>
+      <c r="E72" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="73">
@@ -2512,13 +3001,16 @@
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
-        <v>168</v>
+        <v>239</v>
+      </c>
+      <c r="E73" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="74">
@@ -2526,13 +3018,16 @@
         <v>71</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D74" t="s">
-        <v>162</v>
+        <v>230</v>
+      </c>
+      <c r="E74" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="75">
@@ -2540,13 +3035,16 @@
         <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>243</v>
       </c>
       <c r="C75" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>244</v>
+      </c>
+      <c r="E75" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="76">
@@ -2554,13 +3052,16 @@
         <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="C76" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
+        <v>247</v>
+      </c>
+      <c r="E76" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="77">
@@ -2568,13 +3069,16 @@
         <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
+        <v>250</v>
+      </c>
+      <c r="E77" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="78">
@@ -2582,13 +3086,16 @@
         <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>253</v>
+      </c>
+      <c r="E78" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="79">
@@ -2596,13 +3103,16 @@
         <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="C79" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>256</v>
+      </c>
+      <c r="E79" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="80">
@@ -2610,13 +3120,16 @@
         <v>77</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="C80" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D80" t="s">
-        <v>181</v>
+        <v>259</v>
+      </c>
+      <c r="E80" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="81">
@@ -2624,13 +3137,16 @@
         <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D81" t="s">
-        <v>132</v>
+        <v>189</v>
+      </c>
+      <c r="E81" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -2638,13 +3154,16 @@
         <v>79</v>
       </c>
       <c r="B82" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D82" t="s">
-        <v>184</v>
+        <v>264</v>
+      </c>
+      <c r="E82" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="83">
@@ -2652,13 +3171,16 @@
         <v>80</v>
       </c>
       <c r="B83" t="s">
-        <v>185</v>
+        <v>266</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="D83" t="s">
-        <v>186</v>
+        <v>267</v>
+      </c>
+      <c r="E83" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="84">
@@ -2666,13 +3188,16 @@
         <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>269</v>
       </c>
       <c r="C84" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D84" t="s">
-        <v>188</v>
+        <v>270</v>
+      </c>
+      <c r="E84" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="85">
@@ -2680,13 +3205,16 @@
         <v>82</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="D85" t="s">
-        <v>190</v>
+        <v>273</v>
+      </c>
+      <c r="E85" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="86">
@@ -2694,13 +3222,16 @@
         <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="C86" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="D86" t="s">
-        <v>192</v>
+        <v>276</v>
+      </c>
+      <c r="E86" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="87">
@@ -2708,13 +3239,16 @@
         <v>84</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>278</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="D87" t="s">
-        <v>194</v>
+        <v>279</v>
+      </c>
+      <c r="E87" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="88">
@@ -2722,13 +3256,16 @@
         <v>85</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>281</v>
       </c>
       <c r="C88" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="D88" t="s">
-        <v>164</v>
+        <v>233</v>
+      </c>
+      <c r="E88" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="89">
@@ -2736,13 +3273,16 @@
         <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>283</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="D89" t="s">
-        <v>197</v>
+        <v>284</v>
+      </c>
+      <c r="E89" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="90">
@@ -2750,13 +3290,16 @@
         <v>87</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="D90" t="s">
-        <v>199</v>
+        <v>287</v>
+      </c>
+      <c r="E90" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="91">
@@ -2764,13 +3307,16 @@
         <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>289</v>
       </c>
       <c r="C91" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="D91" t="s">
-        <v>201</v>
+        <v>290</v>
+      </c>
+      <c r="E91" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="92">
@@ -2778,13 +3324,16 @@
         <v>89</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="D92" t="s">
-        <v>203</v>
+        <v>293</v>
+      </c>
+      <c r="E92" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="93">
@@ -2792,13 +3341,16 @@
         <v>90</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>295</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>296</v>
+      </c>
+      <c r="E93" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2838,7 +3390,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -2849,7 +3401,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -2878,7 +3430,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -2899,7 +3451,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -2915,7 +3467,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -2933,7 +3485,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -2950,7 +3502,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -2969,7 +3521,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -2990,7 +3542,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3008,7 +3560,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3022,7 +3574,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3070,7 +3622,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -3084,7 +3636,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3101,7 +3653,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3121,7 +3673,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3142,7 +3694,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3158,7 +3710,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3176,7 +3728,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3193,7 +3745,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3212,7 +3764,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3233,7 +3785,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3251,7 +3803,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3265,7 +3817,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3311,7 +3863,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -3322,7 +3874,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3351,7 +3903,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3372,7 +3924,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3388,7 +3940,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3406,7 +3958,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3423,7 +3975,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3442,7 +3994,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3463,7 +4015,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3481,7 +4033,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3495,7 +4047,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3543,7 +4095,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
@@ -3557,7 +4109,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3574,7 +4126,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3594,7 +4146,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3615,7 +4167,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3631,7 +4183,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3649,7 +4201,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3666,7 +4218,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3685,7 +4237,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3706,7 +4258,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3724,7 +4276,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3738,7 +4290,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3784,7 +4336,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
@@ -3795,7 +4347,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3824,7 +4376,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3845,7 +4397,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3861,7 +4413,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3879,7 +4431,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3896,7 +4448,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>177</v>
+        <v>253</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3915,7 +4467,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3936,7 +4488,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3954,7 +4506,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3968,7 +4520,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4016,7 +4568,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -4030,7 +4582,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4047,7 +4599,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4067,7 +4619,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4088,7 +4640,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4104,7 +4656,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4122,7 +4674,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4139,7 +4691,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4158,7 +4710,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>201</v>
+        <v>290</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4179,7 +4731,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4197,7 +4749,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>205</v>
+        <v>296</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4211,7 +4763,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4235,368 +4787,368 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>0</v>
+      <c r="A1" s="17" t="str">
+        <f>'data'!$E$3</f>
       </c>
       <c r="B1" s="18" t="str">
         <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>23</v>
+      <c r="A2" s="17" t="str">
+        <f>'data'!$E$26</f>
       </c>
       <c r="B2" s="18" t="str">
         <f>'data'!D26</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>24</v>
+      <c r="A3" s="17" t="str">
+        <f>'data'!$E$27</f>
       </c>
       <c r="B3" s="18" t="str">
         <f>'data'!D27</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>59</v>
+      <c r="A4" s="17" t="str">
+        <f>'data'!$E$62</f>
       </c>
       <c r="B4" s="18" t="str">
         <f>'data'!D62</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>22</v>
+      <c r="A5" s="17" t="str">
+        <f>'data'!$E$25</f>
       </c>
       <c r="B5" s="18" t="str">
         <f>'data'!D25</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>79</v>
+      <c r="A6" s="17" t="str">
+        <f>'data'!$E$82</f>
       </c>
       <c r="B6" s="18" t="str">
         <f>'data'!D82</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>80</v>
+      <c r="A7" s="17" t="str">
+        <f>'data'!$E$83</f>
       </c>
       <c r="B7" s="18" t="str">
         <f>'data'!D83</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>31</v>
+      <c r="A8" s="17" t="str">
+        <f>'data'!$E$34</f>
       </c>
       <c r="B8" s="18" t="str">
         <f>'data'!D34</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>77</v>
+      <c r="A9" s="17" t="str">
+        <f>'data'!$E$80</f>
       </c>
       <c r="B9" s="18" t="str">
         <f>'data'!D80</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>78</v>
+      <c r="A10" s="17" t="str">
+        <f>'data'!$E$81</f>
       </c>
       <c r="B10" s="18" t="str">
         <f>'data'!D81</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>13</v>
+      <c r="A11" s="17" t="str">
+        <f>'data'!$E$16</f>
       </c>
       <c r="B11" s="18" t="str">
         <f>'data'!D16</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>14</v>
+      <c r="A12" s="17" t="str">
+        <f>'data'!$E$17</f>
       </c>
       <c r="B12" s="18" t="str">
         <f>'data'!D17</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="17">
-        <v>76</v>
+      <c r="A13" s="17" t="str">
+        <f>'data'!$E$79</f>
       </c>
       <c r="B13" s="18" t="str">
         <f>'data'!D79</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="17">
-        <v>16</v>
+      <c r="A14" s="17" t="str">
+        <f>'data'!$E$19</f>
       </c>
       <c r="B14" s="18" t="str">
         <f>'data'!D19</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="17">
-        <v>17</v>
+      <c r="A15" s="17" t="str">
+        <f>'data'!$E$20</f>
       </c>
       <c r="B15" s="18" t="str">
         <f>'data'!D20</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="17">
-        <v>18</v>
+      <c r="A16" s="17" t="str">
+        <f>'data'!$E$21</f>
       </c>
       <c r="B16" s="18" t="str">
         <f>'data'!D21</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="17">
-        <v>57</v>
+      <c r="A17" s="17" t="str">
+        <f>'data'!$E$60</f>
       </c>
       <c r="B17" s="18" t="str">
         <f>'data'!D60</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="17">
-        <v>60</v>
+      <c r="A18" s="17" t="str">
+        <f>'data'!$E$63</f>
       </c>
       <c r="B18" s="18" t="str">
         <f>'data'!D63</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="17">
-        <v>21</v>
+      <c r="A19" s="17" t="str">
+        <f>'data'!$E$24</f>
       </c>
       <c r="B19" s="18" t="str">
         <f>'data'!D24</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="17">
-        <v>61</v>
+      <c r="A20" s="17" t="str">
+        <f>'data'!$E$64</f>
       </c>
       <c r="B20" s="18" t="str">
         <f>'data'!D64</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="17">
-        <v>83</v>
+      <c r="A21" s="17" t="str">
+        <f>'data'!$E$86</f>
       </c>
       <c r="B21" s="18" t="str">
         <f>'data'!D86</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="17">
-        <v>81</v>
+      <c r="A22" s="17" t="str">
+        <f>'data'!$E$84</f>
       </c>
       <c r="B22" s="18" t="str">
         <f>'data'!D84</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="17">
-        <v>25</v>
+      <c r="A23" s="17" t="str">
+        <f>'data'!$E$28</f>
       </c>
       <c r="B23" s="18" t="str">
         <f>'data'!D28</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="17">
-        <v>26</v>
+      <c r="A24" s="17" t="str">
+        <f>'data'!$E$29</f>
       </c>
       <c r="B24" s="18" t="str">
         <f>'data'!D29</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="17">
-        <v>27</v>
+      <c r="A25" s="17" t="str">
+        <f>'data'!$E$30</f>
       </c>
       <c r="B25" s="18" t="str">
         <f>'data'!D30</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="17">
-        <v>28</v>
+      <c r="A26" s="17" t="str">
+        <f>'data'!$E$31</f>
       </c>
       <c r="B26" s="18" t="str">
         <f>'data'!D31</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="17">
-        <v>29</v>
+      <c r="A27" s="17" t="str">
+        <f>'data'!$E$32</f>
       </c>
       <c r="B27" s="18" t="str">
         <f>'data'!D32</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="17">
-        <v>30</v>
+      <c r="A28" s="17" t="str">
+        <f>'data'!$E$33</f>
       </c>
       <c r="B28" s="18" t="str">
         <f>'data'!D33</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="17">
-        <v>10</v>
+      <c r="A29" s="17" t="str">
+        <f>'data'!$E$13</f>
       </c>
       <c r="B29" s="18" t="str">
         <f>'data'!D13</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="17">
-        <v>32</v>
+      <c r="A30" s="17" t="str">
+        <f>'data'!$E$35</f>
       </c>
       <c r="B30" s="18" t="str">
         <f>'data'!D35</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="17">
-        <v>33</v>
+      <c r="A31" s="17" t="str">
+        <f>'data'!$E$36</f>
       </c>
       <c r="B31" s="18" t="str">
         <f>'data'!D36</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="17">
-        <v>34</v>
+      <c r="A32" s="17" t="str">
+        <f>'data'!$E$37</f>
       </c>
       <c r="B32" s="18" t="str">
         <f>'data'!D37</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="17">
-        <v>3</v>
+      <c r="A33" s="17" t="str">
+        <f>'data'!$E$6</f>
       </c>
       <c r="B33" s="18" t="str">
         <f>'data'!D6</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="17">
-        <v>35</v>
+      <c r="A34" s="17" t="str">
+        <f>'data'!$E$38</f>
       </c>
       <c r="B34" s="18" t="str">
         <f>'data'!D38</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="17">
-        <v>46</v>
+      <c r="A35" s="17" t="str">
+        <f>'data'!$E$49</f>
       </c>
       <c r="B35" s="18" t="str">
         <f>'data'!D49</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="17">
-        <v>37</v>
+      <c r="A36" s="17" t="str">
+        <f>'data'!$E$40</f>
       </c>
       <c r="B36" s="18" t="str">
         <f>'data'!D40</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="17">
-        <v>38</v>
+      <c r="A37" s="17" t="str">
+        <f>'data'!$E$41</f>
       </c>
       <c r="B37" s="18" t="str">
         <f>'data'!D41</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="17">
-        <v>84</v>
+      <c r="A38" s="17" t="str">
+        <f>'data'!$E$87</f>
       </c>
       <c r="B38" s="18" t="str">
         <f>'data'!D87</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="17">
-        <v>40</v>
+      <c r="A39" s="17" t="str">
+        <f>'data'!$E$43</f>
       </c>
       <c r="B39" s="18" t="str">
         <f>'data'!D43</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="17">
-        <v>41</v>
+      <c r="A40" s="17" t="str">
+        <f>'data'!$E$44</f>
       </c>
       <c r="B40" s="18" t="str">
         <f>'data'!D44</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="17">
-        <v>42</v>
+      <c r="A41" s="17" t="str">
+        <f>'data'!$E$45</f>
       </c>
       <c r="B41" s="18" t="str">
         <f>'data'!D45</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="17">
-        <v>43</v>
+      <c r="A42" s="17" t="str">
+        <f>'data'!$E$46</f>
       </c>
       <c r="B42" s="18" t="str">
         <f>'data'!D46</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="17">
-        <v>44</v>
+      <c r="A43" s="17" t="str">
+        <f>'data'!$E$47</f>
       </c>
       <c r="B43" s="18" t="str">
         <f>'data'!D47</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="17">
-        <v>45</v>
+      <c r="A44" s="17" t="str">
+        <f>'data'!$E$48</f>
       </c>
       <c r="B44" s="18" t="str">
         <f>'data'!D48</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="17">
-        <v>36</v>
+      <c r="A45" s="17" t="str">
+        <f>'data'!$E$39</f>
       </c>
       <c r="B45" s="18" t="str">
         <f>'data'!D39</f>
       </c>
     </row>
     <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="17">
-        <v>47</v>
+      <c r="A46" s="17" t="str">
+        <f>'data'!$E$50</f>
       </c>
       <c r="B46" s="18" t="str">
         <f>'data'!D50</f>
@@ -4636,360 +5188,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>48</v>
+      <c r="A1" s="17" t="str">
+        <f>'data'!$E$51</f>
       </c>
       <c r="B1" s="18" t="str">
         <f>'data'!D51</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>49</v>
+      <c r="A2" s="17" t="str">
+        <f>'data'!$E$52</f>
       </c>
       <c r="B2" s="18" t="str">
         <f>'data'!D52</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>50</v>
+      <c r="A3" s="17" t="str">
+        <f>'data'!$E$53</f>
       </c>
       <c r="B3" s="18" t="str">
         <f>'data'!D53</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>51</v>
+      <c r="A4" s="17" t="str">
+        <f>'data'!$E$54</f>
       </c>
       <c r="B4" s="18" t="str">
         <f>'data'!D54</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>52</v>
+      <c r="A5" s="17" t="str">
+        <f>'data'!$E$55</f>
       </c>
       <c r="B5" s="18" t="str">
         <f>'data'!D55</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>53</v>
+      <c r="A6" s="17" t="str">
+        <f>'data'!$E$56</f>
       </c>
       <c r="B6" s="18" t="str">
         <f>'data'!D56</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>54</v>
+      <c r="A7" s="17" t="str">
+        <f>'data'!$E$57</f>
       </c>
       <c r="B7" s="18" t="str">
         <f>'data'!D57</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>55</v>
+      <c r="A8" s="17" t="str">
+        <f>'data'!$E$58</f>
       </c>
       <c r="B8" s="18" t="str">
         <f>'data'!D58</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>56</v>
+      <c r="A9" s="17" t="str">
+        <f>'data'!$E$59</f>
       </c>
       <c r="B9" s="18" t="str">
         <f>'data'!D59</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>19</v>
+      <c r="A10" s="17" t="str">
+        <f>'data'!$E$22</f>
       </c>
       <c r="B10" s="18" t="str">
         <f>'data'!D22</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>58</v>
+      <c r="A11" s="17" t="str">
+        <f>'data'!$E$61</f>
       </c>
       <c r="B11" s="18" t="str">
         <f>'data'!D61</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>6</v>
+      <c r="A12" s="17" t="str">
+        <f>'data'!$E$9</f>
       </c>
       <c r="B12" s="18" t="str">
         <f>'data'!D9</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="17">
-        <v>20</v>
+      <c r="A13" s="17" t="str">
+        <f>'data'!$E$23</f>
       </c>
       <c r="B13" s="18" t="str">
         <f>'data'!D23</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="17">
-        <v>7</v>
+      <c r="A14" s="17" t="str">
+        <f>'data'!$E$10</f>
       </c>
       <c r="B14" s="18" t="str">
         <f>'data'!D10</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="17">
-        <v>62</v>
+      <c r="A15" s="17" t="str">
+        <f>'data'!$E$65</f>
       </c>
       <c r="B15" s="18" t="str">
         <f>'data'!D65</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="17">
-        <v>63</v>
+      <c r="A16" s="17" t="str">
+        <f>'data'!$E$66</f>
       </c>
       <c r="B16" s="18" t="str">
         <f>'data'!D66</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="17">
-        <v>64</v>
+      <c r="A17" s="17" t="str">
+        <f>'data'!$E$67</f>
       </c>
       <c r="B17" s="18" t="str">
         <f>'data'!D67</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="17">
-        <v>65</v>
+      <c r="A18" s="17" t="str">
+        <f>'data'!$E$68</f>
       </c>
       <c r="B18" s="18" t="str">
         <f>'data'!D68</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="17">
-        <v>1</v>
+      <c r="A19" s="17" t="str">
+        <f>'data'!$E$4</f>
       </c>
       <c r="B19" s="18" t="str">
         <f>'data'!D4</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="17">
-        <v>66</v>
+      <c r="A20" s="17" t="str">
+        <f>'data'!$E$69</f>
       </c>
       <c r="B20" s="18" t="str">
         <f>'data'!D69</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="17">
-        <v>82</v>
+      <c r="A21" s="17" t="str">
+        <f>'data'!$E$85</f>
       </c>
       <c r="B21" s="18" t="str">
         <f>'data'!D85</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="17">
-        <v>68</v>
+      <c r="A22" s="17" t="str">
+        <f>'data'!$E$71</f>
       </c>
       <c r="B22" s="18" t="str">
         <f>'data'!D71</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="17">
-        <v>69</v>
+      <c r="A23" s="17" t="str">
+        <f>'data'!$E$72</f>
       </c>
       <c r="B23" s="18" t="str">
         <f>'data'!D72</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="17">
-        <v>70</v>
+      <c r="A24" s="17" t="str">
+        <f>'data'!$E$73</f>
       </c>
       <c r="B24" s="18" t="str">
         <f>'data'!D73</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="17">
-        <v>71</v>
+      <c r="A25" s="17" t="str">
+        <f>'data'!$E$74</f>
       </c>
       <c r="B25" s="18" t="str">
         <f>'data'!D74</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="17">
-        <v>72</v>
+      <c r="A26" s="17" t="str">
+        <f>'data'!$E$75</f>
       </c>
       <c r="B26" s="18" t="str">
         <f>'data'!D75</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="17">
-        <v>73</v>
+      <c r="A27" s="17" t="str">
+        <f>'data'!$E$76</f>
       </c>
       <c r="B27" s="18" t="str">
         <f>'data'!D76</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="17">
-        <v>74</v>
+      <c r="A28" s="17" t="str">
+        <f>'data'!$E$77</f>
       </c>
       <c r="B28" s="18" t="str">
         <f>'data'!D77</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="17">
-        <v>75</v>
+      <c r="A29" s="17" t="str">
+        <f>'data'!$E$78</f>
       </c>
       <c r="B29" s="18" t="str">
         <f>'data'!D78</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="17">
-        <v>15</v>
+      <c r="A30" s="17" t="str">
+        <f>'data'!$E$18</f>
       </c>
       <c r="B30" s="18" t="str">
         <f>'data'!D18</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="17">
-        <v>11</v>
+      <c r="A31" s="17" t="str">
+        <f>'data'!$E$14</f>
       </c>
       <c r="B31" s="18" t="str">
         <f>'data'!D14</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="17">
-        <v>12</v>
+      <c r="A32" s="17" t="str">
+        <f>'data'!$E$15</f>
       </c>
       <c r="B32" s="18" t="str">
         <f>'data'!D15</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="17">
-        <v>8</v>
+      <c r="A33" s="17" t="str">
+        <f>'data'!$E$11</f>
       </c>
       <c r="B33" s="18" t="str">
         <f>'data'!D11</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="17">
-        <v>9</v>
+      <c r="A34" s="17" t="str">
+        <f>'data'!$E$12</f>
       </c>
       <c r="B34" s="18" t="str">
         <f>'data'!D12</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="17">
-        <v>5</v>
+      <c r="A35" s="17" t="str">
+        <f>'data'!$E$8</f>
       </c>
       <c r="B35" s="18" t="str">
         <f>'data'!D8</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="17">
-        <v>67</v>
+      <c r="A36" s="17" t="str">
+        <f>'data'!$E$70</f>
       </c>
       <c r="B36" s="18" t="str">
         <f>'data'!D70</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="17">
-        <v>4</v>
+      <c r="A37" s="17" t="str">
+        <f>'data'!$E$7</f>
       </c>
       <c r="B37" s="18" t="str">
         <f>'data'!D7</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="17">
-        <v>39</v>
+      <c r="A38" s="17" t="str">
+        <f>'data'!$E$42</f>
       </c>
       <c r="B38" s="18" t="str">
         <f>'data'!D42</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="17">
-        <v>85</v>
+      <c r="A39" s="17" t="str">
+        <f>'data'!$E$88</f>
       </c>
       <c r="B39" s="18" t="str">
         <f>'data'!D88</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="17">
-        <v>86</v>
+      <c r="A40" s="17" t="str">
+        <f>'data'!$E$89</f>
       </c>
       <c r="B40" s="18" t="str">
         <f>'data'!D89</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="17">
-        <v>87</v>
+      <c r="A41" s="17" t="str">
+        <f>'data'!$E$90</f>
       </c>
       <c r="B41" s="18" t="str">
         <f>'data'!D90</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="17">
-        <v>88</v>
+      <c r="A42" s="17" t="str">
+        <f>'data'!$E$91</f>
       </c>
       <c r="B42" s="18" t="str">
         <f>'data'!D91</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="17">
-        <v>89</v>
+      <c r="A43" s="17" t="str">
+        <f>'data'!$E$92</f>
       </c>
       <c r="B43" s="18" t="str">
         <f>'data'!D92</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="17">
-        <v>90</v>
+      <c r="A44" s="17" t="str">
+        <f>'data'!$E$93</f>
       </c>
       <c r="B44" s="18" t="str">
         <f>'data'!D93</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="17">
-        <v>2</v>
+      <c r="A45" s="17" t="str">
+        <f>'data'!$E$5</f>
       </c>
       <c r="B45" s="18" t="str">
         <f>'data'!D5</f>
@@ -5220,7 +5772,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>303</v>
+        <v>395</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -5231,7 +5783,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>304</v>
+        <v>396</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -5241,7 +5793,7 @@
     </row>
     <row r="15">
       <c r="E15" s="25" t="s">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
@@ -5251,7 +5803,7 @@
     </row>
     <row r="16">
       <c r="E16" s="25" t="s">
-        <v>306</v>
+        <v>398</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
@@ -5261,7 +5813,7 @@
     </row>
     <row r="17">
       <c r="E17" s="25" t="s">
-        <v>307</v>
+        <v>399</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
@@ -5271,7 +5823,7 @@
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -5281,7 +5833,7 @@
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>309</v>
+        <v>401</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -5317,7 +5869,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>206</v>
+        <v>298</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5326,7 +5878,7 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>207</v>
+        <v>299</v>
       </c>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
@@ -5337,7 +5889,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>208</v>
+        <v>300</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -5346,7 +5898,7 @@
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="I2" s="11" t="s">
-        <v>214</v>
+        <v>306</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
@@ -5357,22 +5909,22 @@
     </row>
     <row r="3">
       <c r="A3" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O3" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4">
@@ -5401,27 +5953,27 @@
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G6" s="23"/>
       <c r="N6" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O6" s="23"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G7" s="23"/>
       <c r="N7" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O7" s="23"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>215</v>
+        <v>307</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -5430,7 +5982,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="I10" s="11" t="s">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -5441,22 +5993,22 @@
     </row>
     <row r="11">
       <c r="A11" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12">
@@ -5485,27 +6037,27 @@
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G14" s="23"/>
       <c r="N14" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O14" s="23"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G15" s="23"/>
       <c r="N15" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O15" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>217</v>
+        <v>309</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5514,7 +6066,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="I18" s="11" t="s">
-        <v>218</v>
+        <v>310</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -5525,22 +6077,22 @@
     </row>
     <row r="19">
       <c r="A19" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L19" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20">
@@ -5569,27 +6121,27 @@
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G22" s="23"/>
       <c r="N22" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O22" s="23"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G23" s="23"/>
       <c r="N23" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O23" s="23"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
-        <v>219</v>
+        <v>311</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -5598,7 +6150,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="I26" s="11" t="s">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -5609,22 +6161,22 @@
     </row>
     <row r="27">
       <c r="A27" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28">
@@ -5653,27 +6205,27 @@
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G30" s="23"/>
       <c r="N30" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O30" s="23"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G31" s="23"/>
       <c r="N31" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O31" s="23"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
-        <v>221</v>
+        <v>313</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -5682,7 +6234,7 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="I34" s="11" t="s">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -5693,22 +6245,22 @@
     </row>
     <row r="35">
       <c r="A35" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L35" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36">
@@ -5737,27 +6289,27 @@
     </row>
     <row r="38">
       <c r="F38" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G38" s="23"/>
       <c r="N38" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O38" s="23"/>
     </row>
     <row r="39">
       <c r="F39" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G39" s="23"/>
       <c r="N39" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O39" s="23"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
-        <v>223</v>
+        <v>315</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -5766,7 +6318,7 @@
       <c r="F42" s="11"/>
       <c r="G42" s="11"/>
       <c r="I42" s="11" t="s">
-        <v>224</v>
+        <v>316</v>
       </c>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
@@ -5777,22 +6329,22 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44">
@@ -5821,27 +6373,27 @@
     </row>
     <row r="46">
       <c r="F46" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G46" s="23"/>
       <c r="N46" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O46" s="23"/>
     </row>
     <row r="47">
       <c r="F47" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G47" s="23"/>
       <c r="N47" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O47" s="23"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="s">
-        <v>225</v>
+        <v>317</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -5850,7 +6402,7 @@
       <c r="F50" s="11"/>
       <c r="G50" s="11"/>
       <c r="I50" s="11" t="s">
-        <v>226</v>
+        <v>318</v>
       </c>
       <c r="J50" s="11"/>
       <c r="K50" s="11"/>
@@ -5861,22 +6413,22 @@
     </row>
     <row r="51">
       <c r="A51" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O51" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52">
@@ -5905,27 +6457,27 @@
     </row>
     <row r="54">
       <c r="F54" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G54" s="23"/>
       <c r="N54" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O54" s="23"/>
     </row>
     <row r="55">
       <c r="F55" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G55" s="23"/>
       <c r="N55" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O55" s="23"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="s">
-        <v>227</v>
+        <v>319</v>
       </c>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
@@ -5934,7 +6486,7 @@
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
       <c r="I58" s="11" t="s">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
@@ -5945,22 +6497,22 @@
     </row>
     <row r="59">
       <c r="A59" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O59" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="60">
@@ -5989,27 +6541,27 @@
     </row>
     <row r="62">
       <c r="F62" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G62" s="23"/>
       <c r="N62" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O62" s="23"/>
     </row>
     <row r="63">
       <c r="F63" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G63" s="23"/>
       <c r="N63" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O63" s="23"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="s">
-        <v>229</v>
+        <v>321</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -6018,7 +6570,7 @@
       <c r="F66" s="11"/>
       <c r="G66" s="11"/>
       <c r="I66" s="11" t="s">
-        <v>230</v>
+        <v>322</v>
       </c>
       <c r="J66" s="11"/>
       <c r="K66" s="11"/>
@@ -6029,22 +6581,22 @@
     </row>
     <row r="67">
       <c r="A67" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L67" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O67" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="68">
@@ -6073,27 +6625,27 @@
     </row>
     <row r="70">
       <c r="F70" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G70" s="23"/>
       <c r="N70" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O70" s="23"/>
     </row>
     <row r="71">
       <c r="F71" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G71" s="23"/>
       <c r="N71" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O71" s="23"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="s">
-        <v>231</v>
+        <v>323</v>
       </c>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
@@ -6102,7 +6654,7 @@
       <c r="F74" s="11"/>
       <c r="G74" s="11"/>
       <c r="I74" s="11" t="s">
-        <v>232</v>
+        <v>324</v>
       </c>
       <c r="J74" s="11"/>
       <c r="K74" s="11"/>
@@ -6113,22 +6665,22 @@
     </row>
     <row r="75">
       <c r="A75" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L75" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O75" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76">
@@ -6157,27 +6709,27 @@
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G78" s="23"/>
       <c r="N78" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O78" s="23"/>
     </row>
     <row r="79">
       <c r="F79" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G79" s="23"/>
       <c r="N79" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O79" s="23"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="s">
-        <v>233</v>
+        <v>325</v>
       </c>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
@@ -6186,7 +6738,7 @@
       <c r="F82" s="11"/>
       <c r="G82" s="11"/>
       <c r="I82" s="11" t="s">
-        <v>234</v>
+        <v>326</v>
       </c>
       <c r="J82" s="11"/>
       <c r="K82" s="11"/>
@@ -6197,22 +6749,22 @@
     </row>
     <row r="83">
       <c r="A83" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I83" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L83" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O83" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84">
@@ -6241,27 +6793,27 @@
     </row>
     <row r="86">
       <c r="F86" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G86" s="23"/>
       <c r="N86" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O86" s="23"/>
     </row>
     <row r="87">
       <c r="F87" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G87" s="23"/>
       <c r="N87" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O87" s="23"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="s">
-        <v>235</v>
+        <v>327</v>
       </c>
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
@@ -6270,7 +6822,7 @@
       <c r="F90" s="11"/>
       <c r="G90" s="11"/>
       <c r="I90" s="11" t="s">
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
@@ -6281,22 +6833,22 @@
     </row>
     <row r="91">
       <c r="A91" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I91" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O91" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92">
@@ -6325,27 +6877,27 @@
     </row>
     <row r="94">
       <c r="F94" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G94" s="23"/>
       <c r="N94" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O94" s="23"/>
     </row>
     <row r="95">
       <c r="F95" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G95" s="23"/>
       <c r="N95" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O95" s="23"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="s">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
@@ -6354,7 +6906,7 @@
       <c r="F98" s="11"/>
       <c r="G98" s="11"/>
       <c r="I98" s="11" t="s">
-        <v>238</v>
+        <v>330</v>
       </c>
       <c r="J98" s="11"/>
       <c r="K98" s="11"/>
@@ -6365,22 +6917,22 @@
     </row>
     <row r="99">
       <c r="A99" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I99" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L99" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O99" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="100">
@@ -6409,27 +6961,27 @@
     </row>
     <row r="102">
       <c r="F102" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G102" s="23"/>
       <c r="N102" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O102" s="23"/>
     </row>
     <row r="103">
       <c r="F103" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G103" s="23"/>
       <c r="N103" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O103" s="23"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="s">
-        <v>239</v>
+        <v>331</v>
       </c>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
@@ -6438,7 +6990,7 @@
       <c r="F106" s="11"/>
       <c r="G106" s="11"/>
       <c r="I106" s="11" t="s">
-        <v>240</v>
+        <v>332</v>
       </c>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
@@ -6449,22 +7001,22 @@
     </row>
     <row r="107">
       <c r="A107" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I107" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L107" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O107" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="108">
@@ -6493,27 +7045,27 @@
     </row>
     <row r="110">
       <c r="F110" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G110" s="23"/>
       <c r="N110" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O110" s="23"/>
     </row>
     <row r="111">
       <c r="F111" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G111" s="23"/>
       <c r="N111" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O111" s="23"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="s">
-        <v>241</v>
+        <v>333</v>
       </c>
       <c r="B114" s="11"/>
       <c r="C114" s="11"/>
@@ -6522,7 +7074,7 @@
       <c r="F114" s="11"/>
       <c r="G114" s="11"/>
       <c r="I114" s="11" t="s">
-        <v>242</v>
+        <v>334</v>
       </c>
       <c r="J114" s="11"/>
       <c r="K114" s="11"/>
@@ -6533,22 +7085,22 @@
     </row>
     <row r="115">
       <c r="A115" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I115" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L115" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O115" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="116">
@@ -6577,27 +7129,27 @@
     </row>
     <row r="118">
       <c r="F118" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G118" s="23"/>
       <c r="N118" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O118" s="23"/>
     </row>
     <row r="119">
       <c r="F119" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G119" s="23"/>
       <c r="N119" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O119" s="23"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="s">
-        <v>243</v>
+        <v>335</v>
       </c>
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
@@ -6606,7 +7158,7 @@
       <c r="F122" s="11"/>
       <c r="G122" s="11"/>
       <c r="I122" s="11" t="s">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="J122" s="11"/>
       <c r="K122" s="11"/>
@@ -6617,22 +7169,22 @@
     </row>
     <row r="123">
       <c r="A123" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I123" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L123" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O123" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124">
@@ -6661,27 +7213,27 @@
     </row>
     <row r="126">
       <c r="F126" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G126" s="23"/>
       <c r="N126" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O126" s="23"/>
     </row>
     <row r="127">
       <c r="F127" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G127" s="23"/>
       <c r="N127" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O127" s="23"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="s">
-        <v>245</v>
+        <v>337</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
@@ -6690,7 +7242,7 @@
       <c r="F135" s="11"/>
       <c r="G135" s="11"/>
       <c r="I135" s="11" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
@@ -6701,22 +7253,22 @@
     </row>
     <row r="136">
       <c r="A136" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G136" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I136" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L136" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O136" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="137">
@@ -6745,27 +7297,27 @@
     </row>
     <row r="139">
       <c r="F139" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G139" s="23"/>
       <c r="N139" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O139" s="23"/>
     </row>
     <row r="140">
       <c r="F140" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G140" s="23"/>
       <c r="N140" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O140" s="23"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="s">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
@@ -6774,7 +7326,7 @@
       <c r="F143" s="11"/>
       <c r="G143" s="11"/>
       <c r="I143" s="11" t="s">
-        <v>248</v>
+        <v>340</v>
       </c>
       <c r="J143" s="11"/>
       <c r="K143" s="11"/>
@@ -6785,22 +7337,22 @@
     </row>
     <row r="144">
       <c r="A144" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G144" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I144" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L144" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O144" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="145">
@@ -6829,27 +7381,27 @@
     </row>
     <row r="147">
       <c r="F147" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G147" s="23"/>
       <c r="N147" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O147" s="23"/>
     </row>
     <row r="148">
       <c r="F148" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G148" s="23"/>
       <c r="N148" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O148" s="23"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="s">
-        <v>249</v>
+        <v>341</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
@@ -6858,7 +7410,7 @@
       <c r="F151" s="11"/>
       <c r="G151" s="11"/>
       <c r="I151" s="11" t="s">
-        <v>250</v>
+        <v>342</v>
       </c>
       <c r="J151" s="11"/>
       <c r="K151" s="11"/>
@@ -6869,22 +7421,22 @@
     </row>
     <row r="152">
       <c r="A152" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D152" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G152" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I152" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L152" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O152" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="153">
@@ -6913,27 +7465,27 @@
     </row>
     <row r="155">
       <c r="F155" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G155" s="23"/>
       <c r="N155" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O155" s="23"/>
     </row>
     <row r="156">
       <c r="F156" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G156" s="23"/>
       <c r="N156" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O156" s="23"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="11"/>
@@ -6942,7 +7494,7 @@
       <c r="F159" s="11"/>
       <c r="G159" s="11"/>
       <c r="I159" s="11" t="s">
-        <v>252</v>
+        <v>344</v>
       </c>
       <c r="J159" s="11"/>
       <c r="K159" s="11"/>
@@ -6953,22 +7505,22 @@
     </row>
     <row r="160">
       <c r="A160" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D160" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I160" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L160" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O160" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="161">
@@ -6997,27 +7549,27 @@
     </row>
     <row r="163">
       <c r="F163" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G163" s="23"/>
       <c r="N163" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O163" s="23"/>
     </row>
     <row r="164">
       <c r="F164" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G164" s="23"/>
       <c r="N164" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O164" s="23"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="s">
-        <v>253</v>
+        <v>345</v>
       </c>
       <c r="B167" s="11"/>
       <c r="C167" s="11"/>
@@ -7026,7 +7578,7 @@
       <c r="F167" s="11"/>
       <c r="G167" s="11"/>
       <c r="I167" s="11" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="J167" s="11"/>
       <c r="K167" s="11"/>
@@ -7037,22 +7589,22 @@
     </row>
     <row r="168">
       <c r="A168" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D168" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G168" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I168" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L168" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O168" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="169">
@@ -7081,27 +7633,27 @@
     </row>
     <row r="171">
       <c r="F171" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G171" s="23"/>
       <c r="N171" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O171" s="23"/>
     </row>
     <row r="172">
       <c r="F172" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G172" s="23"/>
       <c r="N172" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O172" s="23"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="B175" s="11"/>
       <c r="C175" s="11"/>
@@ -7110,7 +7662,7 @@
       <c r="F175" s="11"/>
       <c r="G175" s="11"/>
       <c r="I175" s="11" t="s">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
@@ -7121,22 +7673,22 @@
     </row>
     <row r="176">
       <c r="A176" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D176" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G176" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I176" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L176" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O176" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="177">
@@ -7165,27 +7717,27 @@
     </row>
     <row r="179">
       <c r="F179" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G179" s="23"/>
       <c r="N179" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O179" s="23"/>
     </row>
     <row r="180">
       <c r="F180" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G180" s="23"/>
       <c r="N180" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O180" s="23"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="s">
-        <v>257</v>
+        <v>349</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="11"/>
@@ -7194,7 +7746,7 @@
       <c r="F183" s="11"/>
       <c r="G183" s="11"/>
       <c r="I183" s="11" t="s">
-        <v>258</v>
+        <v>350</v>
       </c>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
@@ -7205,22 +7757,22 @@
     </row>
     <row r="184">
       <c r="A184" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D184" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G184" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I184" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L184" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O184" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="185">
@@ -7249,27 +7801,27 @@
     </row>
     <row r="187">
       <c r="F187" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G187" s="23"/>
       <c r="N187" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O187" s="23"/>
     </row>
     <row r="188">
       <c r="F188" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G188" s="23"/>
       <c r="N188" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O188" s="23"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="s">
-        <v>259</v>
+        <v>351</v>
       </c>
       <c r="B191" s="11"/>
       <c r="C191" s="11"/>
@@ -7278,7 +7830,7 @@
       <c r="F191" s="11"/>
       <c r="G191" s="11"/>
       <c r="I191" s="11" t="s">
-        <v>260</v>
+        <v>352</v>
       </c>
       <c r="J191" s="11"/>
       <c r="K191" s="11"/>
@@ -7289,22 +7841,22 @@
     </row>
     <row r="192">
       <c r="A192" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D192" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G192" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I192" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L192" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O192" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="193">
@@ -7333,27 +7885,27 @@
     </row>
     <row r="195">
       <c r="F195" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G195" s="23"/>
       <c r="N195" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O195" s="23"/>
     </row>
     <row r="196">
       <c r="F196" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G196" s="23"/>
       <c r="N196" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O196" s="23"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="s">
-        <v>261</v>
+        <v>353</v>
       </c>
       <c r="B199" s="11"/>
       <c r="C199" s="11"/>
@@ -7362,7 +7914,7 @@
       <c r="F199" s="11"/>
       <c r="G199" s="11"/>
       <c r="I199" s="11" t="s">
-        <v>262</v>
+        <v>354</v>
       </c>
       <c r="J199" s="11"/>
       <c r="K199" s="11"/>
@@ -7373,22 +7925,22 @@
     </row>
     <row r="200">
       <c r="A200" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D200" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G200" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I200" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L200" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O200" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="201">
@@ -7417,27 +7969,27 @@
     </row>
     <row r="203">
       <c r="F203" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G203" s="23"/>
       <c r="N203" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O203" s="23"/>
     </row>
     <row r="204">
       <c r="F204" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G204" s="23"/>
       <c r="N204" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O204" s="23"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="s">
-        <v>263</v>
+        <v>355</v>
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="11"/>
@@ -7446,7 +7998,7 @@
       <c r="F207" s="11"/>
       <c r="G207" s="11"/>
       <c r="I207" s="11" t="s">
-        <v>264</v>
+        <v>356</v>
       </c>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
@@ -7457,22 +8009,22 @@
     </row>
     <row r="208">
       <c r="A208" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D208" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G208" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I208" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L208" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O208" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="209">
@@ -7501,27 +8053,27 @@
     </row>
     <row r="211">
       <c r="F211" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G211" s="23"/>
       <c r="N211" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O211" s="23"/>
     </row>
     <row r="212">
       <c r="F212" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G212" s="23"/>
       <c r="N212" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O212" s="23"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -7530,7 +8082,7 @@
       <c r="F215" s="11"/>
       <c r="G215" s="11"/>
       <c r="I215" s="11" t="s">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
@@ -7541,22 +8093,22 @@
     </row>
     <row r="216">
       <c r="A216" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D216" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G216" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I216" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L216" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O216" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="217">
@@ -7585,27 +8137,27 @@
     </row>
     <row r="219">
       <c r="F219" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G219" s="23"/>
       <c r="N219" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O219" s="23"/>
     </row>
     <row r="220">
       <c r="F220" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G220" s="23"/>
       <c r="N220" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O220" s="23"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="B223" s="11"/>
       <c r="C223" s="11"/>
@@ -7614,7 +8166,7 @@
       <c r="F223" s="11"/>
       <c r="G223" s="11"/>
       <c r="I223" s="11" t="s">
-        <v>268</v>
+        <v>360</v>
       </c>
       <c r="J223" s="11"/>
       <c r="K223" s="11"/>
@@ -7625,22 +8177,22 @@
     </row>
     <row r="224">
       <c r="A224" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D224" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G224" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I224" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L224" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O224" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="225">
@@ -7669,27 +8221,27 @@
     </row>
     <row r="227">
       <c r="F227" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G227" s="23"/>
       <c r="N227" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O227" s="23"/>
     </row>
     <row r="228">
       <c r="F228" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G228" s="23"/>
       <c r="N228" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O228" s="23"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="s">
-        <v>269</v>
+        <v>361</v>
       </c>
       <c r="B231" s="11"/>
       <c r="C231" s="11"/>
@@ -7698,7 +8250,7 @@
       <c r="F231" s="11"/>
       <c r="G231" s="11"/>
       <c r="I231" s="11" t="s">
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="J231" s="11"/>
       <c r="K231" s="11"/>
@@ -7709,22 +8261,22 @@
     </row>
     <row r="232">
       <c r="A232" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D232" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G232" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I232" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L232" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O232" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="233">
@@ -7753,27 +8305,27 @@
     </row>
     <row r="235">
       <c r="F235" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G235" s="23"/>
       <c r="N235" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O235" s="23"/>
     </row>
     <row r="236">
       <c r="F236" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G236" s="23"/>
       <c r="N236" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O236" s="23"/>
     </row>
     <row r="239">
       <c r="I239" s="11" t="s">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="J239" s="11"/>
       <c r="K239" s="11"/>
@@ -7784,13 +8336,13 @@
     </row>
     <row r="240">
       <c r="I240" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L240" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O240" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="241">
@@ -7808,19 +8360,19 @@
     </row>
     <row r="243">
       <c r="N243" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O243" s="23"/>
     </row>
     <row r="244">
       <c r="N244" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O244" s="23"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="s">
-        <v>272</v>
+        <v>364</v>
       </c>
       <c r="B252" s="11"/>
       <c r="C252" s="11"/>
@@ -7829,7 +8381,7 @@
       <c r="F252" s="11"/>
       <c r="G252" s="11"/>
       <c r="I252" s="11" t="s">
-        <v>273</v>
+        <v>365</v>
       </c>
       <c r="J252" s="11"/>
       <c r="K252" s="11"/>
@@ -7840,22 +8392,22 @@
     </row>
     <row r="253">
       <c r="A253" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D253" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G253" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I253" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L253" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O253" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="254">
@@ -7884,27 +8436,27 @@
     </row>
     <row r="256">
       <c r="F256" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G256" s="23"/>
       <c r="N256" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O256" s="23"/>
     </row>
     <row r="257">
       <c r="F257" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G257" s="23"/>
       <c r="N257" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O257" s="23"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="s">
-        <v>274</v>
+        <v>366</v>
       </c>
       <c r="B260" s="11"/>
       <c r="C260" s="11"/>
@@ -7913,7 +8465,7 @@
       <c r="F260" s="11"/>
       <c r="G260" s="11"/>
       <c r="I260" s="11" t="s">
-        <v>275</v>
+        <v>367</v>
       </c>
       <c r="J260" s="11"/>
       <c r="K260" s="11"/>
@@ -7924,22 +8476,22 @@
     </row>
     <row r="261">
       <c r="A261" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D261" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G261" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I261" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L261" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O261" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="262">
@@ -7968,27 +8520,27 @@
     </row>
     <row r="264">
       <c r="F264" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G264" s="23"/>
       <c r="N264" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O264" s="23"/>
     </row>
     <row r="265">
       <c r="F265" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G265" s="23"/>
       <c r="N265" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O265" s="23"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="s">
-        <v>276</v>
+        <v>368</v>
       </c>
       <c r="B268" s="11"/>
       <c r="C268" s="11"/>
@@ -7997,7 +8549,7 @@
       <c r="F268" s="11"/>
       <c r="G268" s="11"/>
       <c r="I268" s="11" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="J268" s="11"/>
       <c r="K268" s="11"/>
@@ -8008,22 +8560,22 @@
     </row>
     <row r="269">
       <c r="A269" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D269" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G269" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I269" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L269" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O269" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="270">
@@ -8052,27 +8604,27 @@
     </row>
     <row r="272">
       <c r="F272" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G272" s="23"/>
       <c r="N272" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O272" s="23"/>
     </row>
     <row r="273">
       <c r="F273" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G273" s="23"/>
       <c r="N273" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O273" s="23"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="s">
-        <v>278</v>
+        <v>370</v>
       </c>
       <c r="B276" s="11"/>
       <c r="C276" s="11"/>
@@ -8081,7 +8633,7 @@
       <c r="F276" s="11"/>
       <c r="G276" s="11"/>
       <c r="I276" s="11" t="s">
-        <v>279</v>
+        <v>371</v>
       </c>
       <c r="J276" s="11"/>
       <c r="K276" s="11"/>
@@ -8092,22 +8644,22 @@
     </row>
     <row r="277">
       <c r="A277" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D277" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G277" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I277" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L277" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O277" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="278">
@@ -8136,27 +8688,27 @@
     </row>
     <row r="280">
       <c r="F280" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G280" s="23"/>
       <c r="N280" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O280" s="23"/>
     </row>
     <row r="281">
       <c r="F281" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G281" s="23"/>
       <c r="N281" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O281" s="23"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="s">
-        <v>280</v>
+        <v>372</v>
       </c>
       <c r="B284" s="11"/>
       <c r="C284" s="11"/>
@@ -8165,7 +8717,7 @@
       <c r="F284" s="11"/>
       <c r="G284" s="11"/>
       <c r="I284" s="11" t="s">
-        <v>281</v>
+        <v>373</v>
       </c>
       <c r="J284" s="11"/>
       <c r="K284" s="11"/>
@@ -8176,22 +8728,22 @@
     </row>
     <row r="285">
       <c r="A285" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D285" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G285" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I285" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L285" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O285" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="286">
@@ -8220,27 +8772,27 @@
     </row>
     <row r="288">
       <c r="F288" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G288" s="23"/>
       <c r="N288" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O288" s="23"/>
     </row>
     <row r="289">
       <c r="F289" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G289" s="23"/>
       <c r="N289" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O289" s="23"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="s">
-        <v>282</v>
+        <v>374</v>
       </c>
       <c r="B292" s="11"/>
       <c r="C292" s="11"/>
@@ -8249,7 +8801,7 @@
       <c r="F292" s="11"/>
       <c r="G292" s="11"/>
       <c r="I292" s="11" t="s">
-        <v>283</v>
+        <v>375</v>
       </c>
       <c r="J292" s="11"/>
       <c r="K292" s="11"/>
@@ -8260,22 +8812,22 @@
     </row>
     <row r="293">
       <c r="A293" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D293" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G293" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I293" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L293" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O293" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="294">
@@ -8304,27 +8856,27 @@
     </row>
     <row r="296">
       <c r="F296" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G296" s="23"/>
       <c r="N296" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O296" s="23"/>
     </row>
     <row r="297">
       <c r="F297" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G297" s="23"/>
       <c r="N297" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O297" s="23"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="s">
-        <v>284</v>
+        <v>376</v>
       </c>
       <c r="B300" s="11"/>
       <c r="C300" s="11"/>
@@ -8333,7 +8885,7 @@
       <c r="F300" s="11"/>
       <c r="G300" s="11"/>
       <c r="I300" s="11" t="s">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="J300" s="11"/>
       <c r="K300" s="11"/>
@@ -8344,22 +8896,22 @@
     </row>
     <row r="301">
       <c r="A301" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D301" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G301" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I301" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L301" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O301" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="302">
@@ -8388,27 +8940,27 @@
     </row>
     <row r="304">
       <c r="F304" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G304" s="23"/>
       <c r="N304" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O304" s="23"/>
     </row>
     <row r="305">
       <c r="F305" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G305" s="23"/>
       <c r="N305" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O305" s="23"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="s">
-        <v>286</v>
+        <v>378</v>
       </c>
       <c r="B308" s="11"/>
       <c r="C308" s="11"/>
@@ -8417,7 +8969,7 @@
       <c r="F308" s="11"/>
       <c r="G308" s="11"/>
       <c r="I308" s="11" t="s">
-        <v>287</v>
+        <v>379</v>
       </c>
       <c r="J308" s="11"/>
       <c r="K308" s="11"/>
@@ -8428,22 +8980,22 @@
     </row>
     <row r="309">
       <c r="A309" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D309" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G309" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I309" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L309" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O309" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="310">
@@ -8472,27 +9024,27 @@
     </row>
     <row r="312">
       <c r="F312" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G312" s="23"/>
       <c r="N312" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O312" s="23"/>
     </row>
     <row r="313">
       <c r="F313" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G313" s="23"/>
       <c r="N313" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O313" s="23"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="B321" s="11"/>
       <c r="C321" s="11"/>
@@ -8501,7 +9053,7 @@
       <c r="F321" s="11"/>
       <c r="G321" s="11"/>
       <c r="I321" s="11" t="s">
-        <v>289</v>
+        <v>381</v>
       </c>
       <c r="J321" s="11"/>
       <c r="K321" s="11"/>
@@ -8512,22 +9064,22 @@
     </row>
     <row r="322">
       <c r="A322" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D322" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G322" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I322" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L322" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O322" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="323">
@@ -8556,27 +9108,27 @@
     </row>
     <row r="325">
       <c r="F325" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G325" s="23"/>
       <c r="N325" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O325" s="23"/>
     </row>
     <row r="326">
       <c r="F326" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G326" s="23"/>
       <c r="N326" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O326" s="23"/>
     </row>
     <row r="329">
       <c r="A329" s="11" t="s">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="11"/>
@@ -8585,7 +9137,7 @@
       <c r="F329" s="11"/>
       <c r="G329" s="11"/>
       <c r="I329" s="11" t="s">
-        <v>291</v>
+        <v>383</v>
       </c>
       <c r="J329" s="11"/>
       <c r="K329" s="11"/>
@@ -8596,22 +9148,22 @@
     </row>
     <row r="330">
       <c r="A330" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D330" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G330" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I330" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L330" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O330" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="331">
@@ -8640,27 +9192,27 @@
     </row>
     <row r="333">
       <c r="F333" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G333" s="23"/>
       <c r="N333" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O333" s="23"/>
     </row>
     <row r="334">
       <c r="F334" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G334" s="23"/>
       <c r="N334" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O334" s="23"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="s">
-        <v>292</v>
+        <v>384</v>
       </c>
       <c r="B337" s="11"/>
       <c r="C337" s="11"/>
@@ -8669,7 +9221,7 @@
       <c r="F337" s="11"/>
       <c r="G337" s="11"/>
       <c r="I337" s="11" t="s">
-        <v>293</v>
+        <v>385</v>
       </c>
       <c r="J337" s="11"/>
       <c r="K337" s="11"/>
@@ -8680,22 +9232,22 @@
     </row>
     <row r="338">
       <c r="A338" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D338" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G338" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I338" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L338" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O338" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="339">
@@ -8724,27 +9276,27 @@
     </row>
     <row r="341">
       <c r="F341" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G341" s="23"/>
       <c r="N341" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O341" s="23"/>
     </row>
     <row r="342">
       <c r="F342" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G342" s="23"/>
       <c r="N342" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O342" s="23"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="s">
-        <v>294</v>
+        <v>386</v>
       </c>
       <c r="B345" s="11"/>
       <c r="C345" s="11"/>
@@ -8753,7 +9305,7 @@
       <c r="F345" s="11"/>
       <c r="G345" s="11"/>
       <c r="I345" s="11" t="s">
-        <v>295</v>
+        <v>387</v>
       </c>
       <c r="J345" s="11"/>
       <c r="K345" s="11"/>
@@ -8764,22 +9316,22 @@
     </row>
     <row r="346">
       <c r="A346" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D346" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G346" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I346" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L346" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O346" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="347">
@@ -8808,27 +9360,27 @@
     </row>
     <row r="349">
       <c r="F349" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G349" s="23"/>
       <c r="N349" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O349" s="23"/>
     </row>
     <row r="350">
       <c r="F350" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G350" s="23"/>
       <c r="N350" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O350" s="23"/>
     </row>
     <row r="358">
       <c r="A358" s="11" t="s">
-        <v>296</v>
+        <v>388</v>
       </c>
       <c r="B358" s="11"/>
       <c r="C358" s="11"/>
@@ -8837,7 +9389,7 @@
       <c r="F358" s="11"/>
       <c r="G358" s="11"/>
       <c r="I358" s="11" t="s">
-        <v>297</v>
+        <v>389</v>
       </c>
       <c r="J358" s="11"/>
       <c r="K358" s="11"/>
@@ -8848,22 +9400,22 @@
     </row>
     <row r="359">
       <c r="A359" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D359" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G359" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I359" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L359" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O359" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="360">
@@ -8892,27 +9444,27 @@
     </row>
     <row r="362">
       <c r="F362" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G362" s="23"/>
       <c r="N362" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O362" s="23"/>
     </row>
     <row r="363">
       <c r="F363" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G363" s="23"/>
       <c r="N363" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O363" s="23"/>
     </row>
     <row r="366">
       <c r="A366" s="11" t="s">
-        <v>298</v>
+        <v>390</v>
       </c>
       <c r="B366" s="11"/>
       <c r="C366" s="11"/>
@@ -8921,7 +9473,7 @@
       <c r="F366" s="11"/>
       <c r="G366" s="11"/>
       <c r="I366" s="11" t="s">
-        <v>299</v>
+        <v>391</v>
       </c>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
@@ -8932,22 +9484,22 @@
     </row>
     <row r="367">
       <c r="A367" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D367" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G367" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I367" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L367" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O367" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="368">
@@ -8976,27 +9528,27 @@
     </row>
     <row r="370">
       <c r="F370" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G370" s="23"/>
       <c r="N370" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O370" s="23"/>
     </row>
     <row r="371">
       <c r="F371" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G371" s="23"/>
       <c r="N371" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O371" s="23"/>
     </row>
     <row r="379">
       <c r="A379" s="11" t="s">
-        <v>300</v>
+        <v>392</v>
       </c>
       <c r="B379" s="11"/>
       <c r="C379" s="11"/>
@@ -9005,7 +9557,7 @@
       <c r="F379" s="11"/>
       <c r="G379" s="11"/>
       <c r="I379" s="11" t="s">
-        <v>301</v>
+        <v>393</v>
       </c>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
@@ -9016,22 +9568,22 @@
     </row>
     <row r="380">
       <c r="A380" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D380" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G380" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I380" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L380" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O380" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="381">
@@ -9060,27 +9612,27 @@
     </row>
     <row r="383">
       <c r="F383" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G383" s="23"/>
       <c r="N383" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O383" s="23"/>
     </row>
     <row r="384">
       <c r="F384" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G384" s="23"/>
       <c r="N384" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O384" s="23"/>
     </row>
     <row r="392">
       <c r="A392" s="11" t="s">
-        <v>302</v>
+        <v>394</v>
       </c>
       <c r="B392" s="11"/>
       <c r="C392" s="11"/>
@@ -9091,13 +9643,13 @@
     </row>
     <row r="393">
       <c r="A393" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D393" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G393" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="394">
@@ -9115,13 +9667,13 @@
     </row>
     <row r="396">
       <c r="F396" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G396" s="23"/>
     </row>
     <row r="397">
       <c r="F397" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G397" s="23"/>
     </row>
@@ -9271,7 +9823,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -9282,7 +9834,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9311,7 +9863,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9332,7 +9884,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9348,7 +9900,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9366,7 +9918,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9383,7 +9935,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9402,7 +9954,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9423,7 +9975,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9441,7 +9993,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9455,7 +10007,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -9501,7 +10053,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -9512,7 +10064,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9541,7 +10093,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9562,7 +10114,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9578,7 +10130,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9596,7 +10148,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9613,7 +10165,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9632,7 +10184,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9653,7 +10205,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9671,7 +10223,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>192</v>
+        <v>276</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9685,7 +10237,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -74,7 +74,7 @@
     <t/>
   </si>
   <si>
-    <t>Number</t>
+    <t>Draw order</t>
   </si>
   <si>
     <t>Player Name</t>
@@ -1469,7 +1469,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>43</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>49</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>61</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>64</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>70</v>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>73</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>76</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>79</v>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>82</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>85</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>89</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>93</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>101</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>105</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -2284,7 +2284,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>110</v>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>113</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>115</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>117</v>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>119</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>121</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>123</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
         <v>127</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
         <v>129</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
         <v>131</v>
@@ -2471,7 +2471,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
         <v>133</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
         <v>135</v>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
         <v>137</v>
@@ -2522,7 +2522,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
         <v>140</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
         <v>143</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
         <v>146</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
         <v>149</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
         <v>152</v>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
         <v>155</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>158</v>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
         <v>161</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
         <v>164</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
         <v>167</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
         <v>171</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
         <v>175</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
         <v>179</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
         <v>183</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
         <v>187</v>
@@ -2777,7 +2777,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
         <v>191</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
         <v>195</v>
@@ -2811,7 +2811,7 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
         <v>199</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
         <v>203</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
         <v>207</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
         <v>211</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
         <v>215</v>
@@ -2896,7 +2896,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
         <v>219</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
         <v>223</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
         <v>226</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
         <v>229</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
         <v>232</v>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
         <v>235</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
         <v>238</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
         <v>241</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
         <v>243</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
         <v>246</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
         <v>249</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
         <v>252</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
         <v>255</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
         <v>258</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
         <v>261</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
         <v>263</v>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
         <v>266</v>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
         <v>269</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
         <v>272</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
         <v>275</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
         <v>278</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
         <v>281</v>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
         <v>283</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
         <v>286</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
         <v>289</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
         <v>292</v>
@@ -3338,7 +3338,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
         <v>295</v>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -2838,7 +2838,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
@@ -2849,7 +2849,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3121,7 +3121,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3406,7 +3406,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3463,7 +3463,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3481,7 +3481,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3543,7 +3543,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -3557,7 +3557,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3594,7 +3594,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3936,7 +3936,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4016,7 +4016,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
@@ -4030,7 +4030,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>32</v>
+        <v>188</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4067,7 +4067,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4088,7 +4088,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4104,7 +4104,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>199</v>
+        <v>44</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4244,74 +4244,74 @@
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D28</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D27</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D62</f>
+        <f>'data'!D58</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D25</f>
+        <f>'data'!D59</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D82</f>
+        <f>'data'!D29</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D83</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D34</f>
+        <f>'data'!D61</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D80</f>
+        <f>'data'!D14</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D81</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -4332,18 +4332,18 @@
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D79</f>
+        <f>'data'!D56</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D19</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4364,18 +4364,18 @@
     </row>
     <row r="17" ht="270" customHeight="true">
       <c r="A17" s="17">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B17" s="18" t="str">
-        <f>'data'!D60</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
       <c r="A18" s="17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>'data'!D63</f>
+        <f>'data'!D68</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
@@ -4388,42 +4388,42 @@
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D64</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
       <c r="A21" s="17">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>'data'!D86</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
       <c r="A22" s="17">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>'data'!D84</f>
+        <f>'data'!D27</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
       <c r="A23" s="17">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B23" s="18" t="str">
-        <f>'data'!D28</f>
+        <f>'data'!D57</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
       <c r="A24" s="17">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B24" s="18" t="str">
-        <f>'data'!D29</f>
+        <f>'data'!D55</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
@@ -4444,10 +4444,10 @@
     </row>
     <row r="27" ht="270" customHeight="true">
       <c r="A27" s="17">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>'data'!D32</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4460,10 +4460,10 @@
     </row>
     <row r="29" ht="270" customHeight="true">
       <c r="A29" s="17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B29" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
@@ -4508,42 +4508,42 @@
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D49</f>
+        <f>'data'!D39</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
       <c r="A36" s="17">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>'data'!D40</f>
+        <f>'data'!D88</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D41</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D87</f>
+        <f>'data'!D90</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
       <c r="A39" s="17">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="B39" s="18" t="str">
-        <f>'data'!D43</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
@@ -4588,10 +4588,10 @@
     </row>
     <row r="45" ht="270" customHeight="true">
       <c r="A45" s="17">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B45" s="18" t="str">
-        <f>'data'!D39</f>
+        <f>'data'!D49</f>
       </c>
     </row>
     <row r="46" ht="270" customHeight="true">
@@ -4669,82 +4669,82 @@
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D55</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D56</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D57</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D58</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D59</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D22</f>
+        <f>'data'!D60</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D61</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D9</f>
+        <f>'data'!D32</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D23</f>
+        <f>'data'!D63</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D10</f>
+        <f>'data'!D80</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="18" ht="270" customHeight="true">
       <c r="A18" s="17">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>'data'!D68</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
@@ -4797,10 +4797,10 @@
     </row>
     <row r="21" ht="270" customHeight="true">
       <c r="A21" s="17">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>'data'!D85</f>
+        <f>'data'!D74</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="25" ht="270" customHeight="true">
       <c r="A25" s="17">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B25" s="18" t="str">
-        <f>'data'!D74</f>
+        <f>'data'!D70</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
@@ -4869,82 +4869,82 @@
     </row>
     <row r="30" ht="270" customHeight="true">
       <c r="A30" s="17">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B30" s="18" t="str">
-        <f>'data'!D18</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
       <c r="A31" s="17">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>'data'!D14</f>
+        <f>'data'!D41</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
       <c r="A32" s="17">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>'data'!D15</f>
+        <f>'data'!D81</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D11</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
       <c r="A34" s="17">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D83</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D8</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
       <c r="A36" s="17">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>'data'!D70</f>
+        <f>'data'!D34</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D7</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D42</f>
+        <f>'data'!D87</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
       <c r="A39" s="17">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="B39" s="18" t="str">
-        <f>'data'!D88</f>
+        <f>'data'!D40</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
@@ -4957,18 +4957,18 @@
     </row>
     <row r="41" ht="270" customHeight="true">
       <c r="A41" s="17">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="B41" s="18" t="str">
-        <f>'data'!D90</f>
+        <f>'data'!D42</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
       <c r="A42" s="17">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>'data'!D91</f>
+        <f>'data'!D43</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
@@ -5377,7 +5377,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$28</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$25</f>
+        <f>'data'!$B$81</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -5469,7 +5469,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$58</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$54</f>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$61</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -5553,10 +5553,10 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$83</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$57</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -5564,7 +5564,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
-        <f>'data'!$B$56</f>
+        <f>'data'!$B$18</f>
       </c>
     </row>
     <row r="22">
@@ -5637,10 +5637,10 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$59</f>
+        <f>'data'!$B$43</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$22</f>
+        <f>'data'!$B$60</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -5648,7 +5648,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$59</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="30">
@@ -5713,7 +5713,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="str">
-        <f>'data'!$B$79</f>
+        <f>'data'!$B$56</f>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -5724,7 +5724,7 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="I36" s="19" t="str">
-        <f>'data'!$B$23</f>
+        <f>'data'!$B$63</f>
       </c>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
@@ -5732,7 +5732,7 @@
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$32</f>
       </c>
     </row>
     <row r="38">
@@ -5889,7 +5889,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$68</f>
       </c>
       <c r="I52" s="19" t="str">
         <f>'data'!$B$4</f>
@@ -5900,7 +5900,7 @@
       <c r="M52" s="22"/>
       <c r="N52" s="22"/>
       <c r="O52" s="19" t="str">
-        <f>'data'!$B$68</f>
+        <f>'data'!$B$23</f>
       </c>
     </row>
     <row r="54">
@@ -5965,7 +5965,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$27</f>
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -5973,10 +5973,10 @@
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
       <c r="G60" s="19" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="I60" s="19" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$71</f>
       </c>
       <c r="J60" s="22"/>
       <c r="K60" s="22"/>
@@ -5984,7 +5984,7 @@
       <c r="M60" s="22"/>
       <c r="N60" s="22"/>
       <c r="O60" s="19" t="str">
-        <f>'data'!$B$85</f>
+        <f>'data'!$B$70</f>
       </c>
     </row>
     <row r="62">
@@ -6049,7 +6049,7 @@
     </row>
     <row r="68">
       <c r="A68" s="19" t="str">
-        <f>'data'!$B$29</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -6057,7 +6057,7 @@
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
       <c r="G68" s="19" t="str">
-        <f>'data'!$B$28</f>
+        <f>'data'!$B$57</f>
       </c>
       <c r="I68" s="19" t="str">
         <f>'data'!$B$73</f>
@@ -6133,7 +6133,7 @@
     </row>
     <row r="76">
       <c r="A76" s="19" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$62</f>
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -6225,10 +6225,10 @@
       <c r="E84" s="22"/>
       <c r="F84" s="22"/>
       <c r="G84" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="I84" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="J84" s="22"/>
       <c r="K84" s="22"/>
@@ -6312,7 +6312,7 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="I92" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$82</f>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="22"/>
@@ -6320,7 +6320,7 @@
       <c r="M92" s="22"/>
       <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
-        <f>'data'!$B$15</f>
+        <f>'data'!$B$81</f>
       </c>
     </row>
     <row r="94">
@@ -6385,7 +6385,7 @@
     </row>
     <row r="100">
       <c r="A100" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$71</f>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6393,10 +6393,10 @@
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
-        <f>'data'!$B$49</f>
+        <f>'data'!$B$11</f>
       </c>
       <c r="I100" s="19" t="str">
-        <f>'data'!$B$70</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -6404,7 +6404,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$84</f>
       </c>
     </row>
     <row r="102">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="108">
       <c r="A108" s="19" t="str">
-        <f>'data'!$B$15</f>
+        <f>'data'!$B$91</f>
       </c>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -6477,10 +6477,10 @@
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="19" t="str">
-        <f>'data'!$B$87</f>
+        <f>'data'!$B$90</f>
       </c>
       <c r="I108" s="19" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="J108" s="22"/>
       <c r="K108" s="22"/>
@@ -6488,7 +6488,7 @@
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$87</f>
       </c>
     </row>
     <row r="110">
@@ -6564,7 +6564,7 @@
         <f>'data'!$B$45</f>
       </c>
       <c r="I116" s="19" t="str">
-        <f>'data'!$B$91</f>
+        <f>'data'!$B$43</f>
       </c>
       <c r="J116" s="22"/>
       <c r="K116" s="22"/>
@@ -6572,7 +6572,7 @@
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
       <c r="O116" s="19" t="str">
-        <f>'data'!$B$90</f>
+        <f>'data'!$B$42</f>
       </c>
     </row>
     <row r="118">
@@ -6637,7 +6637,7 @@
     </row>
     <row r="124">
       <c r="A124" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$49</f>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -6729,7 +6729,7 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$27</f>
+        <f>'data'!$B$79</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 18 ",O14)</f>
@@ -6813,7 +6813,7 @@
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
-        <f>'data'!$B$82</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="I145" s="19" t="str">
         <f>CONCATENATE("M 19 ",O22)</f>
@@ -6824,7 +6824,7 @@
       <c r="M145" s="22"/>
       <c r="N145" s="22"/>
       <c r="O145" s="19" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="147">
@@ -6897,7 +6897,7 @@
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
-        <f>'data'!$B$80</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I153" s="19" t="str">
         <f>CONCATENATE("M 20 ",O30)</f>
@@ -6908,7 +6908,7 @@
       <c r="M153" s="22"/>
       <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$9</f>
       </c>
     </row>
     <row r="155">
@@ -6981,7 +6981,7 @@
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
       <c r="G161" s="19" t="str">
-        <f>'data'!$B$30</f>
+        <f>'data'!$B$85</f>
       </c>
       <c r="I161" s="19" t="str">
         <f>CONCATENATE("M 21 ",O38)</f>
@@ -6992,7 +6992,7 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
-        <f>'data'!$B$61</f>
+        <f>'data'!$B$41</f>
       </c>
     </row>
     <row r="163">
@@ -7065,7 +7065,7 @@
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
       <c r="G169" s="19" t="str">
-        <f>'data'!$B$60</f>
+        <f>'data'!$B$22</f>
       </c>
       <c r="I169" s="19" t="str">
         <f>CONCATENATE("M 22 ",O46)</f>
@@ -7076,7 +7076,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$80</f>
       </c>
     </row>
     <row r="171">
@@ -7149,7 +7149,7 @@
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
       <c r="G177" s="19" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$25</f>
       </c>
       <c r="I177" s="19" t="str">
         <f>CONCATENATE("M 23 ",O54)</f>
@@ -7233,7 +7233,7 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$30</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>CONCATENATE("M 24 ",O62)</f>
@@ -7496,7 +7496,7 @@
       <c r="M209" s="22"/>
       <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$41</f>
       </c>
     </row>
     <row r="211">
@@ -7569,7 +7569,7 @@
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$64</f>
       </c>
       <c r="I217" s="19" t="str">
         <f>CONCATENATE("M 29 ",O102)</f>
@@ -7580,7 +7580,7 @@
       <c r="M217" s="22"/>
       <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$83</f>
       </c>
     </row>
     <row r="219">
@@ -7664,7 +7664,7 @@
       <c r="M225" s="22"/>
       <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$86</f>
       </c>
     </row>
     <row r="227">
@@ -9282,7 +9282,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9311,7 +9311,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9366,7 +9366,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9402,7 +9402,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9423,7 +9423,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9512,7 +9512,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9541,7 +9541,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9596,7 +9596,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9653,7 +9653,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9685,7 +9685,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -1472,7 +1472,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -4782,8 +4782,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -5183,8 +5183,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -74,7 +74,7 @@
     <t/>
   </si>
   <si>
-    <t>Draw order</t>
+    <t>Entry order</t>
   </si>
   <si>
     <t>Player Name</t>

--- a/playoffs-example-large-seeded.xlsx
+++ b/playoffs-example-large-seeded.xlsx
@@ -104,832 +104,832 @@
     <t>K1</t>
   </si>
   <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>K5</t>
+  </si>
+  <si>
+    <t>Kaden Martin</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>K6</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>K7</t>
+  </si>
+  <si>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>K8</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>K9</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>K10</t>
+  </si>
+  <si>
+    <t>Xavier Scott</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>SCOTT</t>
+  </si>
+  <si>
+    <t>K11</t>
+  </si>
+  <si>
+    <t>Yosef Green</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>K12</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>K13</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>K14</t>
+  </si>
+  <si>
+    <t>Benjamin Evans</t>
+  </si>
+  <si>
+    <t>EVANS</t>
+  </si>
+  <si>
+    <t>K15</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>K16</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>K17</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>K18</t>
+  </si>
+  <si>
+    <t>Finn Anderson</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>K19</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>K20</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>K21</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>K22</t>
+  </si>
+  <si>
+    <t>Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>HAWTHORNE</t>
+  </si>
+  <si>
+    <t>K23</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>K24</t>
+  </si>
+  <si>
+    <t>Liam Thompson</t>
+  </si>
+  <si>
+    <t>THOMPSON</t>
+  </si>
+  <si>
+    <t>K25</t>
+  </si>
+  <si>
+    <t>Mason Martinez</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>K26</t>
+  </si>
+  <si>
+    <t>Sylvia Plath</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>PLATH</t>
+  </si>
+  <si>
+    <t>K27</t>
+  </si>
+  <si>
+    <t>Owen Rodriguez</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>K28</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>K29</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>WALKER</t>
+  </si>
+  <si>
+    <t>K30</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>HALL</t>
+  </si>
+  <si>
+    <t>K31</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>K32</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
+  </si>
+  <si>
+    <t>K33</t>
+  </si>
+  <si>
+    <t>Tristan Young</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>K34</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>K35</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>K36</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>K37</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>K38</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>K39</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>K40</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
+    <t>K41</t>
+  </si>
+  <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>K42</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
+  </si>
+  <si>
+    <t>K43</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>K44</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>DOSTOEVSKY</t>
+  </si>
+  <si>
+    <t>K45</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>ORWELL</t>
+  </si>
+  <si>
+    <t>K46</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
+    <t>K47</t>
+  </si>
+  <si>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>K48</t>
+  </si>
+  <si>
+    <t>Jane Austen</t>
+  </si>
+  <si>
+    <t>AUSTEN</t>
+  </si>
+  <si>
+    <t>K49</t>
+  </si>
+  <si>
+    <t>Kurt Vonnegut</t>
+  </si>
+  <si>
+    <t>VONNEGUT</t>
+  </si>
+  <si>
+    <t>K50</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>K51</t>
+  </si>
+  <si>
+    <t>Zachary Adams</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>K52</t>
+  </si>
+  <si>
+    <t>Oliver Walker</t>
+  </si>
+  <si>
+    <t>K53</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>K54</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>K55</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>K56</t>
+  </si>
+  <si>
+    <t>Uriel Wright</t>
+  </si>
+  <si>
+    <t>WRIGHT</t>
+  </si>
+  <si>
+    <t>K57</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>K58</t>
+  </si>
+  <si>
+    <t>Thomas Hardy</t>
+  </si>
+  <si>
+    <t>HARDY</t>
+  </si>
+  <si>
+    <t>K59</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>K60</t>
+  </si>
+  <si>
+    <t>Virginia Woolf</t>
+  </si>
+  <si>
+    <t>WOOLF</t>
+  </si>
+  <si>
+    <t>K61</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>SHAKESPEARE</t>
+  </si>
+  <si>
+    <t>K62</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>K63</t>
+  </si>
+  <si>
+    <t>Elijah Taylor</t>
+  </si>
+  <si>
+    <t>TAYLOR</t>
+  </si>
+  <si>
+    <t>K64</t>
+  </si>
+  <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
-    <t>Team Beta</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>K2</t>
+    <t>K65</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>K66</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>K67</t>
+  </si>
+  <si>
+    <t>Cersei Lannister</t>
+  </si>
+  <si>
+    <t>K68</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>K69</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>K70</t>
+  </si>
+  <si>
+    <t>Bilbo Baggins</t>
+  </si>
+  <si>
+    <t>K71</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>K72</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>K73</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>K74</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>K75</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>K76</t>
+  </si>
+  <si>
+    <t>William Wright</t>
+  </si>
+  <si>
+    <t>K77</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>K78</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>K79</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>K80</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>K81</t>
+  </si>
+  <si>
+    <t>Parker Lewis</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
+  </si>
+  <si>
+    <t>K82</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>K83</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>K84</t>
+  </si>
+  <si>
+    <t>Vincent King</t>
+  </si>
+  <si>
+    <t>K85</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>K86</t>
+  </si>
+  <si>
+    <t>Xavier Lopez</t>
+  </si>
+  <si>
+    <t>K87</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>K88</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>K89</t>
+  </si>
+  <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>K90</t>
   </si>
   <si>
     <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
-  </si>
-  <si>
-    <t>K3</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>K4</t>
-  </si>
-  <si>
-    <t>Oliver Walker</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>WALKER</t>
-  </si>
-  <si>
-    <t>K5</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>K6</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
-  </si>
-  <si>
-    <t>K7</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>YOUNG</t>
-  </si>
-  <si>
-    <t>K8</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>K9</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>K10</t>
-  </si>
-  <si>
-    <t>Uriel Wright</t>
-  </si>
-  <si>
-    <t>WRIGHT</t>
-  </si>
-  <si>
-    <t>K11</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>K12</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>K13</t>
-  </si>
-  <si>
-    <t>Xavier Scott</t>
-  </si>
-  <si>
-    <t>SCOTT</t>
-  </si>
-  <si>
-    <t>K14</t>
-  </si>
-  <si>
-    <t>Yosef Green</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>K15</t>
-  </si>
-  <si>
-    <t>Zachary Adams</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
-    <t>K16</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>THOMPSON</t>
-  </si>
-  <si>
-    <t>K17</t>
-  </si>
-  <si>
-    <t>Benjamin Evans</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>K18</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>K19</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
-  </si>
-  <si>
-    <t>K20</t>
-  </si>
-  <si>
-    <t>Elijah Taylor</t>
-  </si>
-  <si>
-    <t>TAYLOR</t>
-  </si>
-  <si>
-    <t>K21</t>
-  </si>
-  <si>
-    <t>Finn Anderson</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>K22</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
-  </si>
-  <si>
-    <t>K23</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>K24</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>K25</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>K26</t>
-  </si>
-  <si>
-    <t>Kaden Martin</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>K27</t>
-  </si>
-  <si>
-    <t>Liam Thompson</t>
-  </si>
-  <si>
-    <t>K28</t>
-  </si>
-  <si>
-    <t>Mason Martinez</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>K29</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
-  </si>
-  <si>
-    <t>K30</t>
-  </si>
-  <si>
-    <t>Owen Rodriguez</t>
-  </si>
-  <si>
-    <t>K31</t>
-  </si>
-  <si>
-    <t>Parker Lewis</t>
-  </si>
-  <si>
-    <t>K32</t>
-  </si>
-  <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>K33</t>
-  </si>
-  <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>K34</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>K35</t>
-  </si>
-  <si>
-    <t>Tristan Young</t>
-  </si>
-  <si>
-    <t>K36</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>K37</t>
-  </si>
-  <si>
-    <t>Vincent King</t>
-  </si>
-  <si>
-    <t>K38</t>
-  </si>
-  <si>
-    <t>William Wright</t>
-  </si>
-  <si>
-    <t>K39</t>
-  </si>
-  <si>
-    <t>Xavier Lopez</t>
-  </si>
-  <si>
-    <t>K40</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>K41</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
-    <t>K42</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>K43</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
-  </si>
-  <si>
-    <t>K44</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
-    <t>K45</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
-  </si>
-  <si>
-    <t>K46</t>
-  </si>
-  <si>
-    <t>Fyodor Dostoevsky</t>
-  </si>
-  <si>
-    <t>DOSTOEVSKY</t>
-  </si>
-  <si>
-    <t>K47</t>
-  </si>
-  <si>
-    <t>George Orwell</t>
-  </si>
-  <si>
-    <t>ORWELL</t>
-  </si>
-  <si>
-    <t>K48</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>K49</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>K50</t>
-  </si>
-  <si>
-    <t>Jane Austen</t>
-  </si>
-  <si>
-    <t>AUSTEN</t>
-  </si>
-  <si>
-    <t>K51</t>
-  </si>
-  <si>
-    <t>Kurt Vonnegut</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>VONNEGUT</t>
-  </si>
-  <si>
-    <t>K52</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>K53</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
-  </si>
-  <si>
-    <t>K54</t>
-  </si>
-  <si>
-    <t>Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>HAWTHORNE</t>
-  </si>
-  <si>
-    <t>K55</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>K56</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>K57</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>K58</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>K59</t>
-  </si>
-  <si>
-    <t>Sylvia Plath</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>PLATH</t>
-  </si>
-  <si>
-    <t>K60</t>
-  </si>
-  <si>
-    <t>Thomas Hardy</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>HARDY</t>
-  </si>
-  <si>
-    <t>K61</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>K62</t>
-  </si>
-  <si>
-    <t>Virginia Woolf</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>WOOLF</t>
-  </si>
-  <si>
-    <t>K63</t>
-  </si>
-  <si>
-    <t>William Shakespeare</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>SHAKESPEARE</t>
-  </si>
-  <si>
-    <t>K64</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>K65</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>K66</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>K67</t>
-  </si>
-  <si>
-    <t>Bilbo Baggins</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>K68</t>
-  </si>
-  <si>
-    <t>Cersei Lannister</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>K69</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>K70</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>K71</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>K72</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>K73</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>K74</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>K75</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>K76</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>K77</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>K78</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>K79</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>K80</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>K81</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>K82</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>K83</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>K84</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>K85</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>K86</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>K87</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>K88</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>K89</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>K90</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
   </si>
   <si>
     <t>K91</t>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -1910,1444 +1910,1444 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E40" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="E41" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="E42" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="E45" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="E46" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="E47" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="E48" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="E49" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="E50" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="E51" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="E52" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="E53" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="E54" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="D55" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="E55" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="E56" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="D57" t="s">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="E57" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E58" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C59" t="s">
-        <v>188</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E59" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>57</v>
       </c>
       <c r="D60" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>141</v>
       </c>
       <c r="D61" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E61" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E62" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="C63" t="s">
-        <v>204</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E63" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="D64" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E64" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E65" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C66" t="s">
-        <v>216</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E66" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C67" t="s">
-        <v>220</v>
+        <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E68" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C69" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="D69" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E69" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D70" t="s">
-        <v>230</v>
+        <v>142</v>
       </c>
       <c r="E70" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C71" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="D71" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E71" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D72" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E72" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C73" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E73" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C74" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E74" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D75" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E75" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D76" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E76" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C77" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="D77" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E77" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C78" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>253</v>
+        <v>126</v>
       </c>
       <c r="E78" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C79" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="E79" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="D80" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="E80" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C81" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D81" t="s">
-        <v>189</v>
+        <v>264</v>
       </c>
       <c r="E81" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C82" t="s">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E82" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C83" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E83" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B84" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C84" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="D84" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E84" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C85" t="s">
-        <v>192</v>
+        <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E85" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E86" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="B87" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="E87" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C88" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="E88" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B89" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C89" t="s">
-        <v>208</v>
+        <v>57</v>
       </c>
       <c r="D89" t="s">
-        <v>284</v>
+        <v>50</v>
       </c>
       <c r="E89" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C90" t="s">
-        <v>212</v>
+        <v>41</v>
       </c>
       <c r="D90" t="s">
-        <v>287</v>
+        <v>54</v>
       </c>
       <c r="E90" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C91" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D91" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E91" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E92" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="B93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D93" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="E93" t="s">
         <v>297</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>181</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
@@ -3401,7 +3401,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3430,7 +3430,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>201</v>
+        <v>115</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3485,7 +3485,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3542,7 +3542,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3622,7 +3622,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
@@ -3636,7 +3636,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3673,7 +3673,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>287</v>
+        <v>150</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>290</v>
+        <v>154</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3728,7 +3728,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3785,7 +3785,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
@@ -3874,7 +3874,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3903,7 +3903,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3924,7 +3924,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3958,7 +3958,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>68</v>
+        <v>192</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4015,7 +4015,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4095,7 +4095,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>53</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
@@ -4126,7 +4126,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4146,7 +4146,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4201,7 +4201,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4258,7 +4258,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
@@ -4347,7 +4347,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -4376,7 +4376,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4397,7 +4397,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4431,7 +4431,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4488,7 +4488,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>53</v>
+        <v>204</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4506,7 +4506,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>27</v>
+        <v>273</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4731,7 +4731,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4763,7 +4763,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>27</v>
+        <v>273</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4796,362 +4796,362 @@
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17" t="str">
-        <f>'data'!$E$28</f>
+        <f>'data'!$E$4</f>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D28</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17" t="str">
-        <f>'data'!$E$79</f>
+        <f>'data'!$E$5</f>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D79</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17" t="str">
-        <f>'data'!$E$58</f>
+        <f>'data'!$E$6</f>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D58</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17" t="str">
-        <f>'data'!$E$59</f>
+        <f>'data'!$E$7</f>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D59</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17" t="str">
-        <f>'data'!$E$29</f>
+        <f>'data'!$E$8</f>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D29</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17" t="str">
-        <f>'data'!$E$12</f>
+        <f>'data'!$E$9</f>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17" t="str">
-        <f>'data'!$E$61</f>
+        <f>'data'!$E$10</f>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D61</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17" t="str">
-        <f>'data'!$E$14</f>
+        <f>'data'!$E$11</f>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D14</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17" t="str">
-        <f>'data'!$E$15</f>
+        <f>'data'!$E$12</f>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D15</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17" t="str">
-        <f>'data'!$E$16</f>
+        <f>'data'!$E$13</f>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D16</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17" t="str">
-        <f>'data'!$E$17</f>
+        <f>'data'!$E$14</f>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D17</f>
+        <f>'data'!D14</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17" t="str">
-        <f>'data'!$E$56</f>
+        <f>'data'!$E$15</f>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D56</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17" t="str">
-        <f>'data'!$E$85</f>
+        <f>'data'!$E$16</f>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D85</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
       <c r="A15" s="17" t="str">
-        <f>'data'!$E$20</f>
+        <f>'data'!$E$17</f>
       </c>
       <c r="B15" s="18" t="str">
-        <f>'data'!D20</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
       <c r="A16" s="17" t="str">
-        <f>'data'!$E$21</f>
+        <f>'data'!$E$18</f>
       </c>
       <c r="B16" s="18" t="str">
-        <f>'data'!D21</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
       <c r="A17" s="17" t="str">
-        <f>'data'!$E$22</f>
+        <f>'data'!$E$19</f>
       </c>
       <c r="B17" s="18" t="str">
-        <f>'data'!D22</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
       <c r="A18" s="17" t="str">
-        <f>'data'!$E$68</f>
+        <f>'data'!$E$20</f>
       </c>
       <c r="B18" s="18" t="str">
-        <f>'data'!D68</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
       <c r="A19" s="17" t="str">
-        <f>'data'!$E$24</f>
+        <f>'data'!$E$21</f>
       </c>
       <c r="B19" s="18" t="str">
-        <f>'data'!D24</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17" t="str">
-        <f>'data'!$E$25</f>
+        <f>'data'!$E$22</f>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D25</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
       <c r="A21" s="17" t="str">
-        <f>'data'!$E$26</f>
+        <f>'data'!$E$23</f>
       </c>
       <c r="B21" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
       <c r="A22" s="17" t="str">
-        <f>'data'!$E$27</f>
+        <f>'data'!$E$24</f>
       </c>
       <c r="B22" s="18" t="str">
-        <f>'data'!D27</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
       <c r="A23" s="17" t="str">
-        <f>'data'!$E$57</f>
+        <f>'data'!$E$25</f>
       </c>
       <c r="B23" s="18" t="str">
-        <f>'data'!D57</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
       <c r="A24" s="17" t="str">
-        <f>'data'!$E$55</f>
+        <f>'data'!$E$26</f>
       </c>
       <c r="B24" s="18" t="str">
-        <f>'data'!D55</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
       <c r="A25" s="17" t="str">
-        <f>'data'!$E$30</f>
+        <f>'data'!$E$27</f>
       </c>
       <c r="B25" s="18" t="str">
-        <f>'data'!D30</f>
+        <f>'data'!D27</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
       <c r="A26" s="17" t="str">
-        <f>'data'!$E$31</f>
+        <f>'data'!$E$28</f>
       </c>
       <c r="B26" s="18" t="str">
-        <f>'data'!D31</f>
+        <f>'data'!D28</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
       <c r="A27" s="17" t="str">
-        <f>'data'!$E$62</f>
+        <f>'data'!$E$29</f>
       </c>
       <c r="B27" s="18" t="str">
-        <f>'data'!D62</f>
+        <f>'data'!D29</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
       <c r="A28" s="17" t="str">
-        <f>'data'!$E$33</f>
+        <f>'data'!$E$30</f>
       </c>
       <c r="B28" s="18" t="str">
-        <f>'data'!D33</f>
+        <f>'data'!D30</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
       <c r="A29" s="17" t="str">
-        <f>'data'!$E$19</f>
+        <f>'data'!$E$31</f>
       </c>
       <c r="B29" s="18" t="str">
-        <f>'data'!D19</f>
+        <f>'data'!D31</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
       <c r="A30" s="17" t="str">
-        <f>'data'!$E$35</f>
+        <f>'data'!$E$32</f>
       </c>
       <c r="B30" s="18" t="str">
-        <f>'data'!D35</f>
+        <f>'data'!D32</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
       <c r="A31" s="17" t="str">
-        <f>'data'!$E$36</f>
+        <f>'data'!$E$33</f>
       </c>
       <c r="B31" s="18" t="str">
-        <f>'data'!D36</f>
+        <f>'data'!D33</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
       <c r="A32" s="17" t="str">
-        <f>'data'!$E$37</f>
+        <f>'data'!$E$34</f>
       </c>
       <c r="B32" s="18" t="str">
-        <f>'data'!D37</f>
+        <f>'data'!D34</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17" t="str">
-        <f>'data'!$E$6</f>
+        <f>'data'!$E$35</f>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D6</f>
+        <f>'data'!D35</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
       <c r="A34" s="17" t="str">
-        <f>'data'!$E$38</f>
+        <f>'data'!$E$36</f>
       </c>
       <c r="B34" s="18" t="str">
-        <f>'data'!D38</f>
+        <f>'data'!D36</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17" t="str">
-        <f>'data'!$E$39</f>
+        <f>'data'!$E$37</f>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D39</f>
+        <f>'data'!D37</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
       <c r="A36" s="17" t="str">
-        <f>'data'!$E$88</f>
+        <f>'data'!$E$38</f>
       </c>
       <c r="B36" s="18" t="str">
-        <f>'data'!D88</f>
+        <f>'data'!D38</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17" t="str">
-        <f>'data'!$E$64</f>
+        <f>'data'!$E$39</f>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D64</f>
+        <f>'data'!D39</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17" t="str">
-        <f>'data'!$E$90</f>
+        <f>'data'!$E$40</f>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D90</f>
+        <f>'data'!D40</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
       <c r="A39" s="17" t="str">
-        <f>'data'!$E$91</f>
+        <f>'data'!$E$41</f>
       </c>
       <c r="B39" s="18" t="str">
-        <f>'data'!D91</f>
+        <f>'data'!D41</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
       <c r="A40" s="17" t="str">
-        <f>'data'!$E$44</f>
+        <f>'data'!$E$42</f>
       </c>
       <c r="B40" s="18" t="str">
-        <f>'data'!D44</f>
+        <f>'data'!D42</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
       <c r="A41" s="17" t="str">
-        <f>'data'!$E$45</f>
+        <f>'data'!$E$43</f>
       </c>
       <c r="B41" s="18" t="str">
-        <f>'data'!D45</f>
+        <f>'data'!D43</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
       <c r="A42" s="17" t="str">
-        <f>'data'!$E$46</f>
+        <f>'data'!$E$44</f>
       </c>
       <c r="B42" s="18" t="str">
-        <f>'data'!D46</f>
+        <f>'data'!D44</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
       <c r="A43" s="17" t="str">
-        <f>'data'!$E$47</f>
+        <f>'data'!$E$45</f>
       </c>
       <c r="B43" s="18" t="str">
-        <f>'data'!D47</f>
+        <f>'data'!D45</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
       <c r="A44" s="17" t="str">
-        <f>'data'!$E$48</f>
+        <f>'data'!$E$46</f>
       </c>
       <c r="B44" s="18" t="str">
-        <f>'data'!D48</f>
+        <f>'data'!D46</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
       <c r="A45" s="17" t="str">
-        <f>'data'!$E$49</f>
+        <f>'data'!$E$47</f>
       </c>
       <c r="B45" s="18" t="str">
-        <f>'data'!D49</f>
+        <f>'data'!D47</f>
       </c>
     </row>
     <row r="46" ht="270" customHeight="true">
       <c r="A46" s="17" t="str">
-        <f>'data'!$E$50</f>
+        <f>'data'!$E$48</f>
       </c>
       <c r="B46" s="18" t="str">
-        <f>'data'!D50</f>
+        <f>'data'!D48</f>
       </c>
     </row>
   </sheetData>
@@ -5189,362 +5189,362 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17" t="str">
-        <f>'data'!$E$51</f>
+        <f>'data'!$E$49</f>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D51</f>
+        <f>'data'!D49</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17" t="str">
-        <f>'data'!$E$52</f>
+        <f>'data'!$E$50</f>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D52</f>
+        <f>'data'!D50</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17" t="str">
-        <f>'data'!$E$53</f>
+        <f>'data'!$E$51</f>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D53</f>
+        <f>'data'!D51</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17" t="str">
-        <f>'data'!$E$54</f>
+        <f>'data'!$E$52</f>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D54</f>
+        <f>'data'!D52</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17" t="str">
-        <f>'data'!$E$11</f>
+        <f>'data'!$E$53</f>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D11</f>
+        <f>'data'!D53</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17" t="str">
-        <f>'data'!$E$18</f>
+        <f>'data'!$E$54</f>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D18</f>
+        <f>'data'!D54</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17" t="str">
-        <f>'data'!$E$7</f>
+        <f>'data'!$E$55</f>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D7</f>
+        <f>'data'!D55</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17" t="str">
-        <f>'data'!$E$9</f>
+        <f>'data'!$E$56</f>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D9</f>
+        <f>'data'!D56</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17" t="str">
-        <f>'data'!$E$10</f>
+        <f>'data'!$E$57</f>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D10</f>
+        <f>'data'!D57</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17" t="str">
-        <f>'data'!$E$60</f>
+        <f>'data'!$E$58</f>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D60</f>
+        <f>'data'!D58</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17" t="str">
-        <f>'data'!$E$13</f>
+        <f>'data'!$E$59</f>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D59</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17" t="str">
-        <f>'data'!$E$32</f>
+        <f>'data'!$E$60</f>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D32</f>
+        <f>'data'!D60</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17" t="str">
-        <f>'data'!$E$63</f>
+        <f>'data'!$E$61</f>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D63</f>
+        <f>'data'!D61</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17" t="str">
-        <f>'data'!$E$80</f>
+        <f>'data'!$E$62</f>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D80</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
       <c r="A15" s="17" t="str">
-        <f>'data'!$E$65</f>
+        <f>'data'!$E$63</f>
       </c>
       <c r="B15" s="18" t="str">
-        <f>'data'!D65</f>
+        <f>'data'!D63</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
       <c r="A16" s="17" t="str">
-        <f>'data'!$E$66</f>
+        <f>'data'!$E$64</f>
       </c>
       <c r="B16" s="18" t="str">
-        <f>'data'!D66</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
       <c r="A17" s="17" t="str">
-        <f>'data'!$E$67</f>
+        <f>'data'!$E$65</f>
       </c>
       <c r="B17" s="18" t="str">
-        <f>'data'!D67</f>
+        <f>'data'!D65</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
       <c r="A18" s="17" t="str">
-        <f>'data'!$E$23</f>
+        <f>'data'!$E$66</f>
       </c>
       <c r="B18" s="18" t="str">
-        <f>'data'!D23</f>
+        <f>'data'!D66</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
       <c r="A19" s="17" t="str">
-        <f>'data'!$E$4</f>
+        <f>'data'!$E$67</f>
       </c>
       <c r="B19" s="18" t="str">
-        <f>'data'!D4</f>
+        <f>'data'!D67</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17" t="str">
-        <f>'data'!$E$69</f>
+        <f>'data'!$E$68</f>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D69</f>
+        <f>'data'!D68</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
       <c r="A21" s="17" t="str">
-        <f>'data'!$E$74</f>
+        <f>'data'!$E$69</f>
       </c>
       <c r="B21" s="18" t="str">
-        <f>'data'!D74</f>
+        <f>'data'!D69</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
       <c r="A22" s="17" t="str">
-        <f>'data'!$E$71</f>
+        <f>'data'!$E$70</f>
       </c>
       <c r="B22" s="18" t="str">
-        <f>'data'!D71</f>
+        <f>'data'!D70</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
       <c r="A23" s="17" t="str">
-        <f>'data'!$E$72</f>
+        <f>'data'!$E$71</f>
       </c>
       <c r="B23" s="18" t="str">
-        <f>'data'!D72</f>
+        <f>'data'!D71</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
       <c r="A24" s="17" t="str">
-        <f>'data'!$E$73</f>
+        <f>'data'!$E$72</f>
       </c>
       <c r="B24" s="18" t="str">
-        <f>'data'!D73</f>
+        <f>'data'!D72</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
       <c r="A25" s="17" t="str">
-        <f>'data'!$E$70</f>
+        <f>'data'!$E$73</f>
       </c>
       <c r="B25" s="18" t="str">
-        <f>'data'!D70</f>
+        <f>'data'!D73</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
       <c r="A26" s="17" t="str">
-        <f>'data'!$E$75</f>
+        <f>'data'!$E$74</f>
       </c>
       <c r="B26" s="18" t="str">
-        <f>'data'!D75</f>
+        <f>'data'!D74</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
       <c r="A27" s="17" t="str">
-        <f>'data'!$E$76</f>
+        <f>'data'!$E$75</f>
       </c>
       <c r="B27" s="18" t="str">
-        <f>'data'!D76</f>
+        <f>'data'!D75</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
       <c r="A28" s="17" t="str">
-        <f>'data'!$E$77</f>
+        <f>'data'!$E$76</f>
       </c>
       <c r="B28" s="18" t="str">
-        <f>'data'!D77</f>
+        <f>'data'!D76</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
       <c r="A29" s="17" t="str">
-        <f>'data'!$E$78</f>
+        <f>'data'!$E$77</f>
       </c>
       <c r="B29" s="18" t="str">
-        <f>'data'!D78</f>
+        <f>'data'!D77</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
       <c r="A30" s="17" t="str">
-        <f>'data'!$E$8</f>
+        <f>'data'!$E$78</f>
       </c>
       <c r="B30" s="18" t="str">
-        <f>'data'!D8</f>
+        <f>'data'!D78</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
       <c r="A31" s="17" t="str">
-        <f>'data'!$E$41</f>
+        <f>'data'!$E$79</f>
       </c>
       <c r="B31" s="18" t="str">
-        <f>'data'!D41</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
       <c r="A32" s="17" t="str">
-        <f>'data'!$E$81</f>
+        <f>'data'!$E$80</f>
       </c>
       <c r="B32" s="18" t="str">
-        <f>'data'!D81</f>
+        <f>'data'!D80</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17" t="str">
-        <f>'data'!$E$82</f>
+        <f>'data'!$E$81</f>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D82</f>
+        <f>'data'!D81</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
       <c r="A34" s="17" t="str">
-        <f>'data'!$E$83</f>
+        <f>'data'!$E$82</f>
       </c>
       <c r="B34" s="18" t="str">
-        <f>'data'!D83</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17" t="str">
-        <f>'data'!$E$84</f>
+        <f>'data'!$E$83</f>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D84</f>
+        <f>'data'!D83</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
       <c r="A36" s="17" t="str">
-        <f>'data'!$E$34</f>
+        <f>'data'!$E$84</f>
       </c>
       <c r="B36" s="18" t="str">
-        <f>'data'!D34</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17" t="str">
-        <f>'data'!$E$86</f>
+        <f>'data'!$E$85</f>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D86</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17" t="str">
-        <f>'data'!$E$87</f>
+        <f>'data'!$E$86</f>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D87</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
       <c r="A39" s="17" t="str">
-        <f>'data'!$E$40</f>
+        <f>'data'!$E$87</f>
       </c>
       <c r="B39" s="18" t="str">
-        <f>'data'!D40</f>
+        <f>'data'!D87</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
       <c r="A40" s="17" t="str">
-        <f>'data'!$E$89</f>
+        <f>'data'!$E$88</f>
       </c>
       <c r="B40" s="18" t="str">
-        <f>'data'!D89</f>
+        <f>'data'!D88</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
       <c r="A41" s="17" t="str">
-        <f>'data'!$E$42</f>
+        <f>'data'!$E$89</f>
       </c>
       <c r="B41" s="18" t="str">
-        <f>'data'!D42</f>
+        <f>'data'!D89</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
       <c r="A42" s="17" t="str">
-        <f>'data'!$E$43</f>
+        <f>'data'!$E$90</f>
       </c>
       <c r="B42" s="18" t="str">
-        <f>'data'!D43</f>
+        <f>'data'!D90</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
       <c r="A43" s="17" t="str">
-        <f>'data'!$E$92</f>
+        <f>'data'!$E$91</f>
       </c>
       <c r="B43" s="18" t="str">
-        <f>'data'!D92</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
       <c r="A44" s="17" t="str">
-        <f>'data'!$E$93</f>
+        <f>'data'!$E$92</f>
       </c>
       <c r="B44" s="18" t="str">
-        <f>'data'!D93</f>
+        <f>'data'!D92</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
       <c r="A45" s="17" t="str">
-        <f>'data'!$E$5</f>
+        <f>'data'!$E$93</f>
       </c>
       <c r="B45" s="18" t="str">
-        <f>'data'!D5</f>
+        <f>'data'!D93</f>
       </c>
     </row>
   </sheetData>
@@ -5929,7 +5929,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$28</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5937,10 +5937,10 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$60</f>
       </c>
       <c r="I4" s="19" t="str">
-        <f>'data'!$B$51</f>
+        <f>'data'!$B$49</f>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
@@ -5948,7 +5948,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
-        <f>'data'!$B$50</f>
+        <f>'data'!$B$48</f>
       </c>
     </row>
     <row r="6">
@@ -6013,7 +6013,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$80</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -6021,10 +6021,10 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I12" s="19" t="str">
-        <f>'data'!$B$54</f>
+        <f>'data'!$B$52</f>
       </c>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
@@ -6032,7 +6032,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
-        <f>'data'!$B$53</f>
+        <f>'data'!$B$51</f>
       </c>
     </row>
     <row r="14">
@@ -6097,7 +6097,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$61</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -6105,10 +6105,10 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$87</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -6116,7 +6116,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$54</f>
       </c>
     </row>
     <row r="22">
@@ -6181,7 +6181,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="str">
-        <f>'data'!$B$16</f>
+        <f>'data'!$B$13</f>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -6189,10 +6189,10 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$90</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$60</f>
+        <f>'data'!$B$58</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -6200,7 +6200,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$57</f>
       </c>
     </row>
     <row r="30">
@@ -6265,7 +6265,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="str">
-        <f>'data'!$B$56</f>
+        <f>'data'!$B$15</f>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -6273,10 +6273,10 @@
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
       <c r="G36" s="19" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$14</f>
       </c>
       <c r="I36" s="19" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$61</f>
       </c>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
@@ -6284,7 +6284,7 @@
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="19" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$60</f>
       </c>
     </row>
     <row r="38">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -6357,10 +6357,10 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="19" t="str">
-        <f>'data'!$B$20</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="I44" s="19" t="str">
-        <f>'data'!$B$66</f>
+        <f>'data'!$B$64</f>
       </c>
       <c r="J44" s="22"/>
       <c r="K44" s="22"/>
@@ -6368,7 +6368,7 @@
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
       <c r="O44" s="19" t="str">
-        <f>'data'!$B$65</f>
+        <f>'data'!$B$63</f>
       </c>
     </row>
     <row r="46">
@@ -6433,7 +6433,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="str">
-        <f>'data'!$B$24</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -6441,10 +6441,10 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
-        <f>'data'!$B$68</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="I52" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$67</f>
       </c>
       <c r="J52" s="22"/>
       <c r="K52" s="22"/>
@@ -6452,7 +6452,7 @@
       <c r="M52" s="22"/>
       <c r="N52" s="22"/>
       <c r="O52" s="19" t="str">
-        <f>'data'!$B$23</f>
+        <f>'data'!$B$66</f>
       </c>
     </row>
     <row r="54">
@@ -6517,7 +6517,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="str">
-        <f>'data'!$B$27</f>
+        <f>'data'!$B$24</f>
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -6525,10 +6525,10 @@
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
       <c r="G60" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$23</f>
       </c>
       <c r="I60" s="19" t="str">
-        <f>'data'!$B$71</f>
+        <f>'data'!$B$70</f>
       </c>
       <c r="J60" s="22"/>
       <c r="K60" s="22"/>
@@ -6536,7 +6536,7 @@
       <c r="M60" s="22"/>
       <c r="N60" s="22"/>
       <c r="O60" s="19" t="str">
-        <f>'data'!$B$70</f>
+        <f>'data'!$B$73</f>
       </c>
     </row>
     <row r="62">
@@ -6601,7 +6601,7 @@
     </row>
     <row r="68">
       <c r="A68" s="19" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -6609,10 +6609,10 @@
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
       <c r="G68" s="19" t="str">
-        <f>'data'!$B$57</f>
+        <f>'data'!$B$25</f>
       </c>
       <c r="I68" s="19" t="str">
-        <f>'data'!$B$73</f>
+        <f>'data'!$B$72</f>
       </c>
       <c r="J68" s="22"/>
       <c r="K68" s="22"/>
@@ -6620,7 +6620,7 @@
       <c r="M68" s="22"/>
       <c r="N68" s="22"/>
       <c r="O68" s="19" t="str">
-        <f>'data'!$B$72</f>
+        <f>'data'!$B$71</f>
       </c>
     </row>
     <row r="70">
@@ -6685,7 +6685,7 @@
     </row>
     <row r="76">
       <c r="A76" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -6693,10 +6693,10 @@
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
       <c r="G76" s="19" t="str">
-        <f>'data'!$B$31</f>
+        <f>'data'!$B$28</f>
       </c>
       <c r="I76" s="19" t="str">
-        <f>'data'!$B$76</f>
+        <f>'data'!$B$75</f>
       </c>
       <c r="J76" s="22"/>
       <c r="K76" s="22"/>
@@ -6704,7 +6704,7 @@
       <c r="M76" s="22"/>
       <c r="N76" s="22"/>
       <c r="O76" s="19" t="str">
-        <f>'data'!$B$75</f>
+        <f>'data'!$B$74</f>
       </c>
     </row>
     <row r="78">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="84">
       <c r="A84" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -6777,10 +6777,10 @@
       <c r="E84" s="22"/>
       <c r="F84" s="22"/>
       <c r="G84" s="19" t="str">
-        <f>'data'!$B$19</f>
+        <f>'data'!$B$31</f>
       </c>
       <c r="I84" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$78</f>
       </c>
       <c r="J84" s="22"/>
       <c r="K84" s="22"/>
@@ -6788,7 +6788,7 @@
       <c r="M84" s="22"/>
       <c r="N84" s="22"/>
       <c r="O84" s="19" t="str">
-        <f>'data'!$B$78</f>
+        <f>'data'!$B$77</f>
       </c>
     </row>
     <row r="86">
@@ -6853,7 +6853,7 @@
     </row>
     <row r="92">
       <c r="A92" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6861,10 +6861,10 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$56</f>
       </c>
       <c r="I92" s="19" t="str">
-        <f>'data'!$B$82</f>
+        <f>'data'!$B$81</f>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="22"/>
@@ -6872,7 +6872,7 @@
       <c r="M92" s="22"/>
       <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$80</f>
       </c>
     </row>
     <row r="94">
@@ -6937,7 +6937,7 @@
     </row>
     <row r="100">
       <c r="A100" s="19" t="str">
-        <f>'data'!$B$71</f>
+        <f>'data'!$B$70</f>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6945,10 +6945,10 @@
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$53</f>
       </c>
       <c r="I100" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$93</f>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -6956,7 +6956,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$83</f>
       </c>
     </row>
     <row r="102">
@@ -7021,7 +7021,7 @@
     </row>
     <row r="108">
       <c r="A108" s="19" t="str">
-        <f>'data'!$B$91</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -7029,10 +7029,10 @@
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="19" t="str">
-        <f>'data'!$B$90</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I108" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$87</f>
       </c>
       <c r="J108" s="22"/>
       <c r="K108" s="22"/>
@@ -7040,7 +7040,7 @@
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
-        <f>'data'!$B$87</f>
+        <f>'data'!$B$86</f>
       </c>
     </row>
     <row r="110">
@@ -7105,7 +7105,7 @@
     </row>
     <row r="116">
       <c r="A116" s="19" t="str">
-        <f>'data'!$B$46</f>
+        <f>'data'!$B$44</f>
       </c>
       <c r="B116" s="22"/>
       <c r="C116" s="22"/>
@@ -7113,10 +7113,10 @@
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
       <c r="G116" s="19" t="str">
-        <f>'data'!$B$45</f>
+        <f>'data'!$B$43</f>
       </c>
       <c r="I116" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$90</f>
       </c>
       <c r="J116" s="22"/>
       <c r="K116" s="22"/>
@@ -7124,7 +7124,7 @@
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
       <c r="O116" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$89</f>
       </c>
     </row>
     <row r="118">
@@ -7189,7 +7189,7 @@
     </row>
     <row r="124">
       <c r="A124" s="19" t="str">
-        <f>'data'!$B$49</f>
+        <f>'data'!$B$47</f>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -7197,10 +7197,10 @@
       <c r="E124" s="22"/>
       <c r="F124" s="22"/>
       <c r="G124" s="19" t="str">
-        <f>'data'!$B$48</f>
+        <f>'data'!$B$46</f>
       </c>
       <c r="I124" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$93</f>
       </c>
       <c r="J124" s="22"/>
       <c r="K124" s="22"/>
@@ -7208,7 +7208,7 @@
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="19" t="str">
-        <f>'data'!$B$93</f>
+        <f>'data'!$B$92</f>
       </c>
     </row>
     <row r="126">
@@ -7281,7 +7281,7 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$79</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 18 ",O14)</f>
@@ -7292,7 +7292,7 @@
       <c r="M137" s="22"/>
       <c r="N137" s="22"/>
       <c r="O137" s="19" t="str">
-        <f>'data'!$B$52</f>
+        <f>'data'!$B$50</f>
       </c>
     </row>
     <row r="139">
@@ -7365,7 +7365,7 @@
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
-        <f>'data'!$B$29</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="I145" s="19" t="str">
         <f>CONCATENATE("M 19 ",O22)</f>
@@ -7376,7 +7376,7 @@
       <c r="M145" s="22"/>
       <c r="N145" s="22"/>
       <c r="O145" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$53</f>
       </c>
     </row>
     <row r="147">
@@ -7449,7 +7449,7 @@
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$89</f>
       </c>
       <c r="I153" s="19" t="str">
         <f>CONCATENATE("M 20 ",O30)</f>
@@ -7460,7 +7460,7 @@
       <c r="M153" s="22"/>
       <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$56</f>
       </c>
     </row>
     <row r="155">
@@ -7533,7 +7533,7 @@
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
       <c r="G161" s="19" t="str">
-        <f>'data'!$B$85</f>
+        <f>'data'!$B$16</f>
       </c>
       <c r="I161" s="19" t="str">
         <f>CONCATENATE("M 21 ",O38)</f>
@@ -7544,7 +7544,7 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$79</f>
       </c>
     </row>
     <row r="163">
@@ -7617,7 +7617,7 @@
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
       <c r="G169" s="19" t="str">
-        <f>'data'!$B$22</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="I169" s="19" t="str">
         <f>CONCATENATE("M 22 ",O46)</f>
@@ -7628,7 +7628,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$80</f>
+        <f>'data'!$B$62</f>
       </c>
     </row>
     <row r="171">
@@ -7701,7 +7701,7 @@
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
       <c r="G177" s="19" t="str">
-        <f>'data'!$B$25</f>
+        <f>'data'!$B$22</f>
       </c>
       <c r="I177" s="19" t="str">
         <f>CONCATENATE("M 23 ",O54)</f>
@@ -7712,7 +7712,7 @@
       <c r="M177" s="22"/>
       <c r="N177" s="22"/>
       <c r="O177" s="19" t="str">
-        <f>'data'!$B$67</f>
+        <f>'data'!$B$65</f>
       </c>
     </row>
     <row r="179">
@@ -7785,7 +7785,7 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$19</f>
+        <f>'data'!$B$31</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>CONCATENATE("M 24 ",O62)</f>
@@ -7796,7 +7796,7 @@
       <c r="M185" s="22"/>
       <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
-        <f>'data'!$B$69</f>
+        <f>'data'!$B$68</f>
       </c>
     </row>
     <row r="187">
@@ -7869,7 +7869,7 @@
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
       <c r="G193" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$67</f>
       </c>
       <c r="I193" s="19" t="str">
         <f>CONCATENATE("M 26 ",O78)</f>
@@ -7880,7 +7880,7 @@
       <c r="M193" s="22"/>
       <c r="N193" s="22"/>
       <c r="O193" s="19" t="str">
-        <f>'data'!$B$70</f>
+        <f>'data'!$B$73</f>
       </c>
     </row>
     <row r="195">
@@ -7953,7 +7953,7 @@
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$78</f>
       </c>
       <c r="I201" s="19" t="str">
         <f>CONCATENATE("M 27 ",O86)</f>
@@ -7964,7 +7964,7 @@
       <c r="M201" s="22"/>
       <c r="N201" s="22"/>
       <c r="O201" s="19" t="str">
-        <f>'data'!$B$77</f>
+        <f>'data'!$B$76</f>
       </c>
     </row>
     <row r="203">
@@ -8037,7 +8037,7 @@
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$57</f>
       </c>
       <c r="I209" s="19" t="str">
         <f>CONCATENATE("M 28 ",O94)</f>
@@ -8048,7 +8048,7 @@
       <c r="M209" s="22"/>
       <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$79</f>
       </c>
     </row>
     <row r="211">
@@ -8121,7 +8121,7 @@
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="I217" s="19" t="str">
         <f>CONCATENATE("M 29 ",O102)</f>
@@ -8132,7 +8132,7 @@
       <c r="M217" s="22"/>
       <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
-        <f>'data'!$B$83</f>
+        <f>'data'!$B$82</f>
       </c>
     </row>
     <row r="219">
@@ -8205,7 +8205,7 @@
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
       <c r="G225" s="19" t="str">
-        <f>'data'!$B$44</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I225" s="19" t="str">
         <f>CONCATENATE("M 30 ",O110)</f>
@@ -8216,7 +8216,7 @@
       <c r="M225" s="22"/>
       <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$85</f>
       </c>
     </row>
     <row r="227">
@@ -8289,7 +8289,7 @@
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
       <c r="G233" s="19" t="str">
-        <f>'data'!$B$47</f>
+        <f>'data'!$B$45</f>
       </c>
       <c r="I233" s="19" t="str">
         <f>CONCATENATE("M 31 ",O118)</f>
@@ -8300,7 +8300,7 @@
       <c r="M233" s="22"/>
       <c r="N233" s="22"/>
       <c r="O233" s="19" t="str">
-        <f>'data'!$B$89</f>
+        <f>'data'!$B$88</f>
       </c>
     </row>
     <row r="235">
@@ -8355,7 +8355,7 @@
       <c r="M241" s="22"/>
       <c r="N241" s="22"/>
       <c r="O241" s="19" t="str">
-        <f>'data'!$B$92</f>
+        <f>'data'!$B$91</f>
       </c>
     </row>
     <row r="243">
@@ -9834,7 +9834,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9863,7 +9863,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>256</v>
+        <v>27</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9900,7 +9900,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9918,7 +9918,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9935,7 +9935,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9954,7 +9954,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>197</v>
+        <v>46</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9975,7 +9975,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -10053,7 +10053,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -10064,7 +10064,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -10093,7 +10093,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>273</v>
+        <v>69</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -10114,7 +10114,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -10148,7 +10148,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -10165,7 +10165,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -10184,7 +10184,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -10205,7 +10205,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -10223,7 +10223,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -10237,7 +10237,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
